--- a/database/event/5246/event_5246_evp_summary.xlsx
+++ b/database/event/5246/event_5246_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.1771</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6769</v>
+        <v>2.6115</v>
       </c>
       <c r="E2" t="n">
         <v>7.6693</v>
@@ -548,7 +548,7 @@
         <v>1.1715</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6623</v>
+        <v>2.5972</v>
       </c>
       <c r="E3" t="n">
         <v>7.6332</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9519</v>
+        <v>5.9371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9135</v>
+        <v>0.9112</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9831</v>
+        <v>1.9214</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9519</v>
+        <v>5.9371</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4434</v>
+        <v>5.4286</v>
       </c>
       <c r="G4" t="n">
         <v>0.5085</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2322</v>
+        <v>6.209</v>
       </c>
       <c r="I4" t="n">
         <v>6.2612</v>
@@ -640,7 +640,7 @@
         <v>0.8418</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7943</v>
+        <v>1.7412</v>
       </c>
       <c r="E5" t="n">
         <v>5.4846</v>
@@ -686,7 +686,7 @@
         <v>0.7798</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6313</v>
+        <v>1.5804</v>
       </c>
       <c r="E6" t="n">
         <v>5.0812</v>
@@ -732,7 +732,7 @@
         <v>0.6287</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2335</v>
+        <v>1.1881</v>
       </c>
       <c r="E7" t="n">
         <v>4.0964</v>
@@ -778,7 +778,7 @@
         <v>0.4697</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8151</v>
+        <v>0.7755</v>
       </c>
       <c r="E8" t="n">
         <v>3.0607</v>
@@ -824,7 +824,7 @@
         <v>0.4599</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7891</v>
+        <v>0.7499</v>
       </c>
       <c r="E9" t="n">
         <v>2.9964</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9712</v>
+        <v>2.9564</v>
       </c>
       <c r="C10" t="n">
-        <v>0.456</v>
+        <v>0.4537</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7789</v>
+        <v>0.7339</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9712</v>
+        <v>2.9564</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9712</v>
+        <v>3.9564</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9712</v>
+        <v>3.9564</v>
       </c>
       <c r="I10" t="n">
         <v>3.9897</v>
@@ -916,7 +916,7 @@
         <v>0.4462</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7531</v>
+        <v>0.7144</v>
       </c>
       <c r="E11" t="n">
         <v>2.9073</v>
@@ -962,7 +962,7 @@
         <v>0.4461</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7529</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2.9068</v>
@@ -1008,7 +1008,7 @@
         <v>0.4404</v>
       </c>
       <c r="D13" t="n">
-        <v>0.738</v>
+        <v>0.6994</v>
       </c>
       <c r="E13" t="n">
         <v>2.8698</v>
@@ -1054,7 +1054,7 @@
         <v>0.3596</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5252</v>
+        <v>0.4895</v>
       </c>
       <c r="E14" t="n">
         <v>2.343</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.055</v>
+        <v>2.0436</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3154</v>
+        <v>0.3136</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4088</v>
+        <v>0.3703</v>
       </c>
       <c r="E15" t="n">
-        <v>2.055</v>
+        <v>2.0436</v>
       </c>
       <c r="F15" t="n">
-        <v>3.055</v>
+        <v>3.0436</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.055</v>
+        <v>3.0436</v>
       </c>
       <c r="I15" t="n">
         <v>3.0692</v>
@@ -1146,7 +1146,7 @@
         <v>0.2935</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3512</v>
+        <v>0.318</v>
       </c>
       <c r="E16" t="n">
         <v>1.9125</v>
@@ -1192,7 +1192,7 @@
         <v>0.2278</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1783</v>
+        <v>0.1474</v>
       </c>
       <c r="E17" t="n">
         <v>1.4843</v>
@@ -1238,7 +1238,7 @@
         <v>0.2134</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1403</v>
+        <v>0.11</v>
       </c>
       <c r="E18" t="n">
         <v>1.3904</v>
@@ -1284,7 +1284,7 @@
         <v>0.1936</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0882</v>
+        <v>0.0586</v>
       </c>
       <c r="E19" t="n">
         <v>1.2613</v>
@@ -1330,7 +1330,7 @@
         <v>0.1863</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0689</v>
+        <v>0.0396</v>
       </c>
       <c r="E20" t="n">
         <v>1.2137</v>
@@ -1376,7 +1376,7 @@
         <v>0.1718</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0308</v>
+        <v>0.002</v>
       </c>
       <c r="E21" t="n">
         <v>1.1193</v>
@@ -1422,7 +1422,7 @@
         <v>0.1196</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1065</v>
+        <v>-0.1334</v>
       </c>
       <c r="E22" t="n">
         <v>0.7793</v>
@@ -1468,7 +1468,7 @@
         <v>0.0936</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.175</v>
+        <v>-0.201</v>
       </c>
       <c r="E23" t="n">
         <v>0.6098</v>
@@ -1514,7 +1514,7 @@
         <v>0.057</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2714</v>
+        <v>-0.2961</v>
       </c>
       <c r="E24" t="n">
         <v>0.3711</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0624</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5855</v>
+        <v>-0.6058</v>
       </c>
       <c r="E25" t="n">
         <v>-0.4064</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4717</v>
+        <v>-0.4713</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0723</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6119</v>
+        <v>-0.6317</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4717</v>
+        <v>-0.4713</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1031</v>
+        <v>-0.1027</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3686</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1031</v>
+        <v>-0.1027</v>
       </c>
       <c r="I26" t="n">
         <v>-0.1036</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1955</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9359</v>
+        <v>-0.9514</v>
       </c>
       <c r="E27" t="n">
         <v>-1.2738</v>
@@ -1698,7 +1698,7 @@
         <v>-0.3547</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.3549</v>
+        <v>-1.3646</v>
       </c>
       <c r="E28" t="n">
         <v>-2.3109</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-3.0167</v>
+        <v>-3.007</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.463</v>
+        <v>-0.4615</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.64</v>
+        <v>-1.6419</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.0167</v>
+        <v>-3.007</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.6098</v>
+        <v>-2.6001</v>
       </c>
       <c r="G29" t="n">
         <v>-0.4069</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.6098</v>
+        <v>-2.6001</v>
       </c>
       <c r="I29" t="n">
         <v>-2.6219</v>
@@ -1790,7 +1790,7 @@
         <v>-0.5228</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.7975</v>
+        <v>-1.801</v>
       </c>
       <c r="E30" t="n">
         <v>-3.4064</v>
@@ -1836,7 +1836,7 @@
         <v>-0.5308</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8184</v>
+        <v>-1.8217</v>
       </c>
       <c r="E31" t="n">
         <v>-3.4583</v>

--- a/database/event/5246/event_5246_evp_summary.xlsx
+++ b/database/event/5246/event_5246_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6693</v>
+        <v>7.284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1771</v>
+        <v>1.1179</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6115</v>
+        <v>2.6503</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6693</v>
+        <v>7.284</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3329</v>
+        <v>4.6613</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3364</v>
+        <v>2.6227</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6268</v>
+        <v>6.8754</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6268</v>
+        <v>6.8754</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3364</v>
+        <v>2.6227</v>
       </c>
       <c r="K2" t="n">
         <v>401</v>
@@ -529,7 +529,7 @@
         <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>8.963200000000001</v>
+        <v>9.498100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>429</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6332</v>
+        <v>6.5602</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1715</v>
+        <v>1.0068</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5972</v>
+        <v>2.3236</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6332</v>
+        <v>6.5602</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6735</v>
+        <v>5.2962</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9597</v>
+        <v>1.264</v>
       </c>
       <c r="H3" t="n">
-        <v>5.025</v>
+        <v>8.269600000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.025</v>
+        <v>8.269600000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9597</v>
+        <v>1.264</v>
       </c>
       <c r="K3" t="n">
         <v>401</v>
@@ -575,7 +575,7 @@
         <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>7.9847</v>
+        <v>9.5336</v>
       </c>
       <c r="N3" t="n">
         <v>429</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9371</v>
+        <v>5.4326</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9112</v>
+        <v>0.8338</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9214</v>
+        <v>1.8145</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9371</v>
+        <v>5.4326</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4286</v>
+        <v>5.4326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5085</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.209</v>
+        <v>8.569000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2612</v>
+        <v>8.569000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5085</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>6.769699999999999</v>
+        <v>8.569000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>543</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4846</v>
+        <v>5.1815</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8418</v>
+        <v>0.7952</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7412</v>
+        <v>1.7012</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4846</v>
+        <v>5.1815</v>
       </c>
       <c r="F5" t="n">
-        <v>5.4846</v>
+        <v>4.5652</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.6163</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2968</v>
+        <v>6.6645</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2968</v>
+        <v>6.9386</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.6163</v>
       </c>
       <c r="K5" t="n">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2968</v>
+        <v>7.5549</v>
       </c>
       <c r="N5" t="n">
-        <v>457</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0812</v>
+        <v>4.989</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7798</v>
+        <v>0.7657</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5804</v>
+        <v>1.6143</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0812</v>
+        <v>4.989</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0812</v>
+        <v>4.989</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6642</v>
+        <v>7.5951</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6642</v>
+        <v>7.5951</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.6642</v>
+        <v>7.5951</v>
       </c>
       <c r="N6" t="n">
         <v>457</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0964</v>
+        <v>3.8313</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6287</v>
+        <v>0.588</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1881</v>
+        <v>1.0916</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0964</v>
+        <v>3.8313</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0964</v>
+        <v>3.8313</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1201</v>
+        <v>5.0531</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1201</v>
+        <v>5.0531</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1201</v>
+        <v>5.0531</v>
       </c>
       <c r="N7" t="n">
         <v>457</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0607</v>
+        <v>3.6854</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4697</v>
+        <v>0.5656</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7755</v>
+        <v>1.0258</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0607</v>
+        <v>3.6854</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0607</v>
+        <v>2.9059</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.7795</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0607</v>
+        <v>3.0211</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0607</v>
+        <v>3.0211</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.7795</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0607</v>
+        <v>3.8006</v>
       </c>
       <c r="N8" t="n">
-        <v>356</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9964</v>
+        <v>3.6134</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4599</v>
+        <v>0.5546</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7499</v>
+        <v>0.9933</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9964</v>
+        <v>3.6134</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9964</v>
+        <v>3.6134</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9964</v>
+        <v>4.5746</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9964</v>
+        <v>4.5746</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9964</v>
+        <v>4.5746</v>
       </c>
       <c r="N9" t="n">
-        <v>296</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9564</v>
+        <v>3.3576</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4537</v>
+        <v>0.5153</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7339</v>
+        <v>0.8778</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9564</v>
+        <v>3.3576</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9564</v>
+        <v>3.3576</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9564</v>
+        <v>4.013</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9897</v>
+        <v>4.013</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>515</v>
+        <v>347</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9897</v>
+        <v>4.013</v>
       </c>
       <c r="N10" t="n">
-        <v>543</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9073</v>
+        <v>3.2133</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4462</v>
+        <v>0.4932</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7144</v>
+        <v>0.8126</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9073</v>
+        <v>3.2133</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2268</v>
+        <v>3.2133</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2268</v>
+        <v>3.6961</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2268</v>
+        <v>3.6961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9073</v>
+        <v>3.6961</v>
       </c>
       <c r="N11" t="n">
-        <v>429</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9068</v>
+        <v>3.0391</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4461</v>
+        <v>0.4664</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9068</v>
+        <v>3.0391</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9068</v>
+        <v>3.0391</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9068</v>
+        <v>3.3136</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9068</v>
+        <v>3.3136</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9068</v>
+        <v>3.3136</v>
       </c>
       <c r="N12" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8698</v>
+        <v>2.9382</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4404</v>
+        <v>0.4509</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6994</v>
+        <v>0.6884</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8698</v>
+        <v>2.9382</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8698</v>
+        <v>2.9382</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8698</v>
+        <v>3.0921</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8698</v>
+        <v>3.0921</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8698</v>
+        <v>3.0921</v>
       </c>
       <c r="N13" t="n">
         <v>347</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.343</v>
+        <v>2.8542</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3596</v>
+        <v>0.4381</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4895</v>
+        <v>0.6505</v>
       </c>
       <c r="E14" t="n">
-        <v>2.343</v>
+        <v>2.8542</v>
       </c>
       <c r="F14" t="n">
-        <v>2.343</v>
+        <v>2.8542</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.343</v>
+        <v>2.9076</v>
       </c>
       <c r="I14" t="n">
-        <v>2.343</v>
+        <v>2.9076</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.343</v>
+        <v>2.9076</v>
       </c>
       <c r="N14" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0436</v>
+        <v>2.6729</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3136</v>
+        <v>0.4102</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3703</v>
+        <v>0.5687</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0436</v>
+        <v>2.6729</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0436</v>
+        <v>3.4482</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>-0.7753</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0436</v>
+        <v>4.2119</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0692</v>
+        <v>4.3851</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>-0.7753</v>
       </c>
       <c r="K15" t="n">
         <v>515</v>
@@ -1127,7 +1127,7 @@
         <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0692</v>
+        <v>3.6098</v>
       </c>
       <c r="N15" t="n">
         <v>543</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9125</v>
+        <v>2.5752</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2935</v>
+        <v>0.3952</v>
       </c>
       <c r="D16" t="n">
-        <v>0.318</v>
+        <v>0.5246</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9125</v>
+        <v>2.5752</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9125</v>
+        <v>3.313</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.7378</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9125</v>
+        <v>3.9151</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9125</v>
+        <v>4.0761</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.7378</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>515</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9125</v>
+        <v>3.3383</v>
       </c>
       <c r="N16" t="n">
-        <v>356</v>
+        <v>543</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2278</v>
+        <v>0.3931</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1474</v>
+        <v>0.5182</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4843</v>
+        <v>2.5611</v>
       </c>
       <c r="N17" t="n">
         <v>296</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3904</v>
+        <v>2.3325</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2134</v>
+        <v>0.358</v>
       </c>
       <c r="D18" t="n">
-        <v>0.11</v>
+        <v>0.415</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3904</v>
+        <v>2.3325</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.6709</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5209</v>
+        <v>0.6616</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.6709</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.6709</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5209</v>
+        <v>0.6616</v>
       </c>
       <c r="K18" t="n">
         <v>401</v>
@@ -1265,7 +1265,7 @@
         <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3904</v>
+        <v>2.3325</v>
       </c>
       <c r="N18" t="n">
         <v>429</v>
@@ -1274,231 +1274,231 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1936</v>
+        <v>0.3284</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0586</v>
+        <v>0.328</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2613</v>
+        <v>2.1398</v>
       </c>
       <c r="N19" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1863</v>
+        <v>0.2972</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0396</v>
+        <v>0.2362</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2137</v>
+        <v>1.9365</v>
       </c>
       <c r="N20" t="n">
-        <v>296</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1718</v>
+        <v>0.2894</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002</v>
+        <v>0.2132</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1193</v>
+        <v>1.8856</v>
       </c>
       <c r="N21" t="n">
-        <v>356</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1196</v>
+        <v>0.2817</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1334</v>
+        <v>0.1907</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>356</v>
+        <v>457</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7793</v>
+        <v>1.8356</v>
       </c>
       <c r="N22" t="n">
-        <v>356</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0936</v>
+        <v>0.2731</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.201</v>
+        <v>0.1654</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>457</v>
+        <v>356</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6098</v>
+        <v>1.7796</v>
       </c>
       <c r="N23" t="n">
-        <v>457</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="C24" t="n">
-        <v>0.057</v>
+        <v>0.1986</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2961</v>
+        <v>-0.0539</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3711</v>
+        <v>1.2938</v>
       </c>
       <c r="N24" t="n">
         <v>296</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0624</v>
+        <v>0.1219</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6058</v>
+        <v>-0.2793</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>296</v>
+        <v>457</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4064</v>
+        <v>0.7945</v>
       </c>
       <c r="N25" t="n">
-        <v>296</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4713</v>
+        <v>0.7278</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0723</v>
+        <v>0.1117</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6317</v>
+        <v>-0.3094</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4713</v>
+        <v>0.7278</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1027</v>
+        <v>0.9764</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3686</v>
+        <v>-0.2486</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1027</v>
+        <v>0.9764</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1036</v>
+        <v>1.0166</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3686</v>
+        <v>-0.2486</v>
       </c>
       <c r="K26" t="n">
         <v>515</v>
@@ -1633,7 +1633,7 @@
         <v>28</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4722</v>
+        <v>0.768</v>
       </c>
       <c r="N26" t="n">
         <v>543</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1955</v>
+        <v>0.077</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9514</v>
+        <v>-0.4114</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>457</v>
+        <v>296</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.2738</v>
+        <v>0.502</v>
       </c>
       <c r="N27" t="n">
-        <v>457</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.3109</v>
+        <v>-1.3193</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3547</v>
+        <v>-0.2025</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.3646</v>
+        <v>-1.2336</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.3109</v>
+        <v>-1.3193</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.8751</v>
+        <v>-1.0373</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4358</v>
+        <v>-0.282</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.8751</v>
+        <v>-1.0373</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.8751</v>
+        <v>-1.0373</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4358</v>
+        <v>-0.282</v>
       </c>
       <c r="K28" t="n">
         <v>401</v>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.3109</v>
+        <v>-1.3193</v>
       </c>
       <c r="N28" t="n">
         <v>429</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-3.007</v>
+        <v>-1.495</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4615</v>
+        <v>-0.2294</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.6419</v>
+        <v>-1.3129</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.007</v>
+        <v>-1.495</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.6001</v>
+        <v>-1.1751</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4069</v>
+        <v>-0.3199</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.6001</v>
+        <v>-1.1751</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.6219</v>
+        <v>-1.2234</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4069</v>
+        <v>-0.3199</v>
       </c>
       <c r="K29" t="n">
         <v>515</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>-3.0288</v>
+        <v>-1.5433</v>
       </c>
       <c r="N29" t="n">
         <v>543</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5228</v>
+        <v>-0.355</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.801</v>
+        <v>-1.6821</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.4064</v>
+        <v>-2.3128</v>
       </c>
       <c r="N30" t="n">
         <v>347</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5308</v>
+        <v>-0.3821</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.8217</v>
+        <v>-1.7619</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.4583</v>
+        <v>-2.4894</v>
       </c>
       <c r="N31" t="n">
         <v>347</v>
@@ -1969,10 +1969,10 @@
         <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5559</v>
+        <v>1.3622</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5559</v>
+        <v>1.3622</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.872</v>
+        <v>0.89</v>
       </c>
       <c r="J3" t="n">
-        <v>0.872</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5541</v>
+        <v>0.6212</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5541</v>
+        <v>0.6212</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0077</v>
+        <v>0.0693</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0077</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0864</v>
+        <v>-0.0089</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0864</v>
+        <v>-0.0089</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0767</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0767</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2784</v>
+        <v>-0.2183</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2784</v>
+        <v>-0.2183</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4605</v>
+        <v>-0.3117</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4605</v>
+        <v>-0.3117</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4759</v>
+        <v>-0.321</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4759</v>
+        <v>-0.321</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.535</v>
+        <v>-0.3585</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.535</v>
+        <v>-0.3585</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4228</v>
+        <v>1.2729</v>
       </c>
       <c r="J12" t="n">
-        <v>38.4156</v>
+        <v>34.3683</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4038</v>
+        <v>1.2605</v>
       </c>
       <c r="J13" t="n">
-        <v>37.9026</v>
+        <v>34.0335</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0332</v>
+        <v>0.0404</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8964</v>
+        <v>1.0908</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.99</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1915</v>
+        <v>-0.1105</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.1705</v>
+        <v>-2.9835</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4281</v>
+        <v>-0.3513</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.5587</v>
+        <v>-9.485099999999999</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.7033</v>
       </c>
       <c r="J17" t="n">
-        <v>15.8004</v>
+        <v>18.9891</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0919</v>
+        <v>0.0631</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4813</v>
+        <v>1.7037</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1285</v>
+        <v>-0.1016</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.4695</v>
+        <v>-2.7432</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6276</v>
+        <v>-0.4168</v>
       </c>
       <c r="J20" t="n">
-        <v>-16.9452</v>
+        <v>-11.2536</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6276</v>
+        <v>-0.4168</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.9452</v>
+        <v>-11.2536</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0587</v>
+        <v>0.0149</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5262</v>
+        <v>0.3874</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2458</v>
+        <v>-0.187</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.3908</v>
+        <v>-4.862</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3632</v>
+        <v>-0.2443</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.443199999999999</v>
+        <v>-6.3518</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4266</v>
+        <v>-0.2825</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.0916</v>
+        <v>-7.345</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4711</v>
+        <v>-0.3111</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.2486</v>
+        <v>-8.0886</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9351</v>
+        <v>0.951</v>
       </c>
       <c r="J27" t="n">
-        <v>24.3126</v>
+        <v>24.726</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9351</v>
+        <v>0.951</v>
       </c>
       <c r="J28" t="n">
-        <v>24.3126</v>
+        <v>24.726</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9308</v>
       </c>
       <c r="J29" t="n">
-        <v>23.7328</v>
+        <v>24.2008</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.19</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4455</v>
+        <v>0.5233</v>
       </c>
       <c r="J30" t="n">
-        <v>11.583</v>
+        <v>13.6058</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>1.03</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0104</v>
+        <v>0.0674</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2704</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6357</v>
+        <v>0.7736</v>
       </c>
       <c r="J32" t="n">
-        <v>19.071</v>
+        <v>23.208</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4827</v>
+        <v>0.5668</v>
       </c>
       <c r="J33" t="n">
-        <v>14.481</v>
+        <v>17.004</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1329</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.987</v>
+        <v>-2.259</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.77</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4248</v>
+        <v>-0.2681</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.744</v>
+        <v>-8.042999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6571</v>
+        <v>-0.4377</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.713</v>
+        <v>-13.131</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2693</v>
+        <v>1.1687</v>
       </c>
       <c r="J37" t="n">
-        <v>38.079</v>
+        <v>35.061</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.28</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7759</v>
+        <v>0.7631</v>
       </c>
       <c r="J38" t="n">
-        <v>23.277</v>
+        <v>22.893</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0425</v>
+        <v>0.02</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.275</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1016</v>
+        <v>-0.0348</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.048</v>
+        <v>-1.044</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.372</v>
+        <v>-0.3</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0696</v>
+        <v>1.0326</v>
       </c>
       <c r="J42" t="n">
-        <v>32.088</v>
+        <v>30.978</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5279</v>
+        <v>0.4939</v>
       </c>
       <c r="J43" t="n">
-        <v>15.837</v>
+        <v>14.817</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1601</v>
+        <v>-0.1077</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.803</v>
+        <v>-3.231</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2704</v>
+        <v>-0.2128</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.112</v>
+        <v>-6.384</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6643</v>
+        <v>-0.6121</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.929</v>
+        <v>-18.363</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7529</v>
+        <v>0.9362</v>
       </c>
       <c r="J47" t="n">
-        <v>22.587</v>
+        <v>28.086</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3251</v>
+        <v>0.3646</v>
       </c>
       <c r="J48" t="n">
-        <v>9.753</v>
+        <v>10.938</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.01</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0418</v>
+        <v>0.038</v>
       </c>
       <c r="J49" t="n">
-        <v>1.254</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5199</v>
+        <v>-0.336</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.597</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.63</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6088</v>
+        <v>-0.4015</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.264</v>
+        <v>-12.045</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2294</v>
+        <v>1.148</v>
       </c>
       <c r="J52" t="n">
-        <v>34.4232</v>
+        <v>32.144</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7027</v>
+        <v>0.7181</v>
       </c>
       <c r="J53" t="n">
-        <v>19.6756</v>
+        <v>20.1068</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4441</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>12.4348</v>
+        <v>14.2128</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3356</v>
+        <v>0.4054</v>
       </c>
       <c r="J55" t="n">
-        <v>9.396800000000001</v>
+        <v>11.3512</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.03</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0049</v>
+        <v>0.078</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1372</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2591</v>
+        <v>0.2708</v>
       </c>
       <c r="J57" t="n">
-        <v>7.2548</v>
+        <v>7.5824</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.3128</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.125</v>
+        <v>-0.0929</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.5</v>
+        <v>-2.6012</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2131</v>
+        <v>-0.1364</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.9668</v>
+        <v>-3.8192</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4764</v>
+        <v>-0.3073</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.3392</v>
+        <v>-8.6044</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.7537</v>
+        <v>1.5121</v>
       </c>
       <c r="J62" t="n">
-        <v>35.074</v>
+        <v>30.242</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2667</v>
+        <v>1.2228</v>
       </c>
       <c r="J63" t="n">
-        <v>25.334</v>
+        <v>24.456</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.59</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1908</v>
+        <v>1.1898</v>
       </c>
       <c r="J64" t="n">
-        <v>23.816</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.45</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.0222</v>
       </c>
       <c r="J65" t="n">
-        <v>17.914</v>
+        <v>20.444</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>1.44</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8752</v>
+        <v>1.0072</v>
       </c>
       <c r="J66" t="n">
-        <v>17.504</v>
+        <v>20.144</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4684</v>
+        <v>0.5835</v>
       </c>
       <c r="J67" t="n">
-        <v>9.368</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>0.74</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2654</v>
+        <v>-0.2291</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.308</v>
+        <v>-4.582</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.41</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7941</v>
+        <v>-0.5458</v>
       </c>
       <c r="J69" t="n">
-        <v>-15.882</v>
+        <v>-10.916</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.33</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8984</v>
+        <v>-0.6231</v>
       </c>
       <c r="J70" t="n">
-        <v>-17.968</v>
+        <v>-12.462</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9732</v>
+        <v>-0.6815</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.464</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9714</v>
+        <v>0.9689</v>
       </c>
       <c r="J72" t="n">
-        <v>29.142</v>
+        <v>29.067</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8142</v>
+        <v>0.8159</v>
       </c>
       <c r="J73" t="n">
-        <v>24.426</v>
+        <v>24.477</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.28</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7429</v>
+        <v>0.7468</v>
       </c>
       <c r="J74" t="n">
-        <v>22.287</v>
+        <v>22.404</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2925</v>
+        <v>0.3574</v>
       </c>
       <c r="J75" t="n">
-        <v>8.775</v>
+        <v>10.722</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.92</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4203</v>
+        <v>-0.3449</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.609</v>
+        <v>-10.347</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0716</v>
+        <v>0.0498</v>
       </c>
       <c r="J77" t="n">
-        <v>2.148</v>
+        <v>1.494</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0364</v>
+        <v>0.0109</v>
       </c>
       <c r="J78" t="n">
-        <v>1.092</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1659</v>
+        <v>-0.1054</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.977</v>
+        <v>-3.162</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2401</v>
+        <v>-0.1491</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.203</v>
+        <v>-4.473</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2401</v>
+        <v>-0.1491</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.203</v>
+        <v>-4.473</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.65</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8783</v>
+        <v>0.8534</v>
       </c>
       <c r="J82" t="n">
-        <v>26.349</v>
+        <v>25.602</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.22</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3538</v>
+        <v>0.3319</v>
       </c>
       <c r="J83" t="n">
-        <v>10.614</v>
+        <v>9.957000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2498</v>
+        <v>0.2532</v>
       </c>
       <c r="J84" t="n">
-        <v>7.494</v>
+        <v>7.596</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0168</v>
+        <v>0.0503</v>
       </c>
       <c r="J85" t="n">
-        <v>0.504</v>
+        <v>1.509</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.455</v>
+        <v>-0.2861</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.65</v>
+        <v>-8.583</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5182</v>
+        <v>0.4378</v>
       </c>
       <c r="J87" t="n">
-        <v>15.546</v>
+        <v>13.134</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5051</v>
+        <v>0.4254</v>
       </c>
       <c r="J88" t="n">
-        <v>15.153</v>
+        <v>12.762</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2298</v>
+        <v>-0.1349</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.894</v>
+        <v>-4.047</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2792</v>
+        <v>-0.1675</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.375999999999999</v>
+        <v>-5.025</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5599</v>
+        <v>-0.3652</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.797</v>
+        <v>-10.956</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7117</v>
+        <v>0.6763</v>
       </c>
       <c r="J92" t="n">
-        <v>20.6393</v>
+        <v>19.6127</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4211</v>
+        <v>0.389</v>
       </c>
       <c r="J93" t="n">
-        <v>12.2119</v>
+        <v>11.281</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4211</v>
+        <v>0.389</v>
       </c>
       <c r="J94" t="n">
-        <v>12.2119</v>
+        <v>11.281</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3922</v>
+        <v>-0.334</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.3738</v>
+        <v>-9.686</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5056</v>
+        <v>-0.4482</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.6624</v>
+        <v>-12.9978</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.21</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3979</v>
+        <v>0.457</v>
       </c>
       <c r="J97" t="n">
-        <v>11.5391</v>
+        <v>13.253</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.12</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2613</v>
+        <v>0.2866</v>
       </c>
       <c r="J98" t="n">
-        <v>7.5777</v>
+        <v>8.311400000000001</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1354</v>
+        <v>0.1393</v>
       </c>
       <c r="J99" t="n">
-        <v>3.9266</v>
+        <v>4.0397</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1145</v>
+        <v>0.1161</v>
       </c>
       <c r="J100" t="n">
-        <v>3.3205</v>
+        <v>3.3669</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.67</v>
+        <v>-0.4475</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.43</v>
+        <v>-12.9775</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9516</v>
+        <v>0.9365</v>
       </c>
       <c r="J102" t="n">
-        <v>39.0156</v>
+        <v>38.3965</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9073</v>
+        <v>0.8915</v>
       </c>
       <c r="J103" t="n">
-        <v>37.1993</v>
+        <v>36.5515</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2572</v>
+        <v>0.2929</v>
       </c>
       <c r="J104" t="n">
-        <v>10.5452</v>
+        <v>12.0089</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1252</v>
+        <v>0.1729</v>
       </c>
       <c r="J105" t="n">
-        <v>5.1332</v>
+        <v>7.0889</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.7563</v>
       </c>
       <c r="J106" t="n">
-        <v>-32.8779</v>
+        <v>-31.0083</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3251</v>
+        <v>0.3646</v>
       </c>
       <c r="J107" t="n">
-        <v>13.3291</v>
+        <v>14.9486</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1154</v>
+        <v>0.1164</v>
       </c>
       <c r="J108" t="n">
-        <v>4.7314</v>
+        <v>4.7724</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0669</v>
+        <v>-0.0358</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.7429</v>
+        <v>-1.4678</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1136</v>
+        <v>-0.063</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.6576</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3085</v>
+        <v>-0.1877</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.6485</v>
+        <v>-7.6957</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.98</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0882</v>
+        <v>0.0487</v>
       </c>
       <c r="J112" t="n">
-        <v>1.764</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1175</v>
+        <v>-0.1188</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.35</v>
+        <v>-2.376</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.7</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3948</v>
+        <v>-0.2958</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.896</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.47</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7466</v>
+        <v>-0.5082</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.932</v>
+        <v>-10.164</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8345</v>
+        <v>-0.5738</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.69</v>
+        <v>-11.476</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6932</v>
+        <v>1.4679</v>
       </c>
       <c r="J117" t="n">
-        <v>33.864</v>
+        <v>29.358</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.64</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3436</v>
+        <v>1.2523</v>
       </c>
       <c r="J118" t="n">
-        <v>26.872</v>
+        <v>25.046</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.9666</v>
       </c>
       <c r="J119" t="n">
-        <v>16.764</v>
+        <v>19.332</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.39</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.9281</v>
       </c>
       <c r="J120" t="n">
-        <v>15.918</v>
+        <v>18.562</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7534</v>
+        <v>0.8861</v>
       </c>
       <c r="J121" t="n">
-        <v>15.068</v>
+        <v>17.722</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7764</v>
+        <v>0.7032</v>
       </c>
       <c r="J122" t="n">
-        <v>16.3044</v>
+        <v>14.7672</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.41</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5526</v>
+        <v>0.5037</v>
       </c>
       <c r="J123" t="n">
-        <v>11.6046</v>
+        <v>10.5777</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5396</v>
+        <v>0.4931</v>
       </c>
       <c r="J124" t="n">
-        <v>11.3316</v>
+        <v>10.3551</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.21</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2657</v>
+        <v>0.2801</v>
       </c>
       <c r="J125" t="n">
-        <v>5.5797</v>
+        <v>5.8821</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0878</v>
+        <v>0.1211</v>
       </c>
       <c r="J126" t="n">
-        <v>1.8438</v>
+        <v>2.5431</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>0.88</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1296</v>
+        <v>-0.1227</v>
       </c>
       <c r="J127" t="n">
-        <v>-2.7216</v>
+        <v>-2.5767</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2795</v>
+        <v>-0.2186</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.8695</v>
+        <v>-4.5906</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2964</v>
+        <v>-0.2285</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.2244</v>
+        <v>-4.7985</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3316</v>
+        <v>-0.2477</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.9636</v>
+        <v>-5.2017</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.4803</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.9142</v>
+        <v>-10.0863</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3686</v>
+        <v>0.4149</v>
       </c>
       <c r="J132" t="n">
-        <v>10.3208</v>
+        <v>11.6172</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0261</v>
+        <v>0.0061</v>
       </c>
       <c r="J133" t="n">
-        <v>0.7308</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.736</v>
+        <v>-1.3216</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1576</v>
+        <v>-0.096</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.4128</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4859</v>
+        <v>-0.3125</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.6052</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0447</v>
+        <v>1.0208</v>
       </c>
       <c r="J137" t="n">
-        <v>29.2516</v>
+        <v>28.5824</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6301</v>
+        <v>0.6197</v>
       </c>
       <c r="J138" t="n">
-        <v>17.6428</v>
+        <v>17.3516</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2064</v>
+        <v>0.2581</v>
       </c>
       <c r="J139" t="n">
-        <v>5.7792</v>
+        <v>7.2268</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0394</v>
+        <v>0.0985</v>
       </c>
       <c r="J140" t="n">
-        <v>1.1032</v>
+        <v>2.758</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1598</v>
+        <v>-0.0892</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.4744</v>
+        <v>-2.4976</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3899</v>
+        <v>0.4447</v>
       </c>
       <c r="J142" t="n">
-        <v>10.9172</v>
+        <v>12.4516</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.14</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3</v>
+        <v>0.3309</v>
       </c>
       <c r="J143" t="n">
-        <v>8.4</v>
+        <v>9.2652</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0145</v>
+        <v>0.0022</v>
       </c>
       <c r="J144" t="n">
-        <v>0.406</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.87</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2722</v>
+        <v>-0.1648</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.6216</v>
+        <v>-4.6144</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5169</v>
+        <v>-0.3342</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.4732</v>
+        <v>-9.3576</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.52</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3151</v>
+        <v>1.1971</v>
       </c>
       <c r="J147" t="n">
-        <v>36.8228</v>
+        <v>33.5188</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.17</v>
       </c>
       <c r="I148" t="n">
-        <v>0.53</v>
+        <v>0.5082</v>
       </c>
       <c r="J148" t="n">
-        <v>14.84</v>
+        <v>14.2296</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1024</v>
+        <v>0.1449</v>
       </c>
       <c r="J149" t="n">
-        <v>2.8672</v>
+        <v>4.0572</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0259</v>
+        <v>0.0736</v>
       </c>
       <c r="J150" t="n">
-        <v>0.7252</v>
+        <v>2.0608</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8651</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-24.2228</v>
+        <v>-23.1308</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2615</v>
+        <v>-0.2201</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.4915</v>
+        <v>-4.6221</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2772</v>
+        <v>-0.2306</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.8212</v>
+        <v>-4.8426</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.3721</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.3148</v>
+        <v>-7.8141</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5545</v>
+        <v>-0.3813</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.6445</v>
+        <v>-8.007300000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6705</v>
+        <v>-0.4558</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.0805</v>
+        <v>-9.5718</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.87</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7621</v>
+        <v>1.5123</v>
       </c>
       <c r="J157" t="n">
-        <v>37.0041</v>
+        <v>31.7583</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.85</v>
       </c>
       <c r="I158" t="n">
-        <v>1.7274</v>
+        <v>1.49</v>
       </c>
       <c r="J158" t="n">
-        <v>36.2754</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.79</v>
       </c>
       <c r="I159" t="n">
-        <v>1.6216</v>
+        <v>1.4226</v>
       </c>
       <c r="J159" t="n">
-        <v>34.0536</v>
+        <v>29.8746</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3076</v>
+        <v>0.4178</v>
       </c>
       <c r="J160" t="n">
-        <v>6.4596</v>
+        <v>8.7738</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3418</v>
+        <v>-0.2533</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.1778</v>
+        <v>-5.3193</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.21</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3896</v>
+        <v>0.3439</v>
       </c>
       <c r="J162" t="n">
-        <v>11.688</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2522</v>
+        <v>0.2147</v>
       </c>
       <c r="J163" t="n">
-        <v>7.566</v>
+        <v>6.441</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2184</v>
+        <v>0.1842</v>
       </c>
       <c r="J164" t="n">
-        <v>6.552</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.914</v>
+        <v>-2.718</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4584</v>
+        <v>-0.291</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.752</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4649</v>
+        <v>0.3942</v>
       </c>
       <c r="J167" t="n">
-        <v>13.947</v>
+        <v>11.826</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2598</v>
+        <v>0.2174</v>
       </c>
       <c r="J168" t="n">
-        <v>7.794</v>
+        <v>6.522</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2598</v>
+        <v>0.2174</v>
       </c>
       <c r="J169" t="n">
-        <v>7.794</v>
+        <v>6.522</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1236</v>
+        <v>-0.0588</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.708</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.91</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.235</v>
+        <v>-0.1326</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.05</v>
+        <v>-3.978</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.67</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5427</v>
+        <v>1.3519</v>
       </c>
       <c r="J172" t="n">
-        <v>44.7383</v>
+        <v>39.2051</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.761</v>
+        <v>0.7673</v>
       </c>
       <c r="J173" t="n">
-        <v>22.069</v>
+        <v>22.2517</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5785</v>
+        <v>0.6051</v>
       </c>
       <c r="J174" t="n">
-        <v>16.7765</v>
+        <v>17.5479</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0102</v>
+        <v>0.0815</v>
       </c>
       <c r="J175" t="n">
-        <v>0.2958</v>
+        <v>2.3635</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.611</v>
+        <v>-0.5461</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.719</v>
+        <v>-15.8369</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.334</v>
+        <v>0.361</v>
       </c>
       <c r="J177" t="n">
-        <v>9.686</v>
+        <v>10.469</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0392</v>
+        <v>-0.0015</v>
       </c>
       <c r="J178" t="n">
-        <v>1.1368</v>
+        <v>-0.0435</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4433</v>
+        <v>-0.2888</v>
       </c>
       <c r="J179" t="n">
-        <v>-12.8557</v>
+        <v>-8.3752</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4433</v>
+        <v>-0.2888</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.8557</v>
+        <v>-8.3752</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5272</v>
+        <v>-0.346</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.2888</v>
+        <v>-10.034</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1991</v>
+        <v>1.1272</v>
       </c>
       <c r="J182" t="n">
-        <v>28.7784</v>
+        <v>27.0528</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.402</v>
+        <v>0.4614</v>
       </c>
       <c r="J183" t="n">
-        <v>9.648</v>
+        <v>11.0736</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.15</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3742</v>
+        <v>0.4358</v>
       </c>
       <c r="J184" t="n">
-        <v>8.9808</v>
+        <v>10.4592</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2904</v>
+        <v>0.3565</v>
       </c>
       <c r="J185" t="n">
-        <v>6.9696</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.11</v>
       </c>
       <c r="I186" t="n">
-        <v>0.262</v>
+        <v>0.329</v>
       </c>
       <c r="J186" t="n">
-        <v>6.288</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2996</v>
+        <v>0.3164</v>
       </c>
       <c r="J187" t="n">
-        <v>7.1904</v>
+        <v>7.5936</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.106</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>2.544</v>
+        <v>1.7856</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.74</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4307</v>
+        <v>-0.28</v>
       </c>
       <c r="J189" t="n">
-        <v>-10.3368</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4595</v>
+        <v>-0.2992</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.028</v>
+        <v>-7.1808</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4877</v>
+        <v>-0.3183</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.7048</v>
+        <v>-7.6392</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6501</v>
+        <v>0.794</v>
       </c>
       <c r="J192" t="n">
-        <v>18.2028</v>
+        <v>22.232</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.02</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1056</v>
+        <v>0.0843</v>
       </c>
       <c r="J193" t="n">
-        <v>2.9568</v>
+        <v>2.3604</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.76</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4203</v>
+        <v>-0.2686</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.7684</v>
+        <v>-7.5208</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4486</v>
+        <v>-0.2881</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.5608</v>
+        <v>-8.066800000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5169</v>
+        <v>-0.336</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.4732</v>
+        <v>-9.407999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8567</v>
+        <v>0.8408</v>
       </c>
       <c r="J197" t="n">
-        <v>23.9876</v>
+        <v>23.5424</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6414</v>
+        <v>0.6248</v>
       </c>
       <c r="J198" t="n">
-        <v>17.9592</v>
+        <v>17.4944</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.59</v>
+        <v>0.5755</v>
       </c>
       <c r="J199" t="n">
-        <v>16.52</v>
+        <v>16.114</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.99</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1519</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.2532</v>
+        <v>-2.366</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4236</v>
+        <v>-0.355</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.8608</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0707</v>
+        <v>-0.081</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.6261</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2767</v>
+        <v>-0.2122</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.3641</v>
+        <v>-4.8806</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>0.79</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2943</v>
+        <v>-0.222</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.7689</v>
+        <v>-5.106</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3332</v>
+        <v>-0.2408</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.6636</v>
+        <v>-5.5384</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6518</v>
+        <v>-0.4373</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.9914</v>
+        <v>-10.0579</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2233</v>
+        <v>1.1531</v>
       </c>
       <c r="J207" t="n">
-        <v>28.1359</v>
+        <v>26.5213</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.43</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0165</v>
+        <v>1.0259</v>
       </c>
       <c r="J208" t="n">
-        <v>23.3795</v>
+        <v>23.5957</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>1.34</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8089</v>
+        <v>0.8559</v>
       </c>
       <c r="J209" t="n">
-        <v>18.6047</v>
+        <v>19.6857</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5201</v>
+        <v>0.6095</v>
       </c>
       <c r="J210" t="n">
-        <v>11.9623</v>
+        <v>14.0185</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>1.08</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1307</v>
+        <v>0.216</v>
       </c>
       <c r="J211" t="n">
-        <v>3.0061</v>
+        <v>4.968</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>1.06</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2712</v>
+        <v>0.2121</v>
       </c>
       <c r="J212" t="n">
-        <v>6.5088</v>
+        <v>5.0904</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.78</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2825</v>
+        <v>-0.2246</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.78</v>
+        <v>-5.3904</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.77</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.299</v>
+        <v>-0.2346</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.176</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.625</v>
+        <v>-0.4205</v>
       </c>
       <c r="J215" t="n">
-        <v>-15</v>
+        <v>-10.092</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.42</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8171</v>
+        <v>-0.5604</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.6104</v>
+        <v>-13.4496</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0368</v>
+        <v>0.9537</v>
       </c>
       <c r="J217" t="n">
-        <v>24.8832</v>
+        <v>22.8888</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.43</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>13.536</v>
+        <v>12.4968</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.38</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4893</v>
+        <v>0.4688</v>
       </c>
       <c r="J219" t="n">
-        <v>11.7432</v>
+        <v>11.2512</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.3</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3778</v>
+        <v>0.3817</v>
       </c>
       <c r="J220" t="n">
-        <v>9.0672</v>
+        <v>9.1608</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2173</v>
+        <v>-0.1127</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.2152</v>
+        <v>-2.7048</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.5</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2872</v>
+        <v>1.1781</v>
       </c>
       <c r="J222" t="n">
-        <v>38.616</v>
+        <v>35.343</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.722</v>
+        <v>0.6917</v>
       </c>
       <c r="J223" t="n">
-        <v>21.66</v>
+        <v>20.751</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>1</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0653</v>
+        <v>-0.0162</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.959</v>
+        <v>-0.486</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6449</v>
+        <v>-0.5903</v>
       </c>
       <c r="J225" t="n">
-        <v>-19.347</v>
+        <v>-17.709</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6698</v>
+        <v>-0.6166</v>
       </c>
       <c r="J226" t="n">
-        <v>-20.094</v>
+        <v>-18.498</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2678</v>
+        <v>0.2996</v>
       </c>
       <c r="J227" t="n">
-        <v>8.034000000000001</v>
+        <v>8.988</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.11</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2347</v>
+        <v>0.2603</v>
       </c>
       <c r="J228" t="n">
-        <v>7.041</v>
+        <v>7.809</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2176</v>
+        <v>0.2403</v>
       </c>
       <c r="J229" t="n">
-        <v>6.528</v>
+        <v>7.209</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>1.09</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J230" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5248</v>
+        <v>-0.3391</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.744</v>
+        <v>-10.173</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.54</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3153</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
-        <v>38.1437</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>1.18</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4987</v>
+        <v>0.5161</v>
       </c>
       <c r="J233" t="n">
-        <v>14.4623</v>
+        <v>14.9669</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3098</v>
+        <v>0.364</v>
       </c>
       <c r="J234" t="n">
-        <v>8.9842</v>
+        <v>10.556</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>1.02</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0114</v>
+        <v>0.0544</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.3306</v>
+        <v>1.5776</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1125</v>
+        <v>-0.0415</v>
       </c>
       <c r="J236" t="n">
-        <v>-3.2625</v>
+        <v>-1.2035</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>1.08</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2286</v>
+        <v>0.2314</v>
       </c>
       <c r="J237" t="n">
-        <v>6.6294</v>
+        <v>6.7106</v>
       </c>
     </row>
     <row r="238">
@@ -11409,10 +11409,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0844</v>
+        <v>0.0577</v>
       </c>
       <c r="J238" t="n">
-        <v>2.4476</v>
+        <v>1.6733</v>
       </c>
     </row>
     <row r="239">
@@ -11449,10 +11449,10 @@
         <v>0.88</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2264</v>
+        <v>-0.146</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.5656</v>
+        <v>-4.234</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3735</v>
+        <v>-0.2378</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.8315</v>
+        <v>-6.8962</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3884</v>
+        <v>-0.2477</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.2636</v>
+        <v>-7.1833</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3825</v>
+        <v>0.433</v>
       </c>
       <c r="J242" t="n">
-        <v>10.71</v>
+        <v>12.124</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.171</v>
+        <v>0.1707</v>
       </c>
       <c r="J243" t="n">
-        <v>4.788</v>
+        <v>4.7796</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.05</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1516</v>
+        <v>0.1479</v>
       </c>
       <c r="J244" t="n">
-        <v>4.2448</v>
+        <v>4.1412</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4032</v>
+        <v>-0.2544</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.2896</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4728</v>
+        <v>-0.3032</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.2384</v>
+        <v>-8.489599999999999</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.44</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1141</v>
+        <v>1.0706</v>
       </c>
       <c r="J247" t="n">
-        <v>31.1948</v>
+        <v>29.9768</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5574</v>
+        <v>0.5645</v>
       </c>
       <c r="J248" t="n">
-        <v>15.6072</v>
+        <v>15.806</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4281</v>
+        <v>0.4677</v>
       </c>
       <c r="J249" t="n">
-        <v>11.9868</v>
+        <v>13.0956</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.14</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3682</v>
+        <v>0.4169</v>
       </c>
       <c r="J250" t="n">
-        <v>10.3096</v>
+        <v>11.6732</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4107</v>
+        <v>-0.3373</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.4996</v>
+        <v>-9.4444</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.09</v>
       </c>
       <c r="I252" t="n">
-        <v>0.223</v>
+        <v>0.2341</v>
       </c>
       <c r="J252" t="n">
-        <v>6.69</v>
+        <v>7.023</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1491</v>
+        <v>0.1464</v>
       </c>
       <c r="J253" t="n">
-        <v>4.473</v>
+        <v>4.392</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0477</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.058</v>
+        <v>-1.431</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.501</v>
+        <v>-0.323</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.03</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2533</v>
+        <v>1.1563</v>
       </c>
       <c r="J257" t="n">
-        <v>37.599</v>
+        <v>34.689</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.21</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6322</v>
+        <v>0.6081</v>
       </c>
       <c r="J258" t="n">
-        <v>18.966</v>
+        <v>18.243</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5806</v>
+        <v>0.5579</v>
       </c>
       <c r="J259" t="n">
-        <v>17.418</v>
+        <v>16.737</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.87</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5249</v>
+        <v>-0.4623</v>
       </c>
       <c r="J260" t="n">
-        <v>-15.747</v>
+        <v>-13.869</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8435</v>
+        <v>-0.8023</v>
       </c>
       <c r="J261" t="n">
-        <v>-25.305</v>
+        <v>-24.069</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>1.86</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7956</v>
+        <v>1.5273</v>
       </c>
       <c r="J262" t="n">
-        <v>35.912</v>
+        <v>30.546</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>1.75</v>
       </c>
       <c r="I263" t="n">
-        <v>1.602</v>
+        <v>1.4001</v>
       </c>
       <c r="J263" t="n">
-        <v>32.04</v>
+        <v>28.002</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>1.39</v>
       </c>
       <c r="I264" t="n">
-        <v>0.859</v>
+        <v>0.9477</v>
       </c>
       <c r="J264" t="n">
-        <v>17.18</v>
+        <v>18.954</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>1.07</v>
       </c>
       <c r="I265" t="n">
-        <v>0.078</v>
+        <v>0.1678</v>
       </c>
       <c r="J265" t="n">
-        <v>1.56</v>
+        <v>3.356</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3824</v>
+        <v>-0.297</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.648</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>0.89</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1002</v>
+        <v>-0.1047</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.004</v>
+        <v>-2.094</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2</v>
+        <v>-0.1722</v>
       </c>
       <c r="J268" t="n">
-        <v>-4</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2488</v>
+        <v>-0.2039</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.976</v>
+        <v>-4.078</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>0.64</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5254</v>
+        <v>-0.3548</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.508</v>
+        <v>-7.096</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.43</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8045</v>
+        <v>-0.5508</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.09</v>
+        <v>-11.016</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5542</v>
+        <v>0.5161</v>
       </c>
       <c r="J272" t="n">
-        <v>12.1924</v>
+        <v>11.3542</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.87</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1322</v>
+        <v>-0.1269</v>
       </c>
       <c r="J273" t="n">
-        <v>-2.9084</v>
+        <v>-2.7918</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.73</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3636</v>
+        <v>-0.272</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.9992</v>
+        <v>-5.984</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.47</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.7539</v>
+        <v>-0.513</v>
       </c>
       <c r="J275" t="n">
-        <v>-16.5858</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.26</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.0041</v>
+        <v>-0.7078</v>
       </c>
       <c r="J276" t="n">
-        <v>-22.0902</v>
+        <v>-15.5716</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.69</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8569</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>18.8518</v>
+        <v>17.2436</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.64</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8032</v>
+        <v>0.7336</v>
       </c>
       <c r="J278" t="n">
-        <v>17.6704</v>
+        <v>16.1392</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.46</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5942</v>
+        <v>0.5496</v>
       </c>
       <c r="J279" t="n">
-        <v>13.0724</v>
+        <v>12.0912</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.196</v>
+        <v>0.2227</v>
       </c>
       <c r="J280" t="n">
-        <v>4.312</v>
+        <v>4.8994</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.0607</v>
+        <v>0.099</v>
       </c>
       <c r="J281" t="n">
-        <v>1.3354</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3169</v>
+        <v>1.2087</v>
       </c>
       <c r="J282" t="n">
-        <v>31.6056</v>
+        <v>29.0088</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0544</v>
+        <v>1.0457</v>
       </c>
       <c r="J283" t="n">
-        <v>25.3056</v>
+        <v>25.0968</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5367</v>
+        <v>0.616</v>
       </c>
       <c r="J284" t="n">
-        <v>12.8808</v>
+        <v>14.784</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>1.12</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2532</v>
+        <v>0.3371</v>
       </c>
       <c r="J285" t="n">
-        <v>6.0768</v>
+        <v>8.090400000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1701</v>
+        <v>0.2527</v>
       </c>
       <c r="J286" t="n">
-        <v>4.0824</v>
+        <v>6.0648</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6437</v>
+        <v>0.7892</v>
       </c>
       <c r="J287" t="n">
-        <v>15.4488</v>
+        <v>18.9408</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4393</v>
+        <v>-0.2872</v>
       </c>
       <c r="J288" t="n">
-        <v>-10.5432</v>
+        <v>-6.8928</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.72</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4538</v>
+        <v>-0.2968</v>
       </c>
       <c r="J289" t="n">
-        <v>-10.8912</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4538</v>
+        <v>-0.2968</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.8912</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.524</v>
+        <v>-0.3444</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.576</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.38</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0674</v>
+        <v>1.0292</v>
       </c>
       <c r="J292" t="n">
-        <v>32.022</v>
+        <v>30.876</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2853</v>
+        <v>0.2529</v>
       </c>
       <c r="J293" t="n">
-        <v>8.558999999999999</v>
+        <v>7.587</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1785</v>
+        <v>-0.1358</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.355</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1785</v>
+        <v>-0.1358</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.355</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.8442</v>
+        <v>-0.8064</v>
       </c>
       <c r="J296" t="n">
-        <v>-25.326</v>
+        <v>-24.192</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4694</v>
+        <v>0.5577</v>
       </c>
       <c r="J297" t="n">
-        <v>14.082</v>
+        <v>16.731</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3579</v>
+        <v>0.4179</v>
       </c>
       <c r="J298" t="n">
-        <v>10.737</v>
+        <v>12.537</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0458</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>1.374</v>
+        <v>2.451</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0027</v>
+        <v>0.0271</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.081</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3266</v>
+        <v>-0.1963</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.798</v>
+        <v>-5.889</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.8</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7779</v>
+        <v>1.5116</v>
       </c>
       <c r="J302" t="n">
-        <v>46.2254</v>
+        <v>39.3016</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.3</v>
       </c>
       <c r="I303" t="n">
-        <v>0.786</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J303" t="n">
-        <v>20.436</v>
+        <v>20.5608</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3164</v>
+        <v>0.3825</v>
       </c>
       <c r="J304" t="n">
-        <v>8.2264</v>
+        <v>9.945</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.0793</v>
+        <v>0.1498</v>
       </c>
       <c r="J305" t="n">
-        <v>2.0618</v>
+        <v>3.8948</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.77</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.8021</v>
+        <v>-0.754</v>
       </c>
       <c r="J306" t="n">
-        <v>-20.8546</v>
+        <v>-19.604</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3765</v>
+        <v>0.4198</v>
       </c>
       <c r="J307" t="n">
-        <v>9.789</v>
+        <v>10.9148</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.113</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.938</v>
+        <v>-2.3634</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>0.91</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1535</v>
+        <v>-0.1135</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.991</v>
+        <v>-2.951</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2395</v>
+        <v>-0.1555</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.227</v>
+        <v>-4.043</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>0.61</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6165</v>
+        <v>-0.4085</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.029</v>
+        <v>-10.621</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.52</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7225</v>
+        <v>0.6433</v>
       </c>
       <c r="J312" t="n">
-        <v>18.785</v>
+        <v>16.7258</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6172</v>
+        <v>0.5446</v>
       </c>
       <c r="J313" t="n">
-        <v>16.0472</v>
+        <v>14.1596</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.36</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5306</v>
+        <v>0.4662</v>
       </c>
       <c r="J314" t="n">
-        <v>13.7956</v>
+        <v>12.1212</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.24</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3658</v>
+        <v>0.3279</v>
       </c>
       <c r="J315" t="n">
-        <v>9.5108</v>
+        <v>8.525399999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.5355</v>
       </c>
       <c r="J316" t="n">
-        <v>-20.3528</v>
+        <v>-13.923</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.03</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1469</v>
+        <v>0.0963</v>
       </c>
       <c r="J317" t="n">
-        <v>3.8194</v>
+        <v>2.5038</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0994</v>
+        <v>0.0527</v>
       </c>
       <c r="J318" t="n">
-        <v>2.5844</v>
+        <v>1.3702</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2794</v>
+        <v>-0.1834</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.2644</v>
+        <v>-4.7684</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.76</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4066</v>
+        <v>-0.2627</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.5716</v>
+        <v>-6.8302</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4642</v>
+        <v>-0.3014</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.0692</v>
+        <v>-7.8364</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3206</v>
+        <v>0.3418</v>
       </c>
       <c r="J322" t="n">
-        <v>8.6562</v>
+        <v>9.2286</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>0.86</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1931</v>
+        <v>-0.1561</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.2137</v>
+        <v>-4.2147</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>0.76</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3796</v>
+        <v>-0.2538</v>
       </c>
       <c r="J324" t="n">
-        <v>-10.2492</v>
+        <v>-6.8526</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4266</v>
+        <v>-0.2825</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.5182</v>
+        <v>-7.6275</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6604</v>
+        <v>-0.4425</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.8308</v>
+        <v>-11.9475</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>2.06</v>
       </c>
       <c r="I327" t="n">
-        <v>2.0593</v>
+        <v>1.791</v>
       </c>
       <c r="J327" t="n">
-        <v>55.6011</v>
+        <v>48.357</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.19</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4356</v>
+        <v>0.519</v>
       </c>
       <c r="J328" t="n">
-        <v>11.7612</v>
+        <v>14.013</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3328</v>
+        <v>0.4172</v>
       </c>
       <c r="J329" t="n">
-        <v>8.9856</v>
+        <v>11.2644</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.06</v>
       </c>
       <c r="I330" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="J330" t="n">
-        <v>2.2032</v>
+        <v>4.3875</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.99</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2108</v>
+        <v>-0.1254</v>
       </c>
       <c r="J331" t="n">
-        <v>-5.6916</v>
+        <v>-3.3858</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.24</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4223</v>
+        <v>0.4947</v>
       </c>
       <c r="J332" t="n">
-        <v>12.2467</v>
+        <v>14.3463</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2412</v>
+        <v>0.2743</v>
       </c>
       <c r="J333" t="n">
-        <v>6.9948</v>
+        <v>7.9547</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.08</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1699</v>
+        <v>0.1947</v>
       </c>
       <c r="J334" t="n">
-        <v>4.9271</v>
+        <v>5.6463</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>0.98</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.09</v>
+        <v>-0.0408</v>
       </c>
       <c r="J335" t="n">
-        <v>-2.61</v>
+        <v>-1.1832</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>0.84</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3368</v>
+        <v>-0.2042</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.767200000000001</v>
+        <v>-5.9218</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.36</v>
       </c>
       <c r="I337" t="n">
-        <v>1.0312</v>
+        <v>0.9999</v>
       </c>
       <c r="J337" t="n">
-        <v>29.9048</v>
+        <v>28.9971</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.17</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5833</v>
+        <v>0.5372</v>
       </c>
       <c r="J338" t="n">
-        <v>16.9157</v>
+        <v>15.5788</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.96</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.208</v>
+        <v>-0.1674</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.032</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.92</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3423</v>
+        <v>-0.2935</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.9267</v>
+        <v>-8.5115</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-1.0197</v>
+        <v>-0.999</v>
       </c>
       <c r="J341" t="n">
-        <v>-29.5713</v>
+        <v>-28.971</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.5495</v>
+        <v>1.3554</v>
       </c>
       <c r="J342" t="n">
-        <v>54.2325</v>
+        <v>47.439</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.37</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9909</v>
+        <v>0.9745</v>
       </c>
       <c r="J343" t="n">
-        <v>34.6815</v>
+        <v>34.1075</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.3328</v>
+        <v>-0.2629</v>
       </c>
       <c r="J344" t="n">
-        <v>-11.648</v>
+        <v>-9.201499999999999</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.5596</v>
+        <v>-0.4964</v>
       </c>
       <c r="J345" t="n">
-        <v>-19.586</v>
+        <v>-17.374</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.8</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.7097</v>
+        <v>-0.6561</v>
       </c>
       <c r="J346" t="n">
-        <v>-24.8395</v>
+        <v>-22.9635</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4496</v>
+        <v>0.5214</v>
       </c>
       <c r="J347" t="n">
-        <v>15.736</v>
+        <v>18.249</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>0.93</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1632</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J348" t="n">
-        <v>-5.712</v>
+        <v>-3.402</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1822</v>
+        <v>-0.1087</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.377</v>
+        <v>-3.8045</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.92</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1822</v>
+        <v>-0.1087</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.377</v>
+        <v>-3.8045</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3011</v>
+        <v>-0.1847</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.5385</v>
+        <v>-6.4645</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.32</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8992</v>
+        <v>0.8787</v>
       </c>
       <c r="J352" t="n">
-        <v>26.976</v>
+        <v>26.361</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2473</v>
+        <v>0.2693</v>
       </c>
       <c r="J353" t="n">
-        <v>7.419</v>
+        <v>8.079000000000001</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.05</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1422</v>
+        <v>0.1789</v>
       </c>
       <c r="J354" t="n">
-        <v>4.266</v>
+        <v>5.367</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>1.01</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.0143</v>
+        <v>0.0343</v>
       </c>
       <c r="J355" t="n">
-        <v>-0.429</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.99</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1343</v>
+        <v>-0.0751</v>
       </c>
       <c r="J356" t="n">
-        <v>-4.029</v>
+        <v>-2.253</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.49</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7469</v>
+        <v>0.928</v>
       </c>
       <c r="J357" t="n">
-        <v>22.407</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>1.35</v>
       </c>
       <c r="I358" t="n">
-        <v>0.5788</v>
+        <v>0.6968</v>
       </c>
       <c r="J358" t="n">
-        <v>17.364</v>
+        <v>20.904</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.92</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.198</v>
+        <v>-0.1134</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.94</v>
+        <v>-3.402</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.7</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.5231</v>
+        <v>-0.338</v>
       </c>
       <c r="J360" t="n">
-        <v>-15.693</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.62</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6238</v>
+        <v>-0.4126</v>
       </c>
       <c r="J361" t="n">
-        <v>-18.714</v>
+        <v>-12.378</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.354</v>
+        <v>0.3019</v>
       </c>
       <c r="J362" t="n">
-        <v>9.912000000000001</v>
+        <v>8.453200000000001</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>1.19</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3239</v>
+        <v>0.2769</v>
       </c>
       <c r="J363" t="n">
-        <v>9.0692</v>
+        <v>7.7532</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2227</v>
+        <v>0.2003</v>
       </c>
       <c r="J364" t="n">
-        <v>6.2356</v>
+        <v>5.6084</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>1.11</v>
       </c>
       <c r="I365" t="n">
-        <v>0.1802</v>
+        <v>0.1741</v>
       </c>
       <c r="J365" t="n">
-        <v>5.0456</v>
+        <v>4.8748</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.0873</v>
+        <v>-0.0325</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.4444</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.2</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3662</v>
+        <v>0.3244</v>
       </c>
       <c r="J367" t="n">
-        <v>10.2536</v>
+        <v>9.0832</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1896</v>
+        <v>0.1648</v>
       </c>
       <c r="J368" t="n">
-        <v>5.3088</v>
+        <v>4.6144</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0066</v>
+        <v>0.0238</v>
       </c>
       <c r="J369" t="n">
-        <v>0.1848</v>
+        <v>0.6664</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>0.98</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.0893</v>
+        <v>-0.0406</v>
       </c>
       <c r="J370" t="n">
-        <v>-2.5004</v>
+        <v>-1.1368</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.97</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.112</v>
+        <v>-0.0549</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.136</v>
+        <v>-1.5372</v>
       </c>
     </row>
     <row r="372">
@@ -16769,10 +16769,10 @@
         <v>1.2</v>
       </c>
       <c r="I372" t="n">
-        <v>0.3739</v>
+        <v>0.4301</v>
       </c>
       <c r="J372" t="n">
-        <v>10.8431</v>
+        <v>12.4729</v>
       </c>
     </row>
     <row r="373">
@@ -16809,10 +16809,10 @@
         <v>1.08</v>
       </c>
       <c r="I373" t="n">
-        <v>0.181</v>
+        <v>0.1989</v>
       </c>
       <c r="J373" t="n">
-        <v>5.249</v>
+        <v>5.7681</v>
       </c>
     </row>
     <row r="374">
@@ -16849,10 +16849,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0551</v>
+        <v>-0.0229</v>
       </c>
       <c r="J374" t="n">
-        <v>-1.5979</v>
+        <v>-0.6641</v>
       </c>
     </row>
     <row r="375">
@@ -16889,10 +16889,10 @@
         <v>0.95</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1458</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J375" t="n">
-        <v>-4.2282</v>
+        <v>-2.2823</v>
       </c>
     </row>
     <row r="376">
@@ -16929,10 +16929,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.2018</v>
+        <v>-0.1147</v>
       </c>
       <c r="J376" t="n">
-        <v>-5.8522</v>
+        <v>-3.3263</v>
       </c>
     </row>
     <row r="377">
@@ -16969,10 +16969,10 @@
         <v>1.18</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="J377" t="n">
-        <v>16.0341</v>
+        <v>15.428</v>
       </c>
     </row>
     <row r="378">
@@ -17009,10 +17009,10 @@
         <v>1.16</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4985</v>
+        <v>0.4808</v>
       </c>
       <c r="J378" t="n">
-        <v>14.4565</v>
+        <v>13.9432</v>
       </c>
     </row>
     <row r="379">
@@ -17049,10 +17049,10 @@
         <v>1.14</v>
       </c>
       <c r="I379" t="n">
-        <v>0.4415</v>
+        <v>0.4289</v>
       </c>
       <c r="J379" t="n">
-        <v>12.8035</v>
+        <v>12.4381</v>
       </c>
     </row>
     <row r="380">
@@ -17089,10 +17089,10 @@
         <v>1.09</v>
       </c>
       <c r="I380" t="n">
-        <v>0.2699</v>
+        <v>0.2955</v>
       </c>
       <c r="J380" t="n">
-        <v>7.8271</v>
+        <v>8.5695</v>
       </c>
     </row>
     <row r="381">
@@ -17129,10 +17129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3237</v>
+        <v>-0.2569</v>
       </c>
       <c r="J381" t="n">
-        <v>-9.3873</v>
+        <v>-7.4501</v>
       </c>
     </row>
     <row r="382">
@@ -17169,10 +17169,10 @@
         <v>0.96</v>
       </c>
       <c r="I382" t="n">
-        <v>0.0537</v>
+        <v>0.0048</v>
       </c>
       <c r="J382" t="n">
-        <v>1.1814</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="383">
@@ -17209,10 +17209,10 @@
         <v>0.89</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.6456</v>
+        <v>-1.9668</v>
       </c>
     </row>
     <row r="384">
@@ -17249,10 +17249,10 @@
         <v>0.88</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.0917</v>
+        <v>-0.1014</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.0174</v>
+        <v>-2.2308</v>
       </c>
     </row>
     <row r="385">
@@ -17289,10 +17289,10 @@
         <v>0.34</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.9041</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J385" t="n">
-        <v>-19.8902</v>
+        <v>-13.805</v>
       </c>
     </row>
     <row r="386">
@@ -17329,10 +17329,10 @@
         <v>0.26</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.9986</v>
+        <v>-0.7028</v>
       </c>
       <c r="J386" t="n">
-        <v>-21.9692</v>
+        <v>-15.4616</v>
       </c>
     </row>
     <row r="387">
@@ -17369,10 +17369,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>1.5452</v>
+        <v>1.3638</v>
       </c>
       <c r="J387" t="n">
-        <v>33.9944</v>
+        <v>30.0036</v>
       </c>
     </row>
     <row r="388">
@@ -17409,10 +17409,10 @@
         <v>1.51</v>
       </c>
       <c r="I388" t="n">
-        <v>1.1398</v>
+        <v>1.1148</v>
       </c>
       <c r="J388" t="n">
-        <v>25.0756</v>
+        <v>24.5256</v>
       </c>
     </row>
     <row r="389">
@@ -17449,10 +17449,10 @@
         <v>1.35</v>
       </c>
       <c r="I389" t="n">
-        <v>0.7599</v>
+        <v>0.8647</v>
       </c>
       <c r="J389" t="n">
-        <v>16.7178</v>
+        <v>19.0234</v>
       </c>
     </row>
     <row r="390">
@@ -17489,10 +17489,10 @@
         <v>1.29</v>
       </c>
       <c r="I390" t="n">
-        <v>0.6227</v>
+        <v>0.7313</v>
       </c>
       <c r="J390" t="n">
-        <v>13.6994</v>
+        <v>16.0886</v>
       </c>
     </row>
     <row r="391">
@@ -17529,10 +17529,10 @@
         <v>1.18</v>
       </c>
       <c r="I391" t="n">
-        <v>0.3649</v>
+        <v>0.4679</v>
       </c>
       <c r="J391" t="n">
-        <v>8.027799999999999</v>
+        <v>10.2938</v>
       </c>
     </row>
     <row r="392">
@@ -17569,10 +17569,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7251</v>
       </c>
       <c r="J392" t="n">
-        <v>19.5021</v>
+        <v>19.5777</v>
       </c>
     </row>
     <row r="393">
@@ -17609,10 +17609,10 @@
         <v>1.27</v>
       </c>
       <c r="I393" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7251</v>
       </c>
       <c r="J393" t="n">
-        <v>19.5021</v>
+        <v>19.5777</v>
       </c>
     </row>
     <row r="394">
@@ -17649,10 +17649,10 @@
         <v>1.19</v>
       </c>
       <c r="I394" t="n">
-        <v>0.4968</v>
+        <v>0.5372</v>
       </c>
       <c r="J394" t="n">
-        <v>13.4136</v>
+        <v>14.5044</v>
       </c>
     </row>
     <row r="395">
@@ -17689,10 +17689,10 @@
         <v>1.18</v>
       </c>
       <c r="I395" t="n">
-        <v>0.4662</v>
+        <v>0.5131</v>
       </c>
       <c r="J395" t="n">
-        <v>12.5874</v>
+        <v>13.8537</v>
       </c>
     </row>
     <row r="396">
@@ -17729,10 +17729,10 @@
         <v>1.07</v>
       </c>
       <c r="I396" t="n">
-        <v>0.1486</v>
+        <v>0.2159</v>
       </c>
       <c r="J396" t="n">
-        <v>4.0122</v>
+        <v>5.8293</v>
       </c>
     </row>
     <row r="397">
@@ -17769,10 +17769,10 @@
         <v>1.37</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6179</v>
+        <v>0.7487</v>
       </c>
       <c r="J397" t="n">
-        <v>16.6833</v>
+        <v>20.2149</v>
       </c>
     </row>
     <row r="398">
@@ -17809,10 +17809,10 @@
         <v>1.08</v>
       </c>
       <c r="I398" t="n">
-        <v>0.2031</v>
+        <v>0.2114</v>
       </c>
       <c r="J398" t="n">
-        <v>5.4837</v>
+        <v>5.7078</v>
       </c>
     </row>
     <row r="399">
@@ -17849,10 +17849,10 @@
         <v>0.83</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.3326</v>
+        <v>-0.2056</v>
       </c>
       <c r="J399" t="n">
-        <v>-8.9802</v>
+        <v>-5.5512</v>
       </c>
     </row>
     <row r="400">
@@ -17889,10 +17889,10 @@
         <v>0.83</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.3326</v>
+        <v>-0.2056</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.9802</v>
+        <v>-5.5512</v>
       </c>
     </row>
     <row r="401">
@@ -17929,10 +17929,10 @@
         <v>0.76</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.4343</v>
+        <v>-0.2755</v>
       </c>
       <c r="J401" t="n">
-        <v>-11.7261</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="402">
@@ -17969,10 +17969,10 @@
         <v>1.44</v>
       </c>
       <c r="I402" t="n">
-        <v>1.1019</v>
+        <v>1.0649</v>
       </c>
       <c r="J402" t="n">
-        <v>30.8532</v>
+        <v>29.8172</v>
       </c>
     </row>
     <row r="403">
@@ -18009,10 +18009,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4968</v>
+        <v>0.5372</v>
       </c>
       <c r="J403" t="n">
-        <v>13.9104</v>
+        <v>15.0416</v>
       </c>
     </row>
     <row r="404">
@@ -18049,10 +18049,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4372</v>
+        <v>0.4885</v>
       </c>
       <c r="J404" t="n">
-        <v>12.2416</v>
+        <v>13.678</v>
       </c>
     </row>
     <row r="405">
@@ -18089,10 +18089,10 @@
         <v>1.14</v>
       </c>
       <c r="I405" t="n">
-        <v>0.3523</v>
+        <v>0.412</v>
       </c>
       <c r="J405" t="n">
-        <v>9.8644</v>
+        <v>11.536</v>
       </c>
     </row>
     <row r="406">
@@ -18129,10 +18129,10 @@
         <v>1.04</v>
       </c>
       <c r="I406" t="n">
-        <v>0.0517</v>
+        <v>0.1202</v>
       </c>
       <c r="J406" t="n">
-        <v>1.4476</v>
+        <v>3.3656</v>
       </c>
     </row>
     <row r="407">
@@ -18169,10 +18169,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1845</v>
+        <v>0.1803</v>
       </c>
       <c r="J407" t="n">
-        <v>5.166</v>
+        <v>5.0484</v>
       </c>
     </row>
     <row r="408">
@@ -18209,10 +18209,10 @@
         <v>0.96</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.0663</v>
+        <v>-0.0574</v>
       </c>
       <c r="J408" t="n">
-        <v>-1.8564</v>
+        <v>-1.6072</v>
       </c>
     </row>
     <row r="409">
@@ -18249,10 +18249,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1995</v>
+        <v>-0.1266</v>
       </c>
       <c r="J409" t="n">
-        <v>-5.586</v>
+        <v>-3.5448</v>
       </c>
     </row>
     <row r="410">
@@ -18289,10 +18289,10 @@
         <v>0.88</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2359</v>
+        <v>-0.1481</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.6052</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="411">
@@ -18329,10 +18329,10 @@
         <v>0.84</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3028</v>
+        <v>-0.1899</v>
       </c>
       <c r="J411" t="n">
-        <v>-8.478400000000001</v>
+        <v>-5.3172</v>
       </c>
     </row>
     <row r="412">
@@ -18369,10 +18369,10 @@
         <v>1.76</v>
       </c>
       <c r="I412" t="n">
-        <v>1.6705</v>
+        <v>1.4396</v>
       </c>
       <c r="J412" t="n">
-        <v>38.4215</v>
+        <v>33.1108</v>
       </c>
     </row>
     <row r="413">
@@ -18409,10 +18409,10 @@
         <v>1.57</v>
       </c>
       <c r="I413" t="n">
-        <v>1.3179</v>
+        <v>1.2092</v>
       </c>
       <c r="J413" t="n">
-        <v>30.3117</v>
+        <v>27.8116</v>
       </c>
     </row>
     <row r="414">
@@ -18449,10 +18449,10 @@
         <v>1.22</v>
       </c>
       <c r="I414" t="n">
-        <v>0.5125</v>
+        <v>0.5926</v>
       </c>
       <c r="J414" t="n">
-        <v>11.7875</v>
+        <v>13.6298</v>
       </c>
     </row>
     <row r="415">
@@ -18489,10 +18489,10 @@
         <v>1.02</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.0531</v>
+        <v>0.026</v>
       </c>
       <c r="J415" t="n">
-        <v>-1.2213</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="416">
@@ -18529,10 +18529,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5789</v>
+        <v>-0.5091</v>
       </c>
       <c r="J416" t="n">
-        <v>-13.3147</v>
+        <v>-11.7093</v>
       </c>
     </row>
     <row r="417">
@@ -18569,10 +18569,10 @@
         <v>0.95</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.0355</v>
+        <v>-0.0533</v>
       </c>
       <c r="J417" t="n">
-        <v>-0.8165</v>
+        <v>-1.2259</v>
       </c>
     </row>
     <row r="418">
@@ -18609,10 +18609,10 @@
         <v>0.9</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.1287</v>
+        <v>-0.114</v>
       </c>
       <c r="J418" t="n">
-        <v>-2.9601</v>
+        <v>-2.622</v>
       </c>
     </row>
     <row r="419">
@@ -18649,10 +18649,10 @@
         <v>0.79</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3358</v>
+        <v>-0.2265</v>
       </c>
       <c r="J419" t="n">
-        <v>-7.7234</v>
+        <v>-5.2095</v>
       </c>
     </row>
     <row r="420">
@@ -18689,10 +18689,10 @@
         <v>0.75</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.220700000000001</v>
+        <v>-6.095</v>
       </c>
     </row>
     <row r="421">
@@ -18729,10 +18729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4896</v>
+        <v>-0.3223</v>
       </c>
       <c r="J421" t="n">
-        <v>-11.2608</v>
+        <v>-7.4129</v>
       </c>
     </row>
     <row r="422">
@@ -18769,10 +18769,10 @@
         <v>2.18</v>
       </c>
       <c r="I422" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J422" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="423">
@@ -18809,10 +18809,10 @@
         <v>1.8</v>
       </c>
       <c r="I423" t="n">
-        <v>1.6072</v>
+        <v>1.4217</v>
       </c>
       <c r="J423" t="n">
-        <v>28.9296</v>
+        <v>25.5906</v>
       </c>
     </row>
     <row r="424">
@@ -18849,10 +18849,10 @@
         <v>1.52</v>
       </c>
       <c r="I424" t="n">
-        <v>1.0329</v>
+        <v>1.1083</v>
       </c>
       <c r="J424" t="n">
-        <v>18.5922</v>
+        <v>19.9494</v>
       </c>
     </row>
     <row r="425">
@@ -18889,10 +18889,10 @@
         <v>1.29</v>
       </c>
       <c r="I425" t="n">
-        <v>0.5588</v>
+        <v>0.6919</v>
       </c>
       <c r="J425" t="n">
-        <v>10.0584</v>
+        <v>12.4542</v>
       </c>
     </row>
     <row r="426">
@@ -18929,10 +18929,10 @@
         <v>1.26</v>
       </c>
       <c r="I426" t="n">
-        <v>0.4938</v>
+        <v>0.6223</v>
       </c>
       <c r="J426" t="n">
-        <v>8.888400000000001</v>
+        <v>11.2014</v>
       </c>
     </row>
     <row r="427">
@@ -18969,10 +18969,10 @@
         <v>0.92</v>
       </c>
       <c r="I427" t="n">
-        <v>0.0463</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J427" t="n">
-        <v>0.8334</v>
+        <v>0.1728</v>
       </c>
     </row>
     <row r="428">
@@ -19009,10 +19009,10 @@
         <v>0.63</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.4151</v>
+        <v>-0.3338</v>
       </c>
       <c r="J428" t="n">
-        <v>-7.4718</v>
+        <v>-6.0084</v>
       </c>
     </row>
     <row r="429">
@@ -19049,10 +19049,10 @@
         <v>0.44</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.5104</v>
       </c>
       <c r="J429" t="n">
-        <v>-13.3272</v>
+        <v>-9.187200000000001</v>
       </c>
     </row>
     <row r="430">
@@ -19089,10 +19089,10 @@
         <v>0.4</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.7967</v>
+        <v>-0.549</v>
       </c>
       <c r="J430" t="n">
-        <v>-14.3406</v>
+        <v>-9.882</v>
       </c>
     </row>
     <row r="431">
@@ -19129,10 +19129,10 @@
         <v>0.33</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.8904</v>
+        <v>-0.6173</v>
       </c>
       <c r="J431" t="n">
-        <v>-16.0272</v>
+        <v>-11.1114</v>
       </c>
     </row>
     <row r="432">
@@ -19169,10 +19169,10 @@
         <v>1.35</v>
       </c>
       <c r="I432" t="n">
-        <v>0.5769</v>
+        <v>0.5314</v>
       </c>
       <c r="J432" t="n">
-        <v>20.1915</v>
+        <v>18.599</v>
       </c>
     </row>
     <row r="433">
@@ -19209,10 +19209,10 @@
         <v>1.15</v>
       </c>
       <c r="I433" t="n">
-        <v>0.301</v>
+        <v>0.2593</v>
       </c>
       <c r="J433" t="n">
-        <v>10.535</v>
+        <v>9.0755</v>
       </c>
     </row>
     <row r="434">
@@ -19249,10 +19249,10 @@
         <v>0.95</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.1437</v>
+        <v>-0.0781</v>
       </c>
       <c r="J434" t="n">
-        <v>-5.0295</v>
+        <v>-2.7335</v>
       </c>
     </row>
     <row r="435">
@@ -19289,10 +19289,10 @@
         <v>0.83</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.3449</v>
+        <v>-0.2112</v>
       </c>
       <c r="J435" t="n">
-        <v>-12.0715</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="436">
@@ -19329,10 +19329,10 @@
         <v>0.83</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.3449</v>
+        <v>-0.2112</v>
       </c>
       <c r="J436" t="n">
-        <v>-12.0715</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="437">
@@ -19369,10 +19369,10 @@
         <v>1.48</v>
       </c>
       <c r="I437" t="n">
-        <v>0.7199</v>
+        <v>0.635</v>
       </c>
       <c r="J437" t="n">
-        <v>25.1965</v>
+        <v>22.225</v>
       </c>
     </row>
     <row r="438">
@@ -19409,10 +19409,10 @@
         <v>1.14</v>
       </c>
       <c r="I438" t="n">
-        <v>0.2694</v>
+        <v>0.2208</v>
       </c>
       <c r="J438" t="n">
-        <v>9.429</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="439">
@@ -19449,10 +19449,10 @@
         <v>1.01</v>
       </c>
       <c r="I439" t="n">
-        <v>0.0009</v>
+        <v>0.0205</v>
       </c>
       <c r="J439" t="n">
-        <v>0.0315</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="440">
@@ -19489,10 +19489,10 @@
         <v>0.86</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.3093</v>
+        <v>-0.1847</v>
       </c>
       <c r="J440" t="n">
-        <v>-10.8255</v>
+        <v>-6.4645</v>
       </c>
     </row>
     <row r="441">
@@ -19529,10 +19529,10 @@
         <v>0.83</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.3541</v>
+        <v>-0.2159</v>
       </c>
       <c r="J441" t="n">
-        <v>-12.3935</v>
+        <v>-7.5565</v>
       </c>
     </row>
     <row r="442">
@@ -19569,10 +19569,10 @@
         <v>2.01</v>
       </c>
       <c r="I442" t="n">
-        <v>1.9794</v>
+        <v>1.6816</v>
       </c>
       <c r="J442" t="n">
-        <v>41.5674</v>
+        <v>35.3136</v>
       </c>
     </row>
     <row r="443">
@@ -19609,10 +19609,10 @@
         <v>1.55</v>
       </c>
       <c r="I443" t="n">
-        <v>1.1927</v>
+        <v>1.1552</v>
       </c>
       <c r="J443" t="n">
-        <v>25.0467</v>
+        <v>24.2592</v>
       </c>
     </row>
     <row r="444">
@@ -19649,10 +19649,10 @@
         <v>1.39</v>
       </c>
       <c r="I444" t="n">
-        <v>0.821</v>
+        <v>0.9383</v>
       </c>
       <c r="J444" t="n">
-        <v>17.241</v>
+        <v>19.7043</v>
       </c>
     </row>
     <row r="445">
@@ -19689,10 +19689,10 @@
         <v>1.36</v>
       </c>
       <c r="I445" t="n">
-        <v>0.7551</v>
+        <v>0.8757</v>
       </c>
       <c r="J445" t="n">
-        <v>15.8571</v>
+        <v>18.3897</v>
       </c>
     </row>
     <row r="446">
@@ -19729,10 +19729,10 @@
         <v>1.03</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.0629</v>
+        <v>0.024</v>
       </c>
       <c r="J446" t="n">
-        <v>-1.3209</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="447">
@@ -19769,10 +19769,10 @@
         <v>0.97</v>
       </c>
       <c r="I447" t="n">
-        <v>0.059</v>
+        <v>0.0108</v>
       </c>
       <c r="J447" t="n">
-        <v>1.239</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="448">
@@ -19809,10 +19809,10 @@
         <v>0.87</v>
       </c>
       <c r="I448" t="n">
-        <v>-0.1244</v>
+        <v>-0.1227</v>
       </c>
       <c r="J448" t="n">
-        <v>-2.6124</v>
+        <v>-2.5767</v>
       </c>
     </row>
     <row r="449">
@@ -19849,10 +19849,10 @@
         <v>0.65</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.5008</v>
+        <v>-0.3424</v>
       </c>
       <c r="J449" t="n">
-        <v>-10.5168</v>
+        <v>-7.1904</v>
       </c>
     </row>
     <row r="450">
@@ -19889,10 +19889,10 @@
         <v>0.54</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.6586</v>
+        <v>-0.445</v>
       </c>
       <c r="J450" t="n">
-        <v>-13.8306</v>
+        <v>-9.345000000000001</v>
       </c>
     </row>
     <row r="451">
@@ -19929,10 +19929,10 @@
         <v>0.46</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.7628</v>
+        <v>-0.5198</v>
       </c>
       <c r="J451" t="n">
-        <v>-16.0188</v>
+        <v>-10.9158</v>
       </c>
     </row>
     <row r="452">
@@ -19969,10 +19969,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>1.5852</v>
+        <v>1.3802</v>
       </c>
       <c r="J452" t="n">
-        <v>45.9708</v>
+        <v>40.0258</v>
       </c>
     </row>
     <row r="453">
@@ -20009,10 +20009,10 @@
         <v>1.27</v>
       </c>
       <c r="I453" t="n">
-        <v>0.7198</v>
+        <v>0.7241</v>
       </c>
       <c r="J453" t="n">
-        <v>20.8742</v>
+        <v>20.9989</v>
       </c>
     </row>
     <row r="454">
@@ -20049,10 +20049,10 @@
         <v>1.17</v>
       </c>
       <c r="I454" t="n">
-        <v>0.4341</v>
+        <v>0.4877</v>
       </c>
       <c r="J454" t="n">
-        <v>12.5889</v>
+        <v>14.1433</v>
       </c>
     </row>
     <row r="455">
@@ -20089,10 +20089,10 @@
         <v>0.98</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.2236</v>
+        <v>-0.1447</v>
       </c>
       <c r="J455" t="n">
-        <v>-6.4844</v>
+        <v>-4.1963</v>
       </c>
     </row>
     <row r="456">
@@ -20129,10 +20129,10 @@
         <v>0.89</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.4322</v>
       </c>
       <c r="J456" t="n">
-        <v>-14.6015</v>
+        <v>-12.5338</v>
       </c>
     </row>
     <row r="457">
@@ -20169,10 +20169,10 @@
         <v>1.3</v>
       </c>
       <c r="I457" t="n">
-        <v>0.5149</v>
+        <v>0.6112</v>
       </c>
       <c r="J457" t="n">
-        <v>14.9321</v>
+        <v>17.7248</v>
       </c>
     </row>
     <row r="458">
@@ -20209,10 +20209,10 @@
         <v>1.23</v>
       </c>
       <c r="I458" t="n">
-        <v>0.4206</v>
+        <v>0.488</v>
       </c>
       <c r="J458" t="n">
-        <v>12.1974</v>
+        <v>14.152</v>
       </c>
     </row>
     <row r="459">
@@ -20249,10 +20249,10 @@
         <v>0.95</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.1416</v>
+        <v>-0.0775</v>
       </c>
       <c r="J459" t="n">
-        <v>-4.1064</v>
+        <v>-2.2475</v>
       </c>
     </row>
     <row r="460">
@@ -20289,10 +20289,10 @@
         <v>0.8</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.3872</v>
+        <v>-0.2409</v>
       </c>
       <c r="J460" t="n">
-        <v>-11.2288</v>
+        <v>-6.9861</v>
       </c>
     </row>
     <row r="461">
@@ -20329,10 +20329,10 @@
         <v>0.8</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.3872</v>
+        <v>-0.2409</v>
       </c>
       <c r="J461" t="n">
-        <v>-11.2288</v>
+        <v>-6.9861</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5246/event_5246_evp_summary.xlsx
+++ b/database/event/5246/event_5246_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.284</v>
+        <v>7.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1179</v>
+        <v>1.0897</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6503</v>
+        <v>2.6079</v>
       </c>
       <c r="E2" t="n">
-        <v>7.284</v>
+        <v>7.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6613</v>
+        <v>4.3275</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6227</v>
+        <v>2.7725</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8754</v>
+        <v>6.7467</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8754</v>
+        <v>6.7467</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6227</v>
+        <v>2.7725</v>
       </c>
       <c r="K2" t="n">
         <v>401</v>
@@ -529,7 +529,7 @@
         <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>9.498100000000001</v>
+        <v>9.5192</v>
       </c>
       <c r="N2" t="n">
         <v>429</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5602</v>
+        <v>6.2691</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0068</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3236</v>
+        <v>2.2296</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5602</v>
+        <v>6.2691</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2962</v>
+        <v>4.9222</v>
       </c>
       <c r="G3" t="n">
-        <v>1.264</v>
+        <v>1.3469</v>
       </c>
       <c r="H3" t="n">
-        <v>8.269600000000001</v>
+        <v>8.048299999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>8.269600000000001</v>
+        <v>8.048299999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.264</v>
+        <v>1.3469</v>
       </c>
       <c r="K3" t="n">
         <v>401</v>
@@ -575,7 +575,7 @@
         <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>9.5336</v>
+        <v>9.395199999999999</v>
       </c>
       <c r="N3" t="n">
         <v>429</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4326</v>
+        <v>5.0272</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8338</v>
+        <v>0.7716</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8145</v>
+        <v>1.6643</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4326</v>
+        <v>5.0272</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4326</v>
+        <v>5.0272</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8.569000000000001</v>
+        <v>8.2781</v>
       </c>
       <c r="I4" t="n">
-        <v>8.569000000000001</v>
+        <v>8.2781</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>8.569000000000001</v>
+        <v>8.2781</v>
       </c>
       <c r="N4" t="n">
         <v>457</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1815</v>
+        <v>4.803</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7952</v>
+        <v>0.7372</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7012</v>
+        <v>1.5622</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1815</v>
+        <v>4.803</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5652</v>
+        <v>4.2437</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6163</v>
+        <v>0.5593</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6645</v>
+        <v>6.5633</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9386</v>
+        <v>6.7324</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6163</v>
+        <v>0.5593</v>
       </c>
       <c r="K5" t="n">
         <v>515</v>
@@ -667,7 +667,7 @@
         <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>7.5549</v>
+        <v>7.291700000000001</v>
       </c>
       <c r="N5" t="n">
         <v>543</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.989</v>
+        <v>4.5594</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7657</v>
+        <v>0.6998</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6143</v>
+        <v>1.4513</v>
       </c>
       <c r="E6" t="n">
-        <v>4.989</v>
+        <v>4.5594</v>
       </c>
       <c r="F6" t="n">
-        <v>4.989</v>
+        <v>4.5594</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5951</v>
+        <v>7.2542</v>
       </c>
       <c r="I6" t="n">
-        <v>7.5951</v>
+        <v>7.2542</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5951</v>
+        <v>7.2542</v>
       </c>
       <c r="N6" t="n">
         <v>457</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8313</v>
+        <v>3.4668</v>
       </c>
       <c r="C7" t="n">
-        <v>0.588</v>
+        <v>0.5321</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0916</v>
+        <v>0.954</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8313</v>
+        <v>3.4668</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8313</v>
+        <v>3.4668</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0531</v>
+        <v>4.8629</v>
       </c>
       <c r="I7" t="n">
-        <v>5.0531</v>
+        <v>4.8629</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.0531</v>
+        <v>4.8629</v>
       </c>
       <c r="N7" t="n">
         <v>457</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6854</v>
+        <v>3.3287</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5656</v>
+        <v>0.5109</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0258</v>
+        <v>0.8911</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6854</v>
+        <v>3.3287</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9059</v>
+        <v>2.5863</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7795</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0211</v>
+        <v>2.9356</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0211</v>
+        <v>2.9356</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7795</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>401</v>
@@ -805,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8006</v>
+        <v>3.678</v>
       </c>
       <c r="N8" t="n">
         <v>429</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6134</v>
+        <v>3.2829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5546</v>
+        <v>0.5039</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9933</v>
+        <v>0.8702</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6134</v>
+        <v>3.2829</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6134</v>
+        <v>3.2829</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5746</v>
+        <v>4.4604</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5746</v>
+        <v>4.4604</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5746</v>
+        <v>4.4604</v>
       </c>
       <c r="N9" t="n">
         <v>356</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3576</v>
+        <v>2.9439</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5153</v>
+        <v>0.4518</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8778</v>
+        <v>0.7159</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3576</v>
+        <v>2.9439</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3576</v>
+        <v>2.9439</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.013</v>
+        <v>3.7184</v>
       </c>
       <c r="I10" t="n">
-        <v>4.013</v>
+        <v>3.7184</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.013</v>
+        <v>3.7184</v>
       </c>
       <c r="N10" t="n">
         <v>347</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2133</v>
+        <v>2.91</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4932</v>
+        <v>0.4466</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8126</v>
+        <v>0.7005</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2133</v>
+        <v>2.91</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2133</v>
+        <v>2.91</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6961</v>
+        <v>3.6442</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6961</v>
+        <v>3.6442</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6961</v>
+        <v>3.6442</v>
       </c>
       <c r="N11" t="n">
         <v>356</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0391</v>
+        <v>2.6826</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4664</v>
+        <v>0.4117</v>
       </c>
       <c r="D12" t="n">
-        <v>0.734</v>
+        <v>0.597</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0391</v>
+        <v>2.6826</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0391</v>
+        <v>2.6826</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3136</v>
+        <v>3.1465</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3136</v>
+        <v>3.1465</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3136</v>
+        <v>3.1465</v>
       </c>
       <c r="N12" t="n">
         <v>296</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9382</v>
+        <v>2.5779</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4509</v>
+        <v>0.3956</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6884</v>
+        <v>0.5493</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9382</v>
+        <v>2.5779</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9382</v>
+        <v>2.5779</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0921</v>
+        <v>2.9173</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0921</v>
+        <v>2.9173</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0921</v>
+        <v>2.9173</v>
       </c>
       <c r="N13" t="n">
         <v>347</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8542</v>
+        <v>2.5054</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4381</v>
+        <v>0.3845</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6505</v>
+        <v>0.5163</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8542</v>
+        <v>2.5054</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8542</v>
+        <v>2.5054</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9076</v>
+        <v>2.7585</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9076</v>
+        <v>2.7585</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9076</v>
+        <v>2.7585</v>
       </c>
       <c r="N14" t="n">
         <v>356</v>
@@ -1090,81 +1090,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6729</v>
+        <v>2.3549</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4102</v>
+        <v>0.3614</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5687</v>
+        <v>0.4478</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6729</v>
+        <v>2.3549</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4482</v>
+        <v>2.3549</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7753</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2119</v>
+        <v>2.4293</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3851</v>
+        <v>2.4293</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7753</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>515</v>
+        <v>296</v>
       </c>
       <c r="L15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6098</v>
+        <v>2.4293</v>
       </c>
       <c r="N15" t="n">
-        <v>543</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5752</v>
+        <v>2.352</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3952</v>
+        <v>0.361</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5246</v>
+        <v>0.4465</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5752</v>
+        <v>2.352</v>
       </c>
       <c r="F16" t="n">
-        <v>3.313</v>
+        <v>3.1547</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7378</v>
+        <v>-0.8027</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9151</v>
+        <v>4.1798</v>
       </c>
       <c r="I16" t="n">
-        <v>4.0761</v>
+        <v>4.2875</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7378</v>
+        <v>-0.8027</v>
       </c>
       <c r="K16" t="n">
         <v>515</v>
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3383</v>
+        <v>3.4848</v>
       </c>
       <c r="N16" t="n">
         <v>543</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5611</v>
+        <v>2.2845</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3931</v>
+        <v>0.3506</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5182</v>
+        <v>0.4157</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5611</v>
+        <v>2.2845</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5611</v>
+        <v>1.6194</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5611</v>
+        <v>1.6194</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5611</v>
+        <v>1.6194</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.6651</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>401</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5611</v>
+        <v>2.2845</v>
       </c>
       <c r="N17" t="n">
-        <v>296</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3325</v>
+        <v>2.1949</v>
       </c>
       <c r="C18" t="n">
-        <v>0.358</v>
+        <v>0.3369</v>
       </c>
       <c r="D18" t="n">
-        <v>0.415</v>
+        <v>0.375</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3325</v>
+        <v>2.1949</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6709</v>
+        <v>2.9616</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6616</v>
+        <v>-0.7667</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6709</v>
+        <v>3.7571</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6709</v>
+        <v>3.8539</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6616</v>
+        <v>-0.7667</v>
       </c>
       <c r="K18" t="n">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="L18" t="n">
         <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3325</v>
+        <v>3.0872</v>
       </c>
       <c r="N18" t="n">
-        <v>429</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3284</v>
+        <v>0.316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.328</v>
+        <v>0.3131</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1398</v>
+        <v>2.059</v>
       </c>
       <c r="N19" t="n">
         <v>356</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2972</v>
+        <v>0.2797</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2362</v>
+        <v>0.2054</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9365</v>
+        <v>1.8224</v>
       </c>
       <c r="N20" t="n">
         <v>347</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2894</v>
+        <v>0.2728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2132</v>
+        <v>0.185</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>296</v>
+        <v>457</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8856</v>
+        <v>1.7775</v>
       </c>
       <c r="N21" t="n">
-        <v>296</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2817</v>
+        <v>0.2701</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1907</v>
+        <v>0.1768</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>457</v>
+        <v>296</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8356</v>
+        <v>1.7597</v>
       </c>
       <c r="N22" t="n">
-        <v>457</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2731</v>
+        <v>0.2534</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1654</v>
+        <v>0.1274</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7796</v>
+        <v>1.651</v>
       </c>
       <c r="N23" t="n">
         <v>356</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1986</v>
+        <v>0.1764</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0539</v>
+        <v>-0.1011</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2938</v>
+        <v>1.1492</v>
       </c>
       <c r="N24" t="n">
         <v>296</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7945</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1219</v>
+        <v>0.1034</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2793</v>
+        <v>-0.3174</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7945</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7945</v>
+        <v>0.9426</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.2687</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7945</v>
+        <v>0.9426</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7945</v>
+        <v>0.9669</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.2687</v>
       </c>
       <c r="K25" t="n">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7945</v>
+        <v>0.6981999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>457</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7278</v>
+        <v>0.6201</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1117</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3094</v>
+        <v>-0.3419</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7278</v>
+        <v>0.6201</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9764</v>
+        <v>0.6201</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2486</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9764</v>
+        <v>0.6201</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0166</v>
+        <v>0.6201</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2486</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>515</v>
+        <v>457</v>
       </c>
       <c r="L26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.768</v>
+        <v>0.6201</v>
       </c>
       <c r="N26" t="n">
-        <v>543</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="C27" t="n">
-        <v>0.077</v>
+        <v>0.0605</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4114</v>
+        <v>-0.4447</v>
       </c>
       <c r="E27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="F27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="I27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.502</v>
+        <v>0.3943</v>
       </c>
       <c r="N27" t="n">
         <v>296</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.3193</v>
+        <v>-1.1936</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2025</v>
+        <v>-0.1832</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.2336</v>
+        <v>-1.1676</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3193</v>
+        <v>-1.1936</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0373</v>
+        <v>-0.9568</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.282</v>
+        <v>-0.2368</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0373</v>
+        <v>-0.9568</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0373</v>
+        <v>-0.9568</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.282</v>
+        <v>-0.2368</v>
       </c>
       <c r="K28" t="n">
         <v>401</v>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.3193</v>
+        <v>-1.1936</v>
       </c>
       <c r="N28" t="n">
         <v>429</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.495</v>
+        <v>-1.4813</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2294</v>
+        <v>-0.2273</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.3129</v>
+        <v>-1.2985</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.495</v>
+        <v>-1.4813</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1751</v>
+        <v>-1.1268</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3199</v>
+        <v>-0.3545</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1751</v>
+        <v>-1.1268</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.2234</v>
+        <v>-1.1558</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3199</v>
+        <v>-0.3545</v>
       </c>
       <c r="K29" t="n">
         <v>515</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.5433</v>
+        <v>-1.5103</v>
       </c>
       <c r="N29" t="n">
         <v>543</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.355</v>
+        <v>-0.3526</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.6821</v>
+        <v>-1.67</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.3128</v>
+        <v>-2.2974</v>
       </c>
       <c r="N30" t="n">
         <v>347</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3821</v>
+        <v>-0.3834</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.7619</v>
+        <v>-1.7615</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.4894</v>
+        <v>-2.4983</v>
       </c>
       <c r="N31" t="n">
         <v>347</v>
@@ -1969,10 +1969,10 @@
         <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3622</v>
+        <v>1.4591</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3622</v>
+        <v>1.4591</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.89</v>
+        <v>0.8407</v>
       </c>
       <c r="J3" t="n">
-        <v>0.89</v>
+        <v>0.8407</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6212</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6212</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0693</v>
+        <v>0.0936</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0693</v>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0089</v>
+        <v>0.0156</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0089</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1076</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2183</v>
+        <v>-0.2386</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2183</v>
+        <v>-0.2386</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3117</v>
+        <v>-0.3303</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3117</v>
+        <v>-0.3303</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.321</v>
+        <v>-0.3393</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.321</v>
+        <v>-0.3393</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3585</v>
+        <v>-0.3753</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3585</v>
+        <v>-0.3753</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2729</v>
+        <v>1.3313</v>
       </c>
       <c r="J12" t="n">
-        <v>34.3683</v>
+        <v>35.9451</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2605</v>
+        <v>1.3134</v>
       </c>
       <c r="J13" t="n">
-        <v>34.0335</v>
+        <v>35.4618</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0404</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0908</v>
+        <v>1.6956</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.99</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1105</v>
+        <v>-0.0983</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.9835</v>
+        <v>-2.6541</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3513</v>
+        <v>-0.3304</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.485099999999999</v>
+        <v>-8.9208</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7033</v>
+        <v>0.6669</v>
       </c>
       <c r="J17" t="n">
-        <v>18.9891</v>
+        <v>18.0063</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0631</v>
+        <v>0.0616</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7037</v>
+        <v>1.6632</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1016</v>
+        <v>-0.1159</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7432</v>
+        <v>-3.1293</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4168</v>
+        <v>-0.4274</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.2536</v>
+        <v>-11.5398</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4168</v>
+        <v>-0.4274</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.2536</v>
+        <v>-11.5398</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0149</v>
+        <v>-0.003</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3874</v>
+        <v>-0.078</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.187</v>
+        <v>-0.2056</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.862</v>
+        <v>-5.3456</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2443</v>
+        <v>-0.2627</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.3518</v>
+        <v>-6.8302</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2825</v>
+        <v>-0.3002</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.345</v>
+        <v>-7.8052</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3111</v>
+        <v>-0.328</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.0886</v>
+        <v>-8.528</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>0.951</v>
+        <v>0.8969</v>
       </c>
       <c r="J27" t="n">
-        <v>24.726</v>
+        <v>23.3194</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.951</v>
+        <v>0.8969</v>
       </c>
       <c r="J28" t="n">
-        <v>24.726</v>
+        <v>23.3194</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9308</v>
+        <v>0.8778</v>
       </c>
       <c r="J29" t="n">
-        <v>24.2008</v>
+        <v>22.8228</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.19</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5233</v>
+        <v>0.5148</v>
       </c>
       <c r="J30" t="n">
-        <v>13.6058</v>
+        <v>13.3848</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>1.03</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0674</v>
+        <v>0.0922</v>
       </c>
       <c r="J31" t="n">
-        <v>1.7524</v>
+        <v>2.3972</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7736</v>
+        <v>0.7381</v>
       </c>
       <c r="J32" t="n">
-        <v>23.208</v>
+        <v>22.143</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5668</v>
+        <v>0.5512</v>
       </c>
       <c r="J33" t="n">
-        <v>17.004</v>
+        <v>16.536</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0856</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.259</v>
+        <v>-2.568</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.77</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2681</v>
+        <v>-0.2812</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.042999999999999</v>
+        <v>-8.436</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4377</v>
+        <v>-0.4454</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.131</v>
+        <v>-13.362</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1687</v>
+        <v>1.1307</v>
       </c>
       <c r="J37" t="n">
-        <v>35.061</v>
+        <v>33.921</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.28</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7631</v>
+        <v>0.7232</v>
       </c>
       <c r="J38" t="n">
-        <v>22.893</v>
+        <v>21.696</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.02</v>
+        <v>0.0358</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0348</v>
+        <v>-0.024</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.044</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3</v>
+        <v>-0.2874</v>
       </c>
       <c r="J41" t="n">
-        <v>-9</v>
+        <v>-8.622</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0326</v>
+        <v>0.9707</v>
       </c>
       <c r="J42" t="n">
-        <v>30.978</v>
+        <v>29.121</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4939</v>
+        <v>0.4781</v>
       </c>
       <c r="J43" t="n">
-        <v>14.817</v>
+        <v>14.343</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1077</v>
+        <v>-0.1091</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.231</v>
+        <v>-3.273</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2128</v>
+        <v>-0.211</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.384</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6121</v>
+        <v>-0.5762</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.363</v>
+        <v>-17.286</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9362</v>
+        <v>0.8848</v>
       </c>
       <c r="J47" t="n">
-        <v>28.086</v>
+        <v>26.544</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3646</v>
+        <v>0.3645</v>
       </c>
       <c r="J48" t="n">
-        <v>10.938</v>
+        <v>10.935</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.01</v>
       </c>
       <c r="I49" t="n">
-        <v>0.038</v>
+        <v>0.0435</v>
       </c>
       <c r="J49" t="n">
-        <v>1.14</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.336</v>
+        <v>-0.3475</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.08</v>
+        <v>-10.425</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.63</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4015</v>
+        <v>-0.4106</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.045</v>
+        <v>-12.318</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>1.148</v>
+        <v>1.1124</v>
       </c>
       <c r="J52" t="n">
-        <v>32.144</v>
+        <v>31.1472</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7181</v>
+        <v>0.6877</v>
       </c>
       <c r="J53" t="n">
-        <v>20.1068</v>
+        <v>19.2556</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4987</v>
       </c>
       <c r="J54" t="n">
-        <v>14.2128</v>
+        <v>13.9636</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4054</v>
+        <v>0.406</v>
       </c>
       <c r="J55" t="n">
-        <v>11.3512</v>
+        <v>11.368</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.03</v>
       </c>
       <c r="I56" t="n">
-        <v>0.078</v>
+        <v>0.0997</v>
       </c>
       <c r="J56" t="n">
-        <v>2.184</v>
+        <v>2.7916</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2708</v>
+        <v>0.2702</v>
       </c>
       <c r="J57" t="n">
-        <v>7.5824</v>
+        <v>7.5656</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.932</v>
+        <v>-2.2652</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0929</v>
+        <v>-0.1061</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.6012</v>
+        <v>-2.9708</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1364</v>
+        <v>-0.1514</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.8192</v>
+        <v>-4.2392</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3073</v>
+        <v>-0.3214</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.6044</v>
+        <v>-8.9992</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5121</v>
+        <v>1.5128</v>
       </c>
       <c r="J62" t="n">
-        <v>30.242</v>
+        <v>30.256</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2228</v>
+        <v>1.2044</v>
       </c>
       <c r="J63" t="n">
-        <v>24.456</v>
+        <v>24.088</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.59</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1898</v>
+        <v>1.1686</v>
       </c>
       <c r="J64" t="n">
-        <v>23.796</v>
+        <v>23.372</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.45</v>
       </c>
       <c r="I65" t="n">
-        <v>1.0222</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>20.444</v>
+        <v>19.628</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>1.44</v>
       </c>
       <c r="I66" t="n">
-        <v>1.0072</v>
+        <v>0.9649</v>
       </c>
       <c r="J66" t="n">
-        <v>20.144</v>
+        <v>19.298</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5835</v>
+        <v>0.5152</v>
       </c>
       <c r="J67" t="n">
-        <v>11.67</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>0.74</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2291</v>
+        <v>-0.257</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.582</v>
+        <v>-5.14</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.41</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5458</v>
+        <v>-0.5558</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.916</v>
+        <v>-11.116</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.33</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6231</v>
+        <v>-0.6269</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.462</v>
+        <v>-12.538</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6815</v>
+        <v>-0.6802</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.63</v>
+        <v>-13.604</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9689</v>
+        <v>0.9109</v>
       </c>
       <c r="J72" t="n">
-        <v>29.067</v>
+        <v>27.327</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8159</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>24.477</v>
+        <v>23.181</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.28</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7468</v>
+        <v>0.7119</v>
       </c>
       <c r="J74" t="n">
-        <v>22.404</v>
+        <v>21.357</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3574</v>
+        <v>0.3608</v>
       </c>
       <c r="J75" t="n">
-        <v>10.722</v>
+        <v>10.824</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.92</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3449</v>
+        <v>-0.3259</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.347</v>
+        <v>-9.776999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0498</v>
+        <v>0.052</v>
       </c>
       <c r="J77" t="n">
-        <v>1.494</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0109</v>
+        <v>0.0078</v>
       </c>
       <c r="J78" t="n">
-        <v>0.327</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1054</v>
+        <v>-0.1188</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.162</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1491</v>
+        <v>-0.1639</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.473</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1491</v>
+        <v>-0.1639</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.473</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.65</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8534</v>
+        <v>0.8239</v>
       </c>
       <c r="J82" t="n">
-        <v>25.602</v>
+        <v>24.717</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.22</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3319</v>
+        <v>0.3426</v>
       </c>
       <c r="J83" t="n">
-        <v>9.957000000000001</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2532</v>
+        <v>0.2665</v>
       </c>
       <c r="J84" t="n">
-        <v>7.596</v>
+        <v>7.995</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0503</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>1.509</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2861</v>
+        <v>-0.2954</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.583</v>
+        <v>-8.862</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4378</v>
+        <v>0.4426</v>
       </c>
       <c r="J87" t="n">
-        <v>13.134</v>
+        <v>13.278</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4254</v>
+        <v>0.4309</v>
       </c>
       <c r="J88" t="n">
-        <v>12.762</v>
+        <v>12.927</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1349</v>
+        <v>-0.1475</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.047</v>
+        <v>-4.425</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1675</v>
+        <v>-0.1807</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.025</v>
+        <v>-5.421</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3652</v>
+        <v>-0.3755</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.956</v>
+        <v>-11.265</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6763</v>
+        <v>0.6402</v>
       </c>
       <c r="J92" t="n">
-        <v>19.6127</v>
+        <v>18.5658</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.389</v>
+        <v>0.3824</v>
       </c>
       <c r="J93" t="n">
-        <v>11.281</v>
+        <v>11.0896</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.389</v>
+        <v>0.3824</v>
       </c>
       <c r="J94" t="n">
-        <v>11.281</v>
+        <v>11.0896</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.334</v>
+        <v>-0.325</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.686</v>
+        <v>-9.425000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4482</v>
+        <v>-0.4295</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.9978</v>
+        <v>-12.4555</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.21</v>
       </c>
       <c r="I97" t="n">
-        <v>0.457</v>
+        <v>0.4507</v>
       </c>
       <c r="J97" t="n">
-        <v>13.253</v>
+        <v>13.0703</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.12</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2866</v>
+        <v>0.2909</v>
       </c>
       <c r="J98" t="n">
-        <v>8.311400000000001</v>
+        <v>8.4361</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1393</v>
+        <v>0.1479</v>
       </c>
       <c r="J99" t="n">
-        <v>4.0397</v>
+        <v>4.2891</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1161</v>
+        <v>0.1246</v>
       </c>
       <c r="J100" t="n">
-        <v>3.3669</v>
+        <v>3.6134</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4475</v>
+        <v>-0.4546</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.9775</v>
+        <v>-13.1834</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9365</v>
+        <v>0.8742</v>
       </c>
       <c r="J102" t="n">
-        <v>38.3965</v>
+        <v>35.8422</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8915</v>
+        <v>0.8336</v>
       </c>
       <c r="J103" t="n">
-        <v>36.5515</v>
+        <v>34.1776</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2929</v>
+        <v>0.2968</v>
       </c>
       <c r="J104" t="n">
-        <v>12.0089</v>
+        <v>12.1688</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1729</v>
+        <v>0.1837</v>
       </c>
       <c r="J105" t="n">
-        <v>7.0889</v>
+        <v>7.5317</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7563</v>
+        <v>-0.7009</v>
       </c>
       <c r="J106" t="n">
-        <v>-31.0083</v>
+        <v>-28.7369</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3646</v>
+        <v>0.3645</v>
       </c>
       <c r="J107" t="n">
-        <v>14.9486</v>
+        <v>14.9445</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1164</v>
+        <v>0.1249</v>
       </c>
       <c r="J108" t="n">
-        <v>4.7724</v>
+        <v>5.1209</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0358</v>
+        <v>-0.0426</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.4678</v>
+        <v>-1.7466</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.063</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.583</v>
+        <v>-2.9684</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1877</v>
+        <v>-0.2013</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.6957</v>
+        <v>-8.253299999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.98</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0487</v>
+        <v>0.0104</v>
       </c>
       <c r="J112" t="n">
-        <v>0.974</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1188</v>
+        <v>-0.143</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.376</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.7</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2958</v>
+        <v>-0.3163</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.916</v>
+        <v>-6.326</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.47</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5082</v>
+        <v>-0.5182</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.164</v>
+        <v>-10.364</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5738</v>
+        <v>-0.5792</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.476</v>
+        <v>-11.584</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4679</v>
+        <v>1.4641</v>
       </c>
       <c r="J117" t="n">
-        <v>29.358</v>
+        <v>29.282</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.64</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2523</v>
+        <v>1.2347</v>
       </c>
       <c r="J118" t="n">
-        <v>25.046</v>
+        <v>24.694</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9666</v>
+        <v>0.9207</v>
       </c>
       <c r="J119" t="n">
-        <v>19.332</v>
+        <v>18.414</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.39</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9281</v>
+        <v>0.8839</v>
       </c>
       <c r="J120" t="n">
-        <v>18.562</v>
+        <v>17.678</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8861</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>17.722</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7032</v>
+        <v>0.7036</v>
       </c>
       <c r="J122" t="n">
-        <v>14.7672</v>
+        <v>14.7756</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.41</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5037</v>
+        <v>0.5165</v>
       </c>
       <c r="J123" t="n">
-        <v>10.5777</v>
+        <v>10.8465</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4931</v>
+        <v>0.5063</v>
       </c>
       <c r="J124" t="n">
-        <v>10.3551</v>
+        <v>10.6323</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.21</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2801</v>
+        <v>0.3008</v>
       </c>
       <c r="J125" t="n">
-        <v>5.8821</v>
+        <v>6.3168</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1211</v>
+        <v>0.143</v>
       </c>
       <c r="J126" t="n">
-        <v>2.5431</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>0.88</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1227</v>
+        <v>-0.1436</v>
       </c>
       <c r="J127" t="n">
-        <v>-2.5767</v>
+        <v>-3.0156</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2186</v>
+        <v>-0.2389</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.5906</v>
+        <v>-5.0169</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2285</v>
+        <v>-0.2486</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.7985</v>
+        <v>-5.2206</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2477</v>
+        <v>-0.2675</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.2017</v>
+        <v>-5.6175</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4803</v>
+        <v>-0.4907</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.0863</v>
+        <v>-10.3047</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4149</v>
+        <v>0.409</v>
       </c>
       <c r="J132" t="n">
-        <v>11.6172</v>
+        <v>11.452</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0061</v>
+        <v>0.0043</v>
       </c>
       <c r="J133" t="n">
-        <v>0.1708</v>
+        <v>0.1204</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.3216</v>
+        <v>-1.5708</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.688</v>
+        <v>-3.0352</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3125</v>
+        <v>-0.3255</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.75</v>
+        <v>-9.114000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0208</v>
+        <v>0.9629</v>
       </c>
       <c r="J137" t="n">
-        <v>28.5824</v>
+        <v>26.9612</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6197</v>
+        <v>0.5962</v>
       </c>
       <c r="J138" t="n">
-        <v>17.3516</v>
+        <v>16.6936</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2581</v>
+        <v>0.2658</v>
       </c>
       <c r="J139" t="n">
-        <v>7.2268</v>
+        <v>7.4424</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0985</v>
+        <v>0.1139</v>
       </c>
       <c r="J140" t="n">
-        <v>2.758</v>
+        <v>3.1892</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0892</v>
+        <v>-0.0834</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.4976</v>
+        <v>-2.3352</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4447</v>
+        <v>0.4381</v>
       </c>
       <c r="J142" t="n">
-        <v>12.4516</v>
+        <v>12.2668</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.14</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3309</v>
+        <v>0.3318</v>
       </c>
       <c r="J143" t="n">
-        <v>9.2652</v>
+        <v>9.2904</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0022</v>
+        <v>0.0016</v>
       </c>
       <c r="J144" t="n">
-        <v>0.0616</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.87</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1648</v>
+        <v>-0.1786</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.6144</v>
+        <v>-5.0008</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3342</v>
+        <v>-0.3461</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.3576</v>
+        <v>-9.690799999999999</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.52</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1971</v>
+        <v>1.1583</v>
       </c>
       <c r="J147" t="n">
-        <v>33.5188</v>
+        <v>32.4324</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.17</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5082</v>
+        <v>0.4935</v>
       </c>
       <c r="J148" t="n">
-        <v>14.2296</v>
+        <v>13.818</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J149" t="n">
-        <v>4.0572</v>
+        <v>4.3568</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0736</v>
+        <v>0.0859</v>
       </c>
       <c r="J150" t="n">
-        <v>2.0608</v>
+        <v>2.4052</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.7631</v>
       </c>
       <c r="J151" t="n">
-        <v>-23.1308</v>
+        <v>-21.3668</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2201</v>
+        <v>-0.2442</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.6221</v>
+        <v>-5.1282</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2306</v>
+        <v>-0.2543</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.8426</v>
+        <v>-5.3403</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3721</v>
+        <v>-0.3909</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.8141</v>
+        <v>-8.2089</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3813</v>
+        <v>-0.3996</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.007300000000001</v>
+        <v>-8.3916</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4558</v>
+        <v>-0.47</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.5718</v>
+        <v>-9.869999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.87</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5123</v>
+        <v>1.5111</v>
       </c>
       <c r="J157" t="n">
-        <v>31.7583</v>
+        <v>31.7331</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.85</v>
       </c>
       <c r="I158" t="n">
-        <v>1.49</v>
+        <v>1.4875</v>
       </c>
       <c r="J158" t="n">
-        <v>31.29</v>
+        <v>31.2375</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.79</v>
       </c>
       <c r="I159" t="n">
-        <v>1.4226</v>
+        <v>1.4162</v>
       </c>
       <c r="J159" t="n">
-        <v>29.8746</v>
+        <v>29.7402</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4178</v>
+        <v>0.431</v>
       </c>
       <c r="J160" t="n">
-        <v>8.7738</v>
+        <v>9.051</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2533</v>
+        <v>-0.2216</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.3193</v>
+        <v>-4.6536</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.21</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3439</v>
+        <v>0.3487</v>
       </c>
       <c r="J162" t="n">
-        <v>10.317</v>
+        <v>10.461</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2147</v>
+        <v>0.2244</v>
       </c>
       <c r="J163" t="n">
-        <v>6.441</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1842</v>
+        <v>0.1946</v>
       </c>
       <c r="J164" t="n">
-        <v>5.526</v>
+        <v>5.838</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.718</v>
+        <v>-3.027</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.291</v>
+        <v>-0.3031</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.73</v>
+        <v>-9.093</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3942</v>
+        <v>0.4047</v>
       </c>
       <c r="J167" t="n">
-        <v>11.826</v>
+        <v>12.141</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2174</v>
+        <v>0.2328</v>
       </c>
       <c r="J168" t="n">
-        <v>6.522</v>
+        <v>6.984</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2174</v>
+        <v>0.2328</v>
       </c>
       <c r="J169" t="n">
-        <v>6.522</v>
+        <v>6.984</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0588</v>
+        <v>-0.0649</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.764</v>
+        <v>-1.947</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.91</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1326</v>
+        <v>-0.1429</v>
       </c>
       <c r="J171" t="n">
-        <v>-3.978</v>
+        <v>-4.287</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.67</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3519</v>
+        <v>1.3289</v>
       </c>
       <c r="J172" t="n">
-        <v>39.2051</v>
+        <v>38.5381</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7673</v>
+        <v>0.7305</v>
       </c>
       <c r="J173" t="n">
-        <v>22.2517</v>
+        <v>21.1845</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6051</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>17.5479</v>
+        <v>16.9998</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0815</v>
+        <v>0.1021</v>
       </c>
       <c r="J175" t="n">
-        <v>2.3635</v>
+        <v>2.9609</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5461</v>
+        <v>-0.5093</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.8369</v>
+        <v>-14.7697</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.361</v>
+        <v>0.3498</v>
       </c>
       <c r="J177" t="n">
-        <v>10.469</v>
+        <v>10.1442</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0015</v>
+        <v>-0.0106</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.0435</v>
+        <v>-0.3074</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2888</v>
+        <v>-0.3051</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.3752</v>
+        <v>-8.847899999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2888</v>
+        <v>-0.3051</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.3752</v>
+        <v>-8.847899999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.346</v>
+        <v>-0.3605</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.034</v>
+        <v>-10.4545</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1272</v>
+        <v>1.0892</v>
       </c>
       <c r="J182" t="n">
-        <v>27.0528</v>
+        <v>26.1408</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4614</v>
+        <v>0.456</v>
       </c>
       <c r="J183" t="n">
-        <v>11.0736</v>
+        <v>10.944</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.15</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4358</v>
+        <v>0.4327</v>
       </c>
       <c r="J184" t="n">
-        <v>10.4592</v>
+        <v>10.3848</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3565</v>
+        <v>0.3602</v>
       </c>
       <c r="J185" t="n">
-        <v>8.555999999999999</v>
+        <v>8.6448</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.11</v>
       </c>
       <c r="I186" t="n">
-        <v>0.329</v>
+        <v>0.335</v>
       </c>
       <c r="J186" t="n">
-        <v>7.896</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3164</v>
+        <v>0.3083</v>
       </c>
       <c r="J187" t="n">
-        <v>7.5936</v>
+        <v>7.3992</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0699</v>
       </c>
       <c r="J188" t="n">
-        <v>1.7856</v>
+        <v>1.6776</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.74</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.28</v>
+        <v>-0.2963</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.72</v>
+        <v>-7.1112</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2992</v>
+        <v>-0.3151</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.1808</v>
+        <v>-7.5624</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3183</v>
+        <v>-0.3336</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.6392</v>
+        <v>-8.006399999999999</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.794</v>
+        <v>0.7506</v>
       </c>
       <c r="J192" t="n">
-        <v>22.232</v>
+        <v>21.0168</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.02</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0843</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>2.3604</v>
+        <v>2.422</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.76</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2686</v>
+        <v>-0.2836</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.5208</v>
+        <v>-7.9408</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2881</v>
+        <v>-0.3027</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.066800000000001</v>
+        <v>-8.4756</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.336</v>
+        <v>-0.3492</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.407999999999999</v>
+        <v>-9.7776</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8408</v>
+        <v>0.79</v>
       </c>
       <c r="J197" t="n">
-        <v>23.5424</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6248</v>
+        <v>0.5997</v>
       </c>
       <c r="J198" t="n">
-        <v>17.4944</v>
+        <v>16.7916</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5755</v>
+        <v>0.5557</v>
       </c>
       <c r="J199" t="n">
-        <v>16.114</v>
+        <v>15.5596</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.99</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0801</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.366</v>
+        <v>-2.2428</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.355</v>
+        <v>-0.3397</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.94</v>
+        <v>-9.5116</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.081</v>
+        <v>-0.1</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.863</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2122</v>
+        <v>-0.2318</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.8806</v>
+        <v>-5.3314</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>0.79</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.222</v>
+        <v>-0.2414</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.106</v>
+        <v>-5.5522</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2408</v>
+        <v>-0.2601</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.5384</v>
+        <v>-5.9823</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4373</v>
+        <v>-0.4496</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.0579</v>
+        <v>-10.3408</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1531</v>
+        <v>1.1218</v>
       </c>
       <c r="J207" t="n">
-        <v>26.5213</v>
+        <v>25.8014</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.43</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0259</v>
+        <v>0.9777</v>
       </c>
       <c r="J208" t="n">
-        <v>23.5957</v>
+        <v>22.4871</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>1.34</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8559</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>19.6857</v>
+        <v>18.699</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6095</v>
+        <v>0.5942</v>
       </c>
       <c r="J210" t="n">
-        <v>14.0185</v>
+        <v>13.6666</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>1.08</v>
       </c>
       <c r="I211" t="n">
-        <v>0.216</v>
+        <v>0.2366</v>
       </c>
       <c r="J211" t="n">
-        <v>4.968</v>
+        <v>5.4418</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>1.06</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2121</v>
+        <v>0.1996</v>
       </c>
       <c r="J212" t="n">
-        <v>5.0904</v>
+        <v>4.7904</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.78</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2246</v>
+        <v>-0.2456</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.3904</v>
+        <v>-5.8944</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.77</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2346</v>
+        <v>-0.2554</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.6304</v>
+        <v>-6.1296</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4205</v>
+        <v>-0.435</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.092</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.42</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5604</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.4496</v>
+        <v>-13.584</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9537</v>
+        <v>0.9375</v>
       </c>
       <c r="J217" t="n">
-        <v>22.8888</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.43</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J218" t="n">
-        <v>12.4968</v>
+        <v>12.8016</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.38</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4688</v>
+        <v>0.4838</v>
       </c>
       <c r="J219" t="n">
-        <v>11.2512</v>
+        <v>11.6112</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.3</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3817</v>
+        <v>0.4002</v>
       </c>
       <c r="J220" t="n">
-        <v>9.1608</v>
+        <v>9.604799999999999</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1127</v>
+        <v>-0.1148</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.7048</v>
+        <v>-2.7552</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.5</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1781</v>
+        <v>1.1367</v>
       </c>
       <c r="J222" t="n">
-        <v>35.343</v>
+        <v>34.101</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6917</v>
+        <v>0.6556</v>
       </c>
       <c r="J223" t="n">
-        <v>20.751</v>
+        <v>19.668</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>1</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0162</v>
+        <v>-0.0111</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.486</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5903</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>-17.709</v>
+        <v>-16.677</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6166</v>
+        <v>-0.5793</v>
       </c>
       <c r="J226" t="n">
-        <v>-18.498</v>
+        <v>-17.379</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2996</v>
+        <v>0.3047</v>
       </c>
       <c r="J227" t="n">
-        <v>8.988</v>
+        <v>9.141</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.11</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2603</v>
+        <v>0.2673</v>
       </c>
       <c r="J228" t="n">
-        <v>7.809</v>
+        <v>8.019</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2403</v>
+        <v>0.2481</v>
       </c>
       <c r="J229" t="n">
-        <v>7.209</v>
+        <v>7.443</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>1.09</v>
       </c>
       <c r="I230" t="n">
-        <v>0.22</v>
+        <v>0.2285</v>
       </c>
       <c r="J230" t="n">
-        <v>6.6</v>
+        <v>6.855</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3391</v>
+        <v>-0.3499</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.173</v>
+        <v>-10.497</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.54</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>1.1655</v>
       </c>
       <c r="J232" t="n">
-        <v>34.8</v>
+        <v>33.7995</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>1.18</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5161</v>
+        <v>0.5044</v>
       </c>
       <c r="J233" t="n">
-        <v>14.9669</v>
+        <v>14.6276</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.364</v>
+        <v>0.3654</v>
       </c>
       <c r="J234" t="n">
-        <v>10.556</v>
+        <v>10.5966</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>1.02</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0544</v>
+        <v>0.0725</v>
       </c>
       <c r="J235" t="n">
-        <v>1.5776</v>
+        <v>2.1025</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0415</v>
+        <v>-0.0286</v>
       </c>
       <c r="J236" t="n">
-        <v>-1.2035</v>
+        <v>-0.8294</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>1.08</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2314</v>
+        <v>0.2317</v>
       </c>
       <c r="J237" t="n">
-        <v>6.7106</v>
+        <v>6.7193</v>
       </c>
     </row>
     <row r="238">
@@ -11449,10 +11449,10 @@
         <v>0.88</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.146</v>
+        <v>-0.1615</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.234</v>
+        <v>-4.6835</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2378</v>
+        <v>-0.2536</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.8962</v>
+        <v>-7.3544</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.1833</v>
+        <v>-7.6357</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.433</v>
+        <v>0.4259</v>
       </c>
       <c r="J242" t="n">
-        <v>12.124</v>
+        <v>11.9252</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1707</v>
+        <v>0.1766</v>
       </c>
       <c r="J243" t="n">
-        <v>4.7796</v>
+        <v>4.9448</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.05</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1479</v>
+        <v>0.1541</v>
       </c>
       <c r="J244" t="n">
-        <v>4.1412</v>
+        <v>4.3148</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2544</v>
+        <v>-0.2686</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.1232</v>
+        <v>-7.5208</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3032</v>
+        <v>-0.3163</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.489599999999999</v>
+        <v>-8.856400000000001</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.44</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0706</v>
+        <v>1.0235</v>
       </c>
       <c r="J247" t="n">
-        <v>29.9768</v>
+        <v>28.658</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5645</v>
+        <v>0.5482</v>
       </c>
       <c r="J248" t="n">
-        <v>15.806</v>
+        <v>15.3496</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4677</v>
+        <v>0.4602</v>
       </c>
       <c r="J249" t="n">
-        <v>13.0956</v>
+        <v>12.8856</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.14</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4169</v>
+        <v>0.4139</v>
       </c>
       <c r="J250" t="n">
-        <v>11.6732</v>
+        <v>11.5892</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3373</v>
+        <v>-0.3205</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.4444</v>
+        <v>-8.974</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.09</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2341</v>
+        <v>0.2387</v>
       </c>
       <c r="J252" t="n">
-        <v>7.023</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1464</v>
+        <v>0.153</v>
       </c>
       <c r="J253" t="n">
-        <v>4.392</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0776</v>
       </c>
       <c r="J254" t="n">
-        <v>2.16</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0477</v>
+        <v>-0.0565</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.431</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.323</v>
+        <v>-0.3355</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.69</v>
+        <v>-10.065</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1563</v>
+        <v>1.1149</v>
       </c>
       <c r="J257" t="n">
-        <v>34.689</v>
+        <v>33.447</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.21</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6081</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>18.243</v>
+        <v>17.496</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5579</v>
+        <v>0.5384</v>
       </c>
       <c r="J259" t="n">
-        <v>16.737</v>
+        <v>16.152</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.87</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4623</v>
+        <v>-0.4394</v>
       </c>
       <c r="J260" t="n">
-        <v>-13.869</v>
+        <v>-13.182</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8023</v>
+        <v>-0.742</v>
       </c>
       <c r="J261" t="n">
-        <v>-24.069</v>
+        <v>-22.26</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>1.86</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5273</v>
+        <v>1.5223</v>
       </c>
       <c r="J262" t="n">
-        <v>30.546</v>
+        <v>30.446</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>1.75</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4001</v>
+        <v>1.3882</v>
       </c>
       <c r="J263" t="n">
-        <v>28.002</v>
+        <v>27.764</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>1.39</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9477</v>
+        <v>0.8985</v>
       </c>
       <c r="J264" t="n">
-        <v>18.954</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>1.07</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1678</v>
+        <v>0.1957</v>
       </c>
       <c r="J265" t="n">
-        <v>3.356</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.297</v>
+        <v>-0.27</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.94</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>0.89</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1047</v>
+        <v>-0.1269</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.094</v>
+        <v>-2.538</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1722</v>
+        <v>-0.1941</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.444</v>
+        <v>-3.882</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2039</v>
+        <v>-0.2253</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.078</v>
+        <v>-4.506</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>0.64</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3548</v>
+        <v>-0.3724</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.096</v>
+        <v>-7.448</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.43</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5508</v>
+        <v>-0.5571</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.016</v>
+        <v>-11.142</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5161</v>
+        <v>0.4869</v>
       </c>
       <c r="J272" t="n">
-        <v>11.3542</v>
+        <v>10.7118</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.87</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1269</v>
+        <v>-0.1494</v>
       </c>
       <c r="J273" t="n">
-        <v>-2.7918</v>
+        <v>-3.2868</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.73</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.272</v>
+        <v>-0.2922</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.984</v>
+        <v>-6.4284</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.47</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.513</v>
+        <v>-0.522</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.286</v>
+        <v>-11.484</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.26</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7078</v>
+        <v>-0.7022</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.5716</v>
+        <v>-15.4484</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.69</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="J277" t="n">
-        <v>17.2436</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.64</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7336</v>
+        <v>0.7335</v>
       </c>
       <c r="J278" t="n">
-        <v>16.1392</v>
+        <v>16.137</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.46</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5496</v>
+        <v>0.5613</v>
       </c>
       <c r="J279" t="n">
-        <v>12.0912</v>
+        <v>12.3486</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2227</v>
+        <v>0.2461</v>
       </c>
       <c r="J280" t="n">
-        <v>4.8994</v>
+        <v>5.4142</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.099</v>
+        <v>0.1225</v>
       </c>
       <c r="J281" t="n">
-        <v>2.178</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2087</v>
+        <v>1.1802</v>
       </c>
       <c r="J282" t="n">
-        <v>29.0088</v>
+        <v>28.3248</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0457</v>
+        <v>0.9994</v>
       </c>
       <c r="J283" t="n">
-        <v>25.0968</v>
+        <v>23.9856</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.616</v>
+        <v>0.5987</v>
       </c>
       <c r="J284" t="n">
-        <v>14.784</v>
+        <v>14.3688</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>1.12</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3371</v>
+        <v>0.3468</v>
       </c>
       <c r="J285" t="n">
-        <v>8.090400000000001</v>
+        <v>8.3232</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2527</v>
+        <v>0.269</v>
       </c>
       <c r="J286" t="n">
-        <v>6.0648</v>
+        <v>6.456</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7892</v>
+        <v>0.739</v>
       </c>
       <c r="J287" t="n">
-        <v>18.9408</v>
+        <v>17.736</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2872</v>
+        <v>-0.3038</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.8928</v>
+        <v>-7.2912</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.72</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2968</v>
+        <v>-0.3132</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.1232</v>
+        <v>-7.5168</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2968</v>
+        <v>-0.3132</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.1232</v>
+        <v>-7.5168</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3444</v>
+        <v>-0.3592</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.265599999999999</v>
+        <v>-8.620799999999999</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.38</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0292</v>
+        <v>0.9641</v>
       </c>
       <c r="J292" t="n">
-        <v>30.876</v>
+        <v>28.923</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2529</v>
+        <v>0.2547</v>
       </c>
       <c r="J293" t="n">
-        <v>7.587</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1358</v>
+        <v>-0.1394</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.074</v>
+        <v>-4.182</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1358</v>
+        <v>-0.1394</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.074</v>
+        <v>-4.182</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.8064</v>
+        <v>-0.7492</v>
       </c>
       <c r="J296" t="n">
-        <v>-24.192</v>
+        <v>-22.476</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5577</v>
+        <v>0.5476</v>
       </c>
       <c r="J297" t="n">
-        <v>16.731</v>
+        <v>16.428</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4179</v>
+        <v>0.4185</v>
       </c>
       <c r="J298" t="n">
-        <v>12.537</v>
+        <v>12.555</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>2.451</v>
+        <v>2.784</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0271</v>
+        <v>0.0358</v>
       </c>
       <c r="J300" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1963</v>
+        <v>-0.208</v>
       </c>
       <c r="J301" t="n">
-        <v>-5.889</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.8</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5116</v>
+        <v>1.497</v>
       </c>
       <c r="J302" t="n">
-        <v>39.3016</v>
+        <v>38.922</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.3</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7511</v>
       </c>
       <c r="J303" t="n">
-        <v>20.5608</v>
+        <v>19.5286</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3825</v>
+        <v>0.3843</v>
       </c>
       <c r="J304" t="n">
-        <v>9.945</v>
+        <v>9.9918</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1498</v>
+        <v>0.1678</v>
       </c>
       <c r="J305" t="n">
-        <v>3.8948</v>
+        <v>4.3628</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.77</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.754</v>
+        <v>-0.6948</v>
       </c>
       <c r="J306" t="n">
-        <v>-19.604</v>
+        <v>-18.0648</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4198</v>
+        <v>0.4089</v>
       </c>
       <c r="J307" t="n">
-        <v>10.9148</v>
+        <v>10.6314</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.3634</v>
+        <v>-2.7196</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>0.91</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1135</v>
+        <v>-0.1282</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.951</v>
+        <v>-3.3332</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1555</v>
+        <v>-0.1714</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.043</v>
+        <v>-4.4564</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>0.61</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4085</v>
+        <v>-0.4193</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.621</v>
+        <v>-10.9018</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.52</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6433</v>
+        <v>0.6438</v>
       </c>
       <c r="J312" t="n">
-        <v>16.7258</v>
+        <v>16.7388</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5446</v>
+        <v>0.5515</v>
       </c>
       <c r="J313" t="n">
-        <v>14.1596</v>
+        <v>14.339</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.36</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4662</v>
+        <v>0.4774</v>
       </c>
       <c r="J314" t="n">
-        <v>12.1212</v>
+        <v>12.4124</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.24</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3279</v>
+        <v>0.3446</v>
       </c>
       <c r="J315" t="n">
-        <v>8.525399999999999</v>
+        <v>8.9596</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5355</v>
+        <v>-0.5357</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.923</v>
+        <v>-13.9282</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.03</v>
       </c>
       <c r="I317" t="n">
-        <v>0.0963</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J317" t="n">
-        <v>2.5038</v>
+        <v>2.5376</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0527</v>
+        <v>0.0516</v>
       </c>
       <c r="J318" t="n">
-        <v>1.3702</v>
+        <v>1.3416</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1834</v>
+        <v>-0.2004</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.7684</v>
+        <v>-5.2104</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.76</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2627</v>
+        <v>-0.279</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.8302</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3014</v>
+        <v>-0.3168</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.8364</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3418</v>
+        <v>0.327</v>
       </c>
       <c r="J322" t="n">
-        <v>9.2286</v>
+        <v>8.829000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>0.86</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1561</v>
+        <v>-0.1745</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.2147</v>
+        <v>-4.7115</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>0.76</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2538</v>
+        <v>-0.2722</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.8526</v>
+        <v>-7.3494</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2825</v>
+        <v>-0.3002</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.6275</v>
+        <v>-8.105399999999999</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4425</v>
+        <v>-0.4537</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.9475</v>
+        <v>-12.2499</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>2.06</v>
       </c>
       <c r="I327" t="n">
-        <v>1.791</v>
+        <v>1.7923</v>
       </c>
       <c r="J327" t="n">
-        <v>48.357</v>
+        <v>48.3921</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.19</v>
       </c>
       <c r="I328" t="n">
-        <v>0.519</v>
+        <v>0.5118</v>
       </c>
       <c r="J328" t="n">
-        <v>14.013</v>
+        <v>13.8186</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4172</v>
+        <v>0.4199</v>
       </c>
       <c r="J329" t="n">
-        <v>11.2644</v>
+        <v>11.3373</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.06</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1625</v>
+        <v>0.1846</v>
       </c>
       <c r="J330" t="n">
-        <v>4.3875</v>
+        <v>4.9842</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.99</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1254</v>
+        <v>-0.1087</v>
       </c>
       <c r="J331" t="n">
-        <v>-3.3858</v>
+        <v>-2.9349</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.24</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4947</v>
+        <v>0.4886</v>
       </c>
       <c r="J332" t="n">
-        <v>14.3463</v>
+        <v>14.1694</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2743</v>
+        <v>0.282</v>
       </c>
       <c r="J333" t="n">
-        <v>7.9547</v>
+        <v>8.178000000000001</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.08</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1947</v>
+        <v>0.205</v>
       </c>
       <c r="J334" t="n">
-        <v>5.6463</v>
+        <v>5.945</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>0.98</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0408</v>
+        <v>-0.0464</v>
       </c>
       <c r="J335" t="n">
-        <v>-1.1832</v>
+        <v>-1.3456</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>0.84</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2042</v>
+        <v>-0.2165</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.9218</v>
+        <v>-6.2785</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.36</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9999</v>
+        <v>0.9298</v>
       </c>
       <c r="J337" t="n">
-        <v>28.9971</v>
+        <v>26.9642</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.17</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5372</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>15.5788</v>
+        <v>14.8944</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.96</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1674</v>
+        <v>-0.1708</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.8546</v>
+        <v>-4.9532</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.92</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2935</v>
+        <v>-0.29</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.5115</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.999</v>
+        <v>-0.917</v>
       </c>
       <c r="J341" t="n">
-        <v>-28.971</v>
+        <v>-26.593</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3554</v>
+        <v>1.3279</v>
       </c>
       <c r="J342" t="n">
-        <v>47.439</v>
+        <v>46.4765</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.37</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9745</v>
+        <v>0.9117</v>
       </c>
       <c r="J343" t="n">
-        <v>34.1075</v>
+        <v>31.9095</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2629</v>
+        <v>-0.2539</v>
       </c>
       <c r="J344" t="n">
-        <v>-9.201499999999999</v>
+        <v>-8.8865</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4964</v>
+        <v>-0.4689</v>
       </c>
       <c r="J345" t="n">
-        <v>-17.374</v>
+        <v>-16.4115</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.8</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6561</v>
+        <v>-0.612</v>
       </c>
       <c r="J346" t="n">
-        <v>-22.9635</v>
+        <v>-21.42</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5214</v>
+        <v>0.5081</v>
       </c>
       <c r="J347" t="n">
-        <v>18.249</v>
+        <v>17.7835</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>0.93</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1093</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.402</v>
+        <v>-3.8255</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1087</v>
+        <v>-0.1213</v>
       </c>
       <c r="J349" t="n">
-        <v>-3.8045</v>
+        <v>-4.2455</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.92</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1087</v>
+        <v>-0.1213</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.8045</v>
+        <v>-4.2455</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1847</v>
+        <v>-0.1989</v>
       </c>
       <c r="J351" t="n">
-        <v>-6.4645</v>
+        <v>-6.9615</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.32</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8787</v>
+        <v>0.8207</v>
       </c>
       <c r="J352" t="n">
-        <v>26.361</v>
+        <v>24.621</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2693</v>
+        <v>0.2735</v>
       </c>
       <c r="J353" t="n">
-        <v>8.079000000000001</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.05</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1789</v>
+        <v>0.1879</v>
       </c>
       <c r="J354" t="n">
-        <v>5.367</v>
+        <v>5.637</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>1.01</v>
       </c>
       <c r="I355" t="n">
-        <v>0.0343</v>
+        <v>0.0457</v>
       </c>
       <c r="J355" t="n">
-        <v>1.029</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.99</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.0751</v>
+        <v>-0.0736</v>
       </c>
       <c r="J356" t="n">
-        <v>-2.253</v>
+        <v>-2.208</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.49</v>
       </c>
       <c r="I357" t="n">
-        <v>0.928</v>
+        <v>0.8783</v>
       </c>
       <c r="J357" t="n">
-        <v>27.84</v>
+        <v>26.349</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>1.35</v>
       </c>
       <c r="I358" t="n">
-        <v>0.6968</v>
+        <v>0.6705</v>
       </c>
       <c r="J358" t="n">
-        <v>20.904</v>
+        <v>20.115</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.92</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1134</v>
+        <v>-0.125</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.402</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.7</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.338</v>
+        <v>-0.3491</v>
       </c>
       <c r="J360" t="n">
-        <v>-10.14</v>
+        <v>-10.473</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.62</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4126</v>
+        <v>-0.421</v>
       </c>
       <c r="J361" t="n">
-        <v>-12.378</v>
+        <v>-12.63</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3019</v>
+        <v>0.317</v>
       </c>
       <c r="J362" t="n">
-        <v>8.453200000000001</v>
+        <v>8.875999999999999</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>1.19</v>
       </c>
       <c r="I363" t="n">
-        <v>0.2769</v>
+        <v>0.2926</v>
       </c>
       <c r="J363" t="n">
-        <v>7.7532</v>
+        <v>8.1928</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2003</v>
+        <v>0.2167</v>
       </c>
       <c r="J364" t="n">
-        <v>5.6084</v>
+        <v>6.0676</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>1.11</v>
       </c>
       <c r="I365" t="n">
-        <v>0.1741</v>
+        <v>0.1902</v>
       </c>
       <c r="J365" t="n">
-        <v>4.8748</v>
+        <v>5.3256</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.0325</v>
+        <v>-0.0344</v>
       </c>
       <c r="J366" t="n">
-        <v>-0.91</v>
+        <v>-0.9631999999999999</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.2</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3244</v>
+        <v>0.3313</v>
       </c>
       <c r="J367" t="n">
-        <v>9.0832</v>
+        <v>9.276400000000001</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1648</v>
+        <v>0.1763</v>
       </c>
       <c r="J368" t="n">
-        <v>4.6144</v>
+        <v>4.9364</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0238</v>
+        <v>0.0303</v>
       </c>
       <c r="J369" t="n">
-        <v>0.6664</v>
+        <v>0.8484</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>0.98</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.0406</v>
+        <v>-0.0463</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.1368</v>
+        <v>-1.2964</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.97</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.0549</v>
+        <v>-0.0619</v>
       </c>
       <c r="J371" t="n">
-        <v>-1.5372</v>
+        <v>-1.7332</v>
       </c>
     </row>
     <row r="372">
@@ -16769,10 +16769,10 @@
         <v>1.2</v>
       </c>
       <c r="I372" t="n">
-        <v>0.4301</v>
+        <v>0.4275</v>
       </c>
       <c r="J372" t="n">
-        <v>12.4729</v>
+        <v>12.3975</v>
       </c>
     </row>
     <row r="373">
@@ -16809,10 +16809,10 @@
         <v>1.08</v>
       </c>
       <c r="I373" t="n">
-        <v>0.1989</v>
+        <v>0.2081</v>
       </c>
       <c r="J373" t="n">
-        <v>5.7681</v>
+        <v>6.0349</v>
       </c>
     </row>
     <row r="374">
@@ -16849,10 +16849,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0229</v>
+        <v>-0.027</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.6641</v>
+        <v>-0.783</v>
       </c>
     </row>
     <row r="375">
@@ -16889,10 +16889,10 @@
         <v>0.95</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0882</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.2823</v>
+        <v>-2.5578</v>
       </c>
     </row>
     <row r="376">
@@ -16929,10 +16929,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1147</v>
+        <v>-0.126</v>
       </c>
       <c r="J376" t="n">
-        <v>-3.3263</v>
+        <v>-3.654</v>
       </c>
     </row>
     <row r="377">
@@ -16969,10 +16969,10 @@
         <v>1.18</v>
       </c>
       <c r="I377" t="n">
-        <v>0.532</v>
+        <v>0.5153</v>
       </c>
       <c r="J377" t="n">
-        <v>15.428</v>
+        <v>14.9437</v>
       </c>
     </row>
     <row r="378">
@@ -17009,10 +17009,10 @@
         <v>1.16</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4808</v>
+        <v>0.4691</v>
       </c>
       <c r="J378" t="n">
-        <v>13.9432</v>
+        <v>13.6039</v>
       </c>
     </row>
     <row r="379">
@@ -17049,10 +17049,10 @@
         <v>1.14</v>
       </c>
       <c r="I379" t="n">
-        <v>0.4289</v>
+        <v>0.422</v>
       </c>
       <c r="J379" t="n">
-        <v>12.4381</v>
+        <v>12.238</v>
       </c>
     </row>
     <row r="380">
@@ -17089,10 +17089,10 @@
         <v>1.09</v>
       </c>
       <c r="I380" t="n">
-        <v>0.2955</v>
+        <v>0.2986</v>
       </c>
       <c r="J380" t="n">
-        <v>8.5695</v>
+        <v>8.6594</v>
       </c>
     </row>
     <row r="381">
@@ -17129,10 +17129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.2569</v>
+        <v>-0.2498</v>
       </c>
       <c r="J381" t="n">
-        <v>-7.4501</v>
+        <v>-7.2442</v>
       </c>
     </row>
     <row r="382">
@@ -17169,10 +17169,10 @@
         <v>0.96</v>
       </c>
       <c r="I382" t="n">
-        <v>0.0048</v>
+        <v>-0.0211</v>
       </c>
       <c r="J382" t="n">
-        <v>0.1056</v>
+        <v>-0.4642</v>
       </c>
     </row>
     <row r="383">
@@ -17209,10 +17209,10 @@
         <v>0.89</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1148</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.9668</v>
+        <v>-2.5256</v>
       </c>
     </row>
     <row r="384">
@@ -17249,10 +17249,10 @@
         <v>0.88</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1014</v>
+        <v>-0.1269</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.2308</v>
+        <v>-2.7918</v>
       </c>
     </row>
     <row r="385">
@@ -17289,10 +17289,10 @@
         <v>0.34</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.6292</v>
       </c>
       <c r="J385" t="n">
-        <v>-13.805</v>
+        <v>-13.8424</v>
       </c>
     </row>
     <row r="386">
@@ -17329,10 +17329,10 @@
         <v>0.26</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.7028</v>
+        <v>-0.6982</v>
       </c>
       <c r="J386" t="n">
-        <v>-15.4616</v>
+        <v>-15.3604</v>
       </c>
     </row>
     <row r="387">
@@ -17369,10 +17369,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>1.3638</v>
+        <v>1.35</v>
       </c>
       <c r="J387" t="n">
-        <v>30.0036</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="388">
@@ -17409,10 +17409,10 @@
         <v>1.51</v>
       </c>
       <c r="I388" t="n">
-        <v>1.1148</v>
+        <v>1.0834</v>
       </c>
       <c r="J388" t="n">
-        <v>24.5256</v>
+        <v>23.8348</v>
       </c>
     </row>
     <row r="389">
@@ -17449,10 +17449,10 @@
         <v>1.35</v>
       </c>
       <c r="I389" t="n">
-        <v>0.8647</v>
+        <v>0.8234</v>
       </c>
       <c r="J389" t="n">
-        <v>19.0234</v>
+        <v>18.1148</v>
       </c>
     </row>
     <row r="390">
@@ -17489,10 +17489,10 @@
         <v>1.29</v>
       </c>
       <c r="I390" t="n">
-        <v>0.7313</v>
+        <v>0.7059</v>
       </c>
       <c r="J390" t="n">
-        <v>16.0886</v>
+        <v>15.5298</v>
       </c>
     </row>
     <row r="391">
@@ -17529,10 +17529,10 @@
         <v>1.18</v>
       </c>
       <c r="I391" t="n">
-        <v>0.4679</v>
+        <v>0.4712</v>
       </c>
       <c r="J391" t="n">
-        <v>10.2938</v>
+        <v>10.3664</v>
       </c>
     </row>
     <row r="392">
@@ -17569,10 +17569,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7251</v>
+        <v>0.6925</v>
       </c>
       <c r="J392" t="n">
-        <v>19.5777</v>
+        <v>18.6975</v>
       </c>
     </row>
     <row r="393">
@@ -17609,10 +17609,10 @@
         <v>1.27</v>
       </c>
       <c r="I393" t="n">
-        <v>0.7251</v>
+        <v>0.6925</v>
       </c>
       <c r="J393" t="n">
-        <v>19.5777</v>
+        <v>18.6975</v>
       </c>
     </row>
     <row r="394">
@@ -17649,10 +17649,10 @@
         <v>1.19</v>
       </c>
       <c r="I394" t="n">
-        <v>0.5372</v>
+        <v>0.5243</v>
       </c>
       <c r="J394" t="n">
-        <v>14.5044</v>
+        <v>14.1561</v>
       </c>
     </row>
     <row r="395">
@@ -17689,10 +17689,10 @@
         <v>1.18</v>
       </c>
       <c r="I395" t="n">
-        <v>0.5131</v>
+        <v>0.5024</v>
       </c>
       <c r="J395" t="n">
-        <v>13.8537</v>
+        <v>13.5648</v>
       </c>
     </row>
     <row r="396">
@@ -17729,10 +17729,10 @@
         <v>1.07</v>
       </c>
       <c r="I396" t="n">
-        <v>0.2159</v>
+        <v>0.2293</v>
       </c>
       <c r="J396" t="n">
-        <v>5.8293</v>
+        <v>6.1911</v>
       </c>
     </row>
     <row r="397">
@@ -17769,10 +17769,10 @@
         <v>1.37</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7487</v>
+        <v>0.7144</v>
       </c>
       <c r="J397" t="n">
-        <v>20.2149</v>
+        <v>19.2888</v>
       </c>
     </row>
     <row r="398">
@@ -17809,10 +17809,10 @@
         <v>1.08</v>
       </c>
       <c r="I398" t="n">
-        <v>0.2114</v>
+        <v>0.2171</v>
       </c>
       <c r="J398" t="n">
-        <v>5.7078</v>
+        <v>5.8617</v>
       </c>
     </row>
     <row r="399">
@@ -17849,10 +17849,10 @@
         <v>0.83</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J399" t="n">
-        <v>-5.5512</v>
+        <v>-5.9346</v>
       </c>
     </row>
     <row r="400">
@@ -17889,10 +17889,10 @@
         <v>0.83</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J400" t="n">
-        <v>-5.5512</v>
+        <v>-5.9346</v>
       </c>
     </row>
     <row r="401">
@@ -17929,10 +17929,10 @@
         <v>0.76</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.2755</v>
+        <v>-0.289</v>
       </c>
       <c r="J401" t="n">
-        <v>-7.4385</v>
+        <v>-7.803</v>
       </c>
     </row>
     <row r="402">
@@ -17969,10 +17969,10 @@
         <v>1.44</v>
       </c>
       <c r="I402" t="n">
-        <v>1.0649</v>
+        <v>1.018</v>
       </c>
       <c r="J402" t="n">
-        <v>29.8172</v>
+        <v>28.504</v>
       </c>
     </row>
     <row r="403">
@@ -18009,10 +18009,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5372</v>
+        <v>0.5243</v>
       </c>
       <c r="J403" t="n">
-        <v>15.0416</v>
+        <v>14.6804</v>
       </c>
     </row>
     <row r="404">
@@ -18049,10 +18049,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4885</v>
+        <v>0.4801</v>
       </c>
       <c r="J404" t="n">
-        <v>13.678</v>
+        <v>13.4428</v>
       </c>
     </row>
     <row r="405">
@@ -18089,10 +18089,10 @@
         <v>1.14</v>
       </c>
       <c r="I405" t="n">
-        <v>0.412</v>
+        <v>0.4105</v>
       </c>
       <c r="J405" t="n">
-        <v>11.536</v>
+        <v>11.494</v>
       </c>
     </row>
     <row r="406">
@@ -18129,10 +18129,10 @@
         <v>1.04</v>
       </c>
       <c r="I406" t="n">
-        <v>0.1202</v>
+        <v>0.1385</v>
       </c>
       <c r="J406" t="n">
-        <v>3.3656</v>
+        <v>3.878</v>
       </c>
     </row>
     <row r="407">
@@ -18169,10 +18169,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1803</v>
+        <v>0.1836</v>
       </c>
       <c r="J407" t="n">
-        <v>5.0484</v>
+        <v>5.1408</v>
       </c>
     </row>
     <row r="408">
@@ -18209,10 +18209,10 @@
         <v>0.96</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.0574</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J408" t="n">
-        <v>-1.6072</v>
+        <v>-1.9068</v>
       </c>
     </row>
     <row r="409">
@@ -18249,10 +18249,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1266</v>
+        <v>-0.141</v>
       </c>
       <c r="J409" t="n">
-        <v>-3.5448</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="410">
@@ -18289,10 +18289,10 @@
         <v>0.88</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1481</v>
+        <v>-0.1631</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.1468</v>
+        <v>-4.5668</v>
       </c>
     </row>
     <row r="411">
@@ -18329,10 +18329,10 @@
         <v>0.84</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.1899</v>
+        <v>-0.2053</v>
       </c>
       <c r="J411" t="n">
-        <v>-5.3172</v>
+        <v>-5.7484</v>
       </c>
     </row>
     <row r="412">
@@ -18369,10 +18369,10 @@
         <v>1.76</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4396</v>
+        <v>1.4252</v>
       </c>
       <c r="J412" t="n">
-        <v>33.1108</v>
+        <v>32.7796</v>
       </c>
     </row>
     <row r="413">
@@ -18409,10 +18409,10 @@
         <v>1.57</v>
       </c>
       <c r="I413" t="n">
-        <v>1.2092</v>
+        <v>1.1806</v>
       </c>
       <c r="J413" t="n">
-        <v>27.8116</v>
+        <v>27.1538</v>
       </c>
     </row>
     <row r="414">
@@ -18449,10 +18449,10 @@
         <v>1.22</v>
       </c>
       <c r="I414" t="n">
-        <v>0.5926</v>
+        <v>0.5777</v>
       </c>
       <c r="J414" t="n">
-        <v>13.6298</v>
+        <v>13.2871</v>
       </c>
     </row>
     <row r="415">
@@ -18489,10 +18489,10 @@
         <v>1.02</v>
       </c>
       <c r="I415" t="n">
-        <v>0.026</v>
+        <v>0.0527</v>
       </c>
       <c r="J415" t="n">
-        <v>0.598</v>
+        <v>1.2121</v>
       </c>
     </row>
     <row r="416">
@@ -18529,10 +18529,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.5091</v>
+        <v>-0.4722</v>
       </c>
       <c r="J416" t="n">
-        <v>-11.7093</v>
+        <v>-10.8606</v>
       </c>
     </row>
     <row r="417">
@@ -18569,10 +18569,10 @@
         <v>0.95</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.0533</v>
+        <v>-0.0687</v>
       </c>
       <c r="J417" t="n">
-        <v>-1.2259</v>
+        <v>-1.5801</v>
       </c>
     </row>
     <row r="418">
@@ -18609,10 +18609,10 @@
         <v>0.9</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.114</v>
+        <v>-0.1315</v>
       </c>
       <c r="J418" t="n">
-        <v>-2.622</v>
+        <v>-3.0245</v>
       </c>
     </row>
     <row r="419">
@@ -18649,10 +18649,10 @@
         <v>0.79</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.2265</v>
+        <v>-0.2448</v>
       </c>
       <c r="J419" t="n">
-        <v>-5.2095</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="420">
@@ -18689,10 +18689,10 @@
         <v>0.75</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J420" t="n">
-        <v>-6.095</v>
+        <v>-6.5044</v>
       </c>
     </row>
     <row r="421">
@@ -18729,10 +18729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3223</v>
+        <v>-0.3385</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.4129</v>
+        <v>-7.7855</v>
       </c>
     </row>
     <row r="422">
@@ -18769,10 +18769,10 @@
         <v>2.18</v>
       </c>
       <c r="I422" t="n">
-        <v>1.8338</v>
+        <v>1.8509</v>
       </c>
       <c r="J422" t="n">
-        <v>33.0084</v>
+        <v>33.3162</v>
       </c>
     </row>
     <row r="423">
@@ -18809,10 +18809,10 @@
         <v>1.8</v>
       </c>
       <c r="I423" t="n">
-        <v>1.4217</v>
+        <v>1.4175</v>
       </c>
       <c r="J423" t="n">
-        <v>25.5906</v>
+        <v>25.515</v>
       </c>
     </row>
     <row r="424">
@@ -18849,10 +18849,10 @@
         <v>1.52</v>
       </c>
       <c r="I424" t="n">
-        <v>1.1083</v>
+        <v>1.0805</v>
       </c>
       <c r="J424" t="n">
-        <v>19.9494</v>
+        <v>19.449</v>
       </c>
     </row>
     <row r="425">
@@ -18889,10 +18889,10 @@
         <v>1.29</v>
       </c>
       <c r="I425" t="n">
-        <v>0.6919</v>
+        <v>0.6785</v>
       </c>
       <c r="J425" t="n">
-        <v>12.4542</v>
+        <v>12.213</v>
       </c>
     </row>
     <row r="426">
@@ -18929,10 +18929,10 @@
         <v>1.26</v>
       </c>
       <c r="I426" t="n">
-        <v>0.6223</v>
+        <v>0.6169</v>
       </c>
       <c r="J426" t="n">
-        <v>11.2014</v>
+        <v>11.1042</v>
       </c>
     </row>
     <row r="427">
@@ -18969,10 +18969,10 @@
         <v>0.92</v>
       </c>
       <c r="I427" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="J427" t="n">
-        <v>0.1728</v>
+        <v>-0.5742</v>
       </c>
     </row>
     <row r="428">
@@ -19009,10 +19009,10 @@
         <v>0.63</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.3338</v>
+        <v>-0.3581</v>
       </c>
       <c r="J428" t="n">
-        <v>-6.0084</v>
+        <v>-6.4458</v>
       </c>
     </row>
     <row r="429">
@@ -19049,10 +19049,10 @@
         <v>0.44</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.5104</v>
+        <v>-0.5241</v>
       </c>
       <c r="J429" t="n">
-        <v>-9.187200000000001</v>
+        <v>-9.4338</v>
       </c>
     </row>
     <row r="430">
@@ -19089,10 +19089,10 @@
         <v>0.4</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.549</v>
+        <v>-0.5596</v>
       </c>
       <c r="J430" t="n">
-        <v>-9.882</v>
+        <v>-10.0728</v>
       </c>
     </row>
     <row r="431">
@@ -19129,10 +19129,10 @@
         <v>0.33</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6173</v>
+        <v>-0.6223</v>
       </c>
       <c r="J431" t="n">
-        <v>-11.1114</v>
+        <v>-11.2014</v>
       </c>
     </row>
     <row r="432">
@@ -19169,10 +19169,10 @@
         <v>1.35</v>
       </c>
       <c r="I432" t="n">
-        <v>0.5314</v>
+        <v>0.5238</v>
       </c>
       <c r="J432" t="n">
-        <v>18.599</v>
+        <v>18.333</v>
       </c>
     </row>
     <row r="433">
@@ -19209,10 +19209,10 @@
         <v>1.15</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2593</v>
+        <v>0.2677</v>
       </c>
       <c r="J433" t="n">
-        <v>9.0755</v>
+        <v>9.3695</v>
       </c>
     </row>
     <row r="434">
@@ -19249,10 +19249,10 @@
         <v>0.95</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.0781</v>
+        <v>-0.0878</v>
       </c>
       <c r="J434" t="n">
-        <v>-2.7335</v>
+        <v>-3.073</v>
       </c>
     </row>
     <row r="435">
@@ -19289,10 +19289,10 @@
         <v>0.83</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.2112</v>
+        <v>-0.2242</v>
       </c>
       <c r="J435" t="n">
-        <v>-7.392</v>
+        <v>-7.847</v>
       </c>
     </row>
     <row r="436">
@@ -19329,10 +19329,10 @@
         <v>0.83</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.2112</v>
+        <v>-0.2242</v>
       </c>
       <c r="J436" t="n">
-        <v>-7.392</v>
+        <v>-7.847</v>
       </c>
     </row>
     <row r="437">
@@ -19369,10 +19369,10 @@
         <v>1.48</v>
       </c>
       <c r="I437" t="n">
-        <v>0.635</v>
+        <v>0.6303</v>
       </c>
       <c r="J437" t="n">
-        <v>22.225</v>
+        <v>22.0605</v>
       </c>
     </row>
     <row r="438">
@@ -19409,10 +19409,10 @@
         <v>1.14</v>
       </c>
       <c r="I438" t="n">
-        <v>0.2208</v>
+        <v>0.2353</v>
       </c>
       <c r="J438" t="n">
-        <v>7.728</v>
+        <v>8.2355</v>
       </c>
     </row>
     <row r="439">
@@ -19449,10 +19449,10 @@
         <v>1.01</v>
       </c>
       <c r="I439" t="n">
-        <v>0.0205</v>
+        <v>0.0275</v>
       </c>
       <c r="J439" t="n">
-        <v>0.7175</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="440">
@@ -19489,10 +19489,10 @@
         <v>0.86</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.1847</v>
+        <v>-0.1965</v>
       </c>
       <c r="J440" t="n">
-        <v>-6.4645</v>
+        <v>-6.8775</v>
       </c>
     </row>
     <row r="441">
@@ -19529,10 +19529,10 @@
         <v>0.83</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.2159</v>
+        <v>-0.2278</v>
       </c>
       <c r="J441" t="n">
-        <v>-7.5565</v>
+        <v>-7.973</v>
       </c>
     </row>
     <row r="442">
@@ -19569,10 +19569,10 @@
         <v>2.01</v>
       </c>
       <c r="I442" t="n">
-        <v>1.6816</v>
+        <v>1.6865</v>
       </c>
       <c r="J442" t="n">
-        <v>35.3136</v>
+        <v>35.4165</v>
       </c>
     </row>
     <row r="443">
@@ -19609,10 +19609,10 @@
         <v>1.55</v>
       </c>
       <c r="I443" t="n">
-        <v>1.1552</v>
+        <v>1.1286</v>
       </c>
       <c r="J443" t="n">
-        <v>24.2592</v>
+        <v>23.7006</v>
       </c>
     </row>
     <row r="444">
@@ -19649,10 +19649,10 @@
         <v>1.39</v>
       </c>
       <c r="I444" t="n">
-        <v>0.9383</v>
+        <v>0.8915</v>
       </c>
       <c r="J444" t="n">
-        <v>19.7043</v>
+        <v>18.7215</v>
       </c>
     </row>
     <row r="445">
@@ -19689,10 +19689,10 @@
         <v>1.36</v>
       </c>
       <c r="I445" t="n">
-        <v>0.8757</v>
+        <v>0.8351</v>
       </c>
       <c r="J445" t="n">
-        <v>18.3897</v>
+        <v>17.5371</v>
       </c>
     </row>
     <row r="446">
@@ -19729,10 +19729,10 @@
         <v>1.03</v>
       </c>
       <c r="I446" t="n">
-        <v>0.024</v>
+        <v>0.0618</v>
       </c>
       <c r="J446" t="n">
-        <v>0.504</v>
+        <v>1.2978</v>
       </c>
     </row>
     <row r="447">
@@ -19769,10 +19769,10 @@
         <v>0.97</v>
       </c>
       <c r="I447" t="n">
-        <v>0.0108</v>
+        <v>-0.0146</v>
       </c>
       <c r="J447" t="n">
-        <v>0.2268</v>
+        <v>-0.3066</v>
       </c>
     </row>
     <row r="448">
@@ -19809,10 +19809,10 @@
         <v>0.87</v>
       </c>
       <c r="I448" t="n">
-        <v>-0.1227</v>
+        <v>-0.1461</v>
       </c>
       <c r="J448" t="n">
-        <v>-2.5767</v>
+        <v>-3.0681</v>
       </c>
     </row>
     <row r="449">
@@ -19849,10 +19849,10 @@
         <v>0.65</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.3424</v>
+        <v>-0.3612</v>
       </c>
       <c r="J449" t="n">
-        <v>-7.1904</v>
+        <v>-7.5852</v>
       </c>
     </row>
     <row r="450">
@@ -19889,10 +19889,10 @@
         <v>0.54</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.445</v>
+        <v>-0.4586</v>
       </c>
       <c r="J450" t="n">
-        <v>-9.345000000000001</v>
+        <v>-9.630599999999999</v>
       </c>
     </row>
     <row r="451">
@@ -19929,10 +19929,10 @@
         <v>0.46</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.5198</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J451" t="n">
-        <v>-10.9158</v>
+        <v>-11.1027</v>
       </c>
     </row>
     <row r="452">
@@ -19969,10 +19969,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>1.3802</v>
+        <v>1.3583</v>
       </c>
       <c r="J452" t="n">
-        <v>40.0258</v>
+        <v>39.3907</v>
       </c>
     </row>
     <row r="453">
@@ -20009,10 +20009,10 @@
         <v>1.27</v>
       </c>
       <c r="I453" t="n">
-        <v>0.7241</v>
+        <v>0.6918</v>
       </c>
       <c r="J453" t="n">
-        <v>20.9989</v>
+        <v>20.0622</v>
       </c>
     </row>
     <row r="454">
@@ -20049,10 +20049,10 @@
         <v>1.17</v>
       </c>
       <c r="I454" t="n">
-        <v>0.4877</v>
+        <v>0.4796</v>
       </c>
       <c r="J454" t="n">
-        <v>14.1433</v>
+        <v>13.9084</v>
       </c>
     </row>
     <row r="455">
@@ -20089,10 +20089,10 @@
         <v>0.98</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1447</v>
+        <v>-0.1349</v>
       </c>
       <c r="J455" t="n">
-        <v>-4.1963</v>
+        <v>-3.9121</v>
       </c>
     </row>
     <row r="456">
@@ -20129,10 +20129,10 @@
         <v>0.89</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.4322</v>
+        <v>-0.4065</v>
       </c>
       <c r="J456" t="n">
-        <v>-12.5338</v>
+        <v>-11.7885</v>
       </c>
     </row>
     <row r="457">
@@ -20169,10 +20169,10 @@
         <v>1.3</v>
       </c>
       <c r="I457" t="n">
-        <v>0.6112</v>
+        <v>0.593</v>
       </c>
       <c r="J457" t="n">
-        <v>17.7248</v>
+        <v>17.197</v>
       </c>
     </row>
     <row r="458">
@@ -20209,10 +20209,10 @@
         <v>1.23</v>
       </c>
       <c r="I458" t="n">
-        <v>0.488</v>
+        <v>0.4803</v>
       </c>
       <c r="J458" t="n">
-        <v>14.152</v>
+        <v>13.9287</v>
       </c>
     </row>
     <row r="459">
@@ -20249,10 +20249,10 @@
         <v>0.95</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.0775</v>
+        <v>-0.0873</v>
       </c>
       <c r="J459" t="n">
-        <v>-2.2475</v>
+        <v>-2.5317</v>
       </c>
     </row>
     <row r="460">
@@ -20289,10 +20289,10 @@
         <v>0.8</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.2409</v>
+        <v>-0.2539</v>
       </c>
       <c r="J460" t="n">
-        <v>-6.9861</v>
+        <v>-7.3631</v>
       </c>
     </row>
     <row r="461">
@@ -20329,10 +20329,10 @@
         <v>0.8</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.2409</v>
+        <v>-0.2539</v>
       </c>
       <c r="J461" t="n">
-        <v>-6.9861</v>
+        <v>-7.3631</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5246/event_5246_evp_summary.xlsx
+++ b/database/event/5246/event_5246_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1</v>
+        <v>7.0073</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0897</v>
+        <v>1.0755</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6079</v>
+        <v>2.5864</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1</v>
+        <v>7.0073</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3275</v>
+        <v>4.1698</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7725</v>
+        <v>2.8375</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7467</v>
+        <v>6.6059</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7467</v>
+        <v>6.6059</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7725</v>
+        <v>2.8375</v>
       </c>
       <c r="K2" t="n">
         <v>401</v>
@@ -529,7 +529,7 @@
         <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5192</v>
+        <v>9.4434</v>
       </c>
       <c r="N2" t="n">
         <v>429</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2691</v>
+        <v>6.0564</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9295</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2296</v>
+        <v>2.1532</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2691</v>
+        <v>6.0564</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9222</v>
+        <v>4.6878</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3469</v>
+        <v>1.3686</v>
       </c>
       <c r="H3" t="n">
-        <v>8.048299999999999</v>
+        <v>7.793</v>
       </c>
       <c r="I3" t="n">
-        <v>8.048299999999999</v>
+        <v>7.793</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3469</v>
+        <v>1.3686</v>
       </c>
       <c r="K3" t="n">
         <v>401</v>
@@ -575,7 +575,7 @@
         <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>9.395199999999999</v>
+        <v>9.1616</v>
       </c>
       <c r="N3" t="n">
         <v>429</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0272</v>
+        <v>4.9003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7716</v>
+        <v>0.7521</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6643</v>
+        <v>1.6265</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0272</v>
+        <v>4.9003</v>
       </c>
       <c r="F4" t="n">
-        <v>5.0272</v>
+        <v>4.9003</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8.2781</v>
+        <v>8.2799</v>
       </c>
       <c r="I4" t="n">
-        <v>8.2781</v>
+        <v>8.2799</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>8.2781</v>
+        <v>8.2799</v>
       </c>
       <c r="N4" t="n">
         <v>457</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.803</v>
+        <v>4.5209</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7372</v>
+        <v>0.6939</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5622</v>
+        <v>1.4537</v>
       </c>
       <c r="E5" t="n">
-        <v>4.803</v>
+        <v>4.5209</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2437</v>
+        <v>4.0016</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5593</v>
+        <v>0.5194</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5633</v>
+        <v>6.2203</v>
       </c>
       <c r="I5" t="n">
-        <v>6.7324</v>
+        <v>6.3865</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5593</v>
+        <v>0.5194</v>
       </c>
       <c r="K5" t="n">
         <v>515</v>
@@ -667,7 +667,7 @@
         <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>7.291700000000001</v>
+        <v>6.9059</v>
       </c>
       <c r="N5" t="n">
         <v>543</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5594</v>
+        <v>4.4443</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6998</v>
+        <v>0.6821</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4513</v>
+        <v>1.4188</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5594</v>
+        <v>4.4443</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5594</v>
+        <v>4.4443</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2542</v>
+        <v>7.2348</v>
       </c>
       <c r="I6" t="n">
-        <v>7.2542</v>
+        <v>7.2348</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.2542</v>
+        <v>7.2348</v>
       </c>
       <c r="N6" t="n">
         <v>457</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4668</v>
+        <v>3.3441</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5321</v>
+        <v>0.5132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.954</v>
+        <v>0.9176</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4668</v>
+        <v>3.3441</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4668</v>
+        <v>3.3441</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8629</v>
+        <v>4.7136</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8629</v>
+        <v>4.7136</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8629</v>
+        <v>4.7136</v>
       </c>
       <c r="N7" t="n">
         <v>457</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3287</v>
+        <v>3.2324</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5109</v>
+        <v>0.4961</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8911</v>
+        <v>0.8667</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3287</v>
+        <v>3.2324</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5863</v>
+        <v>2.4886</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9356</v>
+        <v>2.7531</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9356</v>
+        <v>2.7531</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="K8" t="n">
         <v>401</v>
@@ -805,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="M8" t="n">
-        <v>3.678</v>
+        <v>3.4969</v>
       </c>
       <c r="N8" t="n">
         <v>429</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2829</v>
+        <v>3.2039</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5039</v>
+        <v>0.4917</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8702</v>
+        <v>0.8537</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2829</v>
+        <v>3.2039</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2829</v>
+        <v>3.2039</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4604</v>
+        <v>4.3923</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4604</v>
+        <v>4.3923</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.4604</v>
+        <v>4.3923</v>
       </c>
       <c r="N9" t="n">
         <v>356</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9439</v>
+        <v>2.9122</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4518</v>
+        <v>0.447</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7159</v>
+        <v>0.7209</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9439</v>
+        <v>2.9122</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9439</v>
+        <v>2.9122</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7184</v>
+        <v>3.7237</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7184</v>
+        <v>3.7237</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7184</v>
+        <v>3.7237</v>
       </c>
       <c r="N10" t="n">
         <v>347</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.91</v>
+        <v>2.7926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4466</v>
+        <v>0.4286</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7005</v>
+        <v>0.6664</v>
       </c>
       <c r="E11" t="n">
-        <v>2.91</v>
+        <v>2.7926</v>
       </c>
       <c r="F11" t="n">
-        <v>2.91</v>
+        <v>2.7926</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6442</v>
+        <v>3.4498</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6442</v>
+        <v>3.4498</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6442</v>
+        <v>3.4498</v>
       </c>
       <c r="N11" t="n">
         <v>356</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6826</v>
+        <v>2.5973</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4117</v>
+        <v>0.3986</v>
       </c>
       <c r="D12" t="n">
-        <v>0.597</v>
+        <v>0.5774</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6826</v>
+        <v>2.5973</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6826</v>
+        <v>2.5973</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1465</v>
+        <v>3.002</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1465</v>
+        <v>3.002</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1465</v>
+        <v>3.002</v>
       </c>
       <c r="N12" t="n">
         <v>296</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5779</v>
+        <v>2.5426</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3956</v>
+        <v>0.3902</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5493</v>
+        <v>0.5525</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5779</v>
+        <v>2.5426</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5779</v>
+        <v>2.5426</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9173</v>
+        <v>2.8767</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9173</v>
+        <v>2.8767</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9173</v>
+        <v>2.8767</v>
       </c>
       <c r="N13" t="n">
         <v>347</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5054</v>
+        <v>2.4095</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3845</v>
+        <v>0.3698</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5163</v>
+        <v>0.4919</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5054</v>
+        <v>2.4095</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5054</v>
+        <v>2.4095</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7585</v>
+        <v>2.5718</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7585</v>
+        <v>2.5718</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7585</v>
+        <v>2.5718</v>
       </c>
       <c r="N14" t="n">
         <v>356</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3549</v>
+        <v>2.2869</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3614</v>
+        <v>0.351</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4478</v>
+        <v>0.436</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3549</v>
+        <v>2.2869</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3549</v>
+        <v>1.6678</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.6191</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4293</v>
+        <v>1.6678</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4293</v>
+        <v>1.6678</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6191</v>
       </c>
       <c r="K15" t="n">
-        <v>296</v>
+        <v>401</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4293</v>
+        <v>2.2869</v>
       </c>
       <c r="N15" t="n">
-        <v>296</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.352</v>
+        <v>2.2398</v>
       </c>
       <c r="C16" t="n">
-        <v>0.361</v>
+        <v>0.3438</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4465</v>
+        <v>0.4145</v>
       </c>
       <c r="E16" t="n">
-        <v>2.352</v>
+        <v>2.2398</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1547</v>
+        <v>2.2398</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8027</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1798</v>
+        <v>2.2398</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2875</v>
+        <v>2.2398</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8027</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>515</v>
+        <v>296</v>
       </c>
       <c r="L16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4848</v>
+        <v>2.2398</v>
       </c>
       <c r="N16" t="n">
-        <v>543</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2845</v>
+        <v>2.2191</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3506</v>
+        <v>0.3406</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4157</v>
+        <v>0.4051</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2845</v>
+        <v>2.2191</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6194</v>
+        <v>3.0004</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6651</v>
+        <v>-0.7813</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6194</v>
+        <v>3.9258</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6194</v>
+        <v>4.0307</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6651</v>
+        <v>-0.7813</v>
       </c>
       <c r="K17" t="n">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="L17" t="n">
         <v>28</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2845</v>
+        <v>3.249400000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>429</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1949</v>
+        <v>2.1075</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3369</v>
+        <v>0.3235</v>
       </c>
       <c r="D18" t="n">
-        <v>0.375</v>
+        <v>0.3543</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1949</v>
+        <v>2.1075</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9616</v>
+        <v>2.8511</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7667</v>
+        <v>-0.7436</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7571</v>
+        <v>3.5837</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8539</v>
+        <v>3.6795</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7667</v>
+        <v>-0.7436</v>
       </c>
       <c r="K18" t="n">
         <v>515</v>
@@ -1265,7 +1265,7 @@
         <v>28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0872</v>
+        <v>2.9359</v>
       </c>
       <c r="N18" t="n">
         <v>543</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="C19" t="n">
-        <v>0.316</v>
+        <v>0.2979</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3131</v>
+        <v>0.2783</v>
       </c>
       <c r="E19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="F19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="I19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.059</v>
+        <v>1.9408</v>
       </c>
       <c r="N19" t="n">
         <v>356</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2797</v>
+        <v>0.262</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2054</v>
+        <v>0.172</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>347</v>
+        <v>457</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8224</v>
+        <v>1.7073</v>
       </c>
       <c r="N20" t="n">
-        <v>347</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2728</v>
+        <v>0.2579</v>
       </c>
       <c r="D21" t="n">
-        <v>0.185</v>
+        <v>0.1597</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>457</v>
+        <v>356</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7775</v>
+        <v>1.6804</v>
       </c>
       <c r="N21" t="n">
-        <v>457</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2701</v>
+        <v>0.2458</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1768</v>
+        <v>0.1237</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7597</v>
+        <v>1.6014</v>
       </c>
       <c r="N22" t="n">
         <v>296</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2534</v>
+        <v>0.2335</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1274</v>
+        <v>0.0872</v>
       </c>
       <c r="E23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="F23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="I23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.651</v>
+        <v>1.5212</v>
       </c>
       <c r="N23" t="n">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1764</v>
+        <v>0.1645</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1011</v>
+        <v>-0.1177</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1492</v>
+        <v>1.0715</v>
       </c>
       <c r="N24" t="n">
         <v>296</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1034</v>
+        <v>0.0993</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3174</v>
+        <v>-0.3112</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9426</v>
+        <v>0.9191</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2687</v>
+        <v>-0.2724</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9426</v>
+        <v>0.9191</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9669</v>
+        <v>0.9437</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2687</v>
+        <v>-0.2724</v>
       </c>
       <c r="K25" t="n">
         <v>515</v>
@@ -1587,7 +1587,7 @@
         <v>28</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6981999999999999</v>
+        <v>0.6713</v>
       </c>
       <c r="N25" t="n">
         <v>543</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3419</v>
+        <v>-0.3436</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6201</v>
+        <v>0.5756</v>
       </c>
       <c r="N26" t="n">
         <v>457</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0605</v>
+        <v>0.0471</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4447</v>
+        <v>-0.4661</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3943</v>
+        <v>0.3066</v>
       </c>
       <c r="N27" t="n">
         <v>296</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.1936</v>
+        <v>-1.0069</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1832</v>
+        <v>-0.1545</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1676</v>
+        <v>-1.0645</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1936</v>
+        <v>-1.0069</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.9568</v>
+        <v>-0.7892</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2368</v>
+        <v>-0.2177</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9568</v>
+        <v>-0.7892</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9568</v>
+        <v>-0.7892</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2368</v>
+        <v>-0.2177</v>
       </c>
       <c r="K28" t="n">
         <v>401</v>
@@ -1725,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.1936</v>
+        <v>-1.0069</v>
       </c>
       <c r="N28" t="n">
         <v>429</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4813</v>
+        <v>-1.4581</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2273</v>
+        <v>-0.2238</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2985</v>
+        <v>-1.27</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4813</v>
+        <v>-1.4581</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.1268</v>
+        <v>-1.1349</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3545</v>
+        <v>-0.3232</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.1268</v>
+        <v>-1.1349</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.1558</v>
+        <v>-1.1652</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3545</v>
+        <v>-0.3232</v>
       </c>
       <c r="K29" t="n">
         <v>515</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.5103</v>
+        <v>-1.4884</v>
       </c>
       <c r="N29" t="n">
         <v>543</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3526</v>
+        <v>-0.3572</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.67</v>
+        <v>-1.6659</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.2974</v>
+        <v>-2.3272</v>
       </c>
       <c r="N30" t="n">
         <v>347</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3834</v>
+        <v>-0.3682</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.7615</v>
+        <v>-1.6986</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.4983</v>
+        <v>-2.3988</v>
       </c>
       <c r="N31" t="n">
         <v>347</v>
@@ -1969,10 +1969,10 @@
         <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4591</v>
+        <v>1.4943</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4591</v>
+        <v>1.4943</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8407</v>
+        <v>0.8214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8407</v>
+        <v>0.8214</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0936</v>
+        <v>0.073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0936</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0156</v>
+        <v>0.0055</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0156</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1076</v>
+        <v>-0.0927</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1076</v>
+        <v>-0.0927</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.79</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2386</v>
+        <v>-0.223</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2386</v>
+        <v>-0.223</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3303</v>
+        <v>-0.3154</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3303</v>
+        <v>-0.3154</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3393</v>
+        <v>-0.3247</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3393</v>
+        <v>-0.3247</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.64</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3753</v>
+        <v>-0.3624</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3753</v>
+        <v>-0.3624</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3313</v>
+        <v>1.3631</v>
       </c>
       <c r="J12" t="n">
-        <v>35.9451</v>
+        <v>36.8037</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3134</v>
+        <v>1.3432</v>
       </c>
       <c r="J13" t="n">
-        <v>35.4618</v>
+        <v>36.2664</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0466</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6956</v>
+        <v>1.2582</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.99</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0983</v>
+        <v>-0.0776</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.6541</v>
+        <v>-2.0952</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3304</v>
+        <v>-0.2907</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.9208</v>
+        <v>-7.8489</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6669</v>
+        <v>0.6157</v>
       </c>
       <c r="J17" t="n">
-        <v>18.0063</v>
+        <v>16.6239</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0616</v>
+        <v>0.043</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6632</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1159</v>
+        <v>-0.1002</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1293</v>
+        <v>-2.7054</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4274</v>
+        <v>-0.4189</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.5398</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4274</v>
+        <v>-0.4189</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.5398</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.078</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>0.83</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2056</v>
+        <v>-0.1885</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.3456</v>
+        <v>-4.901</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>0.77</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2627</v>
+        <v>-0.2451</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.8302</v>
+        <v>-6.3726</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3002</v>
+        <v>-0.2831</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.8052</v>
+        <v>-7.3606</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.328</v>
+        <v>-0.3119</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.528</v>
+        <v>-8.109400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8969</v>
+        <v>0.8819</v>
       </c>
       <c r="J27" t="n">
-        <v>23.3194</v>
+        <v>22.9294</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8969</v>
+        <v>0.8819</v>
       </c>
       <c r="J28" t="n">
-        <v>23.3194</v>
+        <v>22.9294</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8778</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>22.8228</v>
+        <v>22.3964</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>1.19</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5148</v>
+        <v>0.4834</v>
       </c>
       <c r="J30" t="n">
-        <v>13.3848</v>
+        <v>12.5684</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>1.03</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0922</v>
+        <v>0.0716</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3972</v>
+        <v>1.8616</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7381</v>
+        <v>0.6837</v>
       </c>
       <c r="J32" t="n">
-        <v>22.143</v>
+        <v>20.511</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5512</v>
+        <v>0.492</v>
       </c>
       <c r="J33" t="n">
-        <v>16.536</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0856</v>
+        <v>-0.0701</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.568</v>
+        <v>-2.103</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.77</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2812</v>
+        <v>-0.2624</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.436</v>
+        <v>-7.872</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4454</v>
+        <v>-0.4401</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.362</v>
+        <v>-13.203</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1307</v>
+        <v>1.1437</v>
       </c>
       <c r="J37" t="n">
-        <v>33.921</v>
+        <v>34.311</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.28</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7232</v>
+        <v>0.6924</v>
       </c>
       <c r="J38" t="n">
-        <v>21.696</v>
+        <v>20.772</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0358</v>
+        <v>0.0256</v>
       </c>
       <c r="J39" t="n">
-        <v>1.074</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.024</v>
+        <v>-0.0186</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.72</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2874</v>
+        <v>-0.2473</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.622</v>
+        <v>-7.419</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9707</v>
+        <v>0.9634</v>
       </c>
       <c r="J42" t="n">
-        <v>29.121</v>
+        <v>28.902</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4781</v>
+        <v>0.4367</v>
       </c>
       <c r="J43" t="n">
-        <v>14.343</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>0.98</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1091</v>
+        <v>-0.0834</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.273</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.211</v>
+        <v>-0.1747</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.33</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5762</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.286</v>
+        <v>-16.104</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8848</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>26.544</v>
+        <v>25.176</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.16</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3645</v>
+        <v>0.3099</v>
       </c>
       <c r="J48" t="n">
-        <v>10.935</v>
+        <v>9.297000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.01</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0435</v>
+        <v>0.0294</v>
       </c>
       <c r="J49" t="n">
-        <v>1.305</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3475</v>
+        <v>-0.3327</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.425</v>
+        <v>-9.981</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.63</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4106</v>
+        <v>-0.4015</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.318</v>
+        <v>-12.045</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.51</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1124</v>
+        <v>1.1243</v>
       </c>
       <c r="J52" t="n">
-        <v>31.1472</v>
+        <v>31.4804</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6877</v>
+        <v>0.6587</v>
       </c>
       <c r="J53" t="n">
-        <v>19.2556</v>
+        <v>18.4436</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4987</v>
+        <v>0.4653</v>
       </c>
       <c r="J54" t="n">
-        <v>13.9636</v>
+        <v>13.0284</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.406</v>
+        <v>0.3724</v>
       </c>
       <c r="J55" t="n">
-        <v>11.368</v>
+        <v>10.4272</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.03</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0997</v>
+        <v>0.0793</v>
       </c>
       <c r="J56" t="n">
-        <v>2.7916</v>
+        <v>2.2204</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2702</v>
+        <v>0.2222</v>
       </c>
       <c r="J57" t="n">
-        <v>7.5656</v>
+        <v>6.2216</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0809</v>
+        <v>-0.0674</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2652</v>
+        <v>-1.8872</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.9708</v>
+        <v>-2.5284</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1514</v>
+        <v>-0.1328</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.2392</v>
+        <v>-3.7184</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3214</v>
+        <v>-0.3045</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.9992</v>
+        <v>-8.526</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5128</v>
+        <v>1.5465</v>
       </c>
       <c r="J62" t="n">
-        <v>30.256</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2044</v>
+        <v>1.2265</v>
       </c>
       <c r="J63" t="n">
-        <v>24.088</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.59</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1686</v>
+        <v>1.1901</v>
       </c>
       <c r="J64" t="n">
-        <v>23.372</v>
+        <v>23.802</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.45</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9901</v>
       </c>
       <c r="J65" t="n">
-        <v>19.628</v>
+        <v>19.802</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>1.44</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9649</v>
+        <v>0.9714</v>
       </c>
       <c r="J66" t="n">
-        <v>19.298</v>
+        <v>19.428</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5152</v>
+        <v>0.5223</v>
       </c>
       <c r="J67" t="n">
-        <v>10.304</v>
+        <v>10.446</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>0.74</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.257</v>
+        <v>-0.2429</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.14</v>
+        <v>-4.858</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.41</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5558</v>
+        <v>-0.5605</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.116</v>
+        <v>-11.21</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.33</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6269</v>
+        <v>-0.6424</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.538</v>
+        <v>-12.848</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6802</v>
+        <v>-0.7058</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.604</v>
+        <v>-14.116</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.38</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9109</v>
+        <v>0.895</v>
       </c>
       <c r="J72" t="n">
-        <v>27.327</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7468</v>
       </c>
       <c r="J73" t="n">
-        <v>23.181</v>
+        <v>22.404</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.28</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7119</v>
+        <v>0.6828</v>
       </c>
       <c r="J74" t="n">
-        <v>21.357</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>1.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3608</v>
+        <v>0.327</v>
       </c>
       <c r="J75" t="n">
-        <v>10.824</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.92</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3259</v>
+        <v>-0.2857</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.776999999999999</v>
+        <v>-8.571</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.052</v>
+        <v>0.035</v>
       </c>
       <c r="J77" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="J78" t="n">
-        <v>0.234</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.92</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1188</v>
+        <v>-0.1017</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.564</v>
+        <v>-3.051</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1639</v>
+        <v>-0.1444</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.917</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1639</v>
+        <v>-0.1444</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.917</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.65</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8239</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>24.717</v>
+        <v>26.688</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.22</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3426</v>
+        <v>0.3363</v>
       </c>
       <c r="J83" t="n">
-        <v>10.278</v>
+        <v>10.089</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2665</v>
+        <v>0.2561</v>
       </c>
       <c r="J84" t="n">
-        <v>7.995</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="J85" t="n">
-        <v>1.911</v>
+        <v>1.617</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2954</v>
+        <v>-0.2787</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.862</v>
+        <v>-8.361000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4426</v>
+        <v>0.3773</v>
       </c>
       <c r="J87" t="n">
-        <v>13.278</v>
+        <v>11.319</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.29</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4309</v>
+        <v>0.3661</v>
       </c>
       <c r="J88" t="n">
-        <v>12.927</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1475</v>
+        <v>-0.1278</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.425</v>
+        <v>-3.834</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1807</v>
+        <v>-0.1602</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.421</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3755</v>
+        <v>-0.3631</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.265</v>
+        <v>-10.893</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6402</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>18.5658</v>
+        <v>17.4957</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3824</v>
+        <v>0.3412</v>
       </c>
       <c r="J93" t="n">
-        <v>11.0896</v>
+        <v>9.8948</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3824</v>
+        <v>0.3412</v>
       </c>
       <c r="J94" t="n">
-        <v>11.0896</v>
+        <v>9.8948</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.325</v>
+        <v>-0.283</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.425000000000001</v>
+        <v>-8.207000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.87</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4295</v>
+        <v>-0.3864</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.4555</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.21</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4507</v>
+        <v>0.3927</v>
       </c>
       <c r="J97" t="n">
-        <v>13.0703</v>
+        <v>11.3883</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.12</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2909</v>
+        <v>0.2411</v>
       </c>
       <c r="J98" t="n">
-        <v>8.4361</v>
+        <v>6.9919</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1479</v>
+        <v>0.1138</v>
       </c>
       <c r="J99" t="n">
-        <v>4.2891</v>
+        <v>3.3002</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1.04</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1246</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>3.6134</v>
+        <v>2.7318</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4546</v>
+        <v>-0.4504</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.1834</v>
+        <v>-13.0616</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.35</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8742</v>
+        <v>0.8537</v>
       </c>
       <c r="J102" t="n">
-        <v>35.8422</v>
+        <v>35.0017</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8336</v>
+        <v>0.8098</v>
       </c>
       <c r="J103" t="n">
-        <v>34.1776</v>
+        <v>33.2018</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2968</v>
+        <v>0.2617</v>
       </c>
       <c r="J104" t="n">
-        <v>12.1688</v>
+        <v>10.7297</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1837</v>
+        <v>0.1556</v>
       </c>
       <c r="J105" t="n">
-        <v>7.5317</v>
+        <v>6.3796</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.76</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7009</v>
+        <v>-0.67</v>
       </c>
       <c r="J106" t="n">
-        <v>-28.7369</v>
+        <v>-27.47</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3645</v>
+        <v>0.3099</v>
       </c>
       <c r="J107" t="n">
-        <v>14.9445</v>
+        <v>12.7059</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1249</v>
+        <v>0.0944</v>
       </c>
       <c r="J108" t="n">
-        <v>5.1209</v>
+        <v>3.8704</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0426</v>
+        <v>-0.0324</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.7466</v>
+        <v>-1.3284</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.9684</v>
+        <v>-2.3821</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2013</v>
+        <v>-0.1807</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.253299999999999</v>
+        <v>-7.4087</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>0.98</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0104</v>
+        <v>0.0304</v>
       </c>
       <c r="J112" t="n">
-        <v>0.208</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.143</v>
+        <v>-0.1265</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.86</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>0.7</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3163</v>
+        <v>-0.3032</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.326</v>
+        <v>-6.064</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.47</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5182</v>
+        <v>-0.5187</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.364</v>
+        <v>-10.374</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.4</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5792</v>
+        <v>-0.5883</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.584</v>
+        <v>-11.766</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4641</v>
+        <v>1.4939</v>
       </c>
       <c r="J117" t="n">
-        <v>29.282</v>
+        <v>29.878</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.64</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2347</v>
+        <v>1.2551</v>
       </c>
       <c r="J118" t="n">
-        <v>24.694</v>
+        <v>25.102</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9207</v>
+        <v>0.9198</v>
       </c>
       <c r="J119" t="n">
-        <v>18.414</v>
+        <v>18.396</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>1.39</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8839</v>
+        <v>0.8796</v>
       </c>
       <c r="J120" t="n">
-        <v>17.678</v>
+        <v>17.592</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>1.37</v>
       </c>
       <c r="I121" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8389</v>
       </c>
       <c r="J121" t="n">
-        <v>16.926</v>
+        <v>16.778</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7036</v>
+        <v>0.6318</v>
       </c>
       <c r="J122" t="n">
-        <v>14.7756</v>
+        <v>13.2678</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.41</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5165</v>
+        <v>0.4503</v>
       </c>
       <c r="J123" t="n">
-        <v>10.8465</v>
+        <v>9.456300000000001</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.4</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5063</v>
+        <v>0.4407</v>
       </c>
       <c r="J124" t="n">
-        <v>10.6323</v>
+        <v>9.2547</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.21</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3008</v>
+        <v>0.2508</v>
       </c>
       <c r="J125" t="n">
-        <v>6.3168</v>
+        <v>5.2668</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>1.09</v>
       </c>
       <c r="I126" t="n">
-        <v>0.143</v>
+        <v>0.1108</v>
       </c>
       <c r="J126" t="n">
-        <v>3.003</v>
+        <v>2.3268</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>0.88</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1436</v>
+        <v>-0.1281</v>
       </c>
       <c r="J127" t="n">
-        <v>-3.0156</v>
+        <v>-2.6901</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2389</v>
+        <v>-0.2232</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.0169</v>
+        <v>-4.6872</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2486</v>
+        <v>-0.2329</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.2206</v>
+        <v>-4.8909</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2675</v>
+        <v>-0.2518</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.6175</v>
+        <v>-5.2878</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.51</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4907</v>
+        <v>-0.4881</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.3047</v>
+        <v>-10.2501</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.18</v>
       </c>
       <c r="I132" t="n">
-        <v>0.409</v>
+        <v>0.3526</v>
       </c>
       <c r="J132" t="n">
-        <v>11.452</v>
+        <v>9.8728</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0043</v>
+        <v>0.0023</v>
       </c>
       <c r="J133" t="n">
-        <v>0.1204</v>
+        <v>0.0644</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.97</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.5708</v>
+        <v>-1.2488</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.0352</v>
+        <v>-2.562</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.72</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3255</v>
+        <v>-0.3089</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.114000000000001</v>
+        <v>-8.6492</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9629</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>26.9612</v>
+        <v>26.6868</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5962</v>
+        <v>0.5602</v>
       </c>
       <c r="J138" t="n">
-        <v>16.6936</v>
+        <v>15.6856</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J139" t="n">
-        <v>7.4424</v>
+        <v>6.5324</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1139</v>
+        <v>0.0927</v>
       </c>
       <c r="J140" t="n">
-        <v>3.1892</v>
+        <v>2.5956</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0834</v>
+        <v>-0.0626</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.3352</v>
+        <v>-1.7528</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4381</v>
+        <v>0.3805</v>
       </c>
       <c r="J142" t="n">
-        <v>12.2668</v>
+        <v>10.654</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.14</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3318</v>
+        <v>0.279</v>
       </c>
       <c r="J143" t="n">
-        <v>9.2904</v>
+        <v>7.812</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0016</v>
+        <v>0.0007</v>
       </c>
       <c r="J144" t="n">
-        <v>0.0448</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.87</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1786</v>
+        <v>-0.1582</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.0008</v>
+        <v>-4.4296</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3461</v>
+        <v>-0.331</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.690799999999999</v>
+        <v>-9.268000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.52</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1583</v>
+        <v>1.1737</v>
       </c>
       <c r="J147" t="n">
-        <v>32.4324</v>
+        <v>32.8636</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.17</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4935</v>
+        <v>0.4536</v>
       </c>
       <c r="J148" t="n">
-        <v>13.818</v>
+        <v>12.7008</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.04</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1556</v>
+        <v>0.1294</v>
       </c>
       <c r="J149" t="n">
-        <v>4.3568</v>
+        <v>3.6232</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0859</v>
+        <v>0.068</v>
       </c>
       <c r="J150" t="n">
-        <v>2.4052</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.73</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7631</v>
+        <v>-0.7366</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.3668</v>
+        <v>-20.6248</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>0.77</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2442</v>
+        <v>-0.2301</v>
       </c>
       <c r="J152" t="n">
-        <v>-5.1282</v>
+        <v>-4.8321</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2543</v>
+        <v>-0.2406</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.3403</v>
+        <v>-5.0526</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.61</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3909</v>
+        <v>-0.3807</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.2089</v>
+        <v>-7.9947</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3996</v>
+        <v>-0.3898</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.3916</v>
+        <v>-8.1858</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.52</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.47</v>
+        <v>-0.4651</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.767099999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.87</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5111</v>
+        <v>1.5438</v>
       </c>
       <c r="J157" t="n">
-        <v>31.7331</v>
+        <v>32.4198</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.85</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4875</v>
+        <v>1.5187</v>
       </c>
       <c r="J158" t="n">
-        <v>31.2375</v>
+        <v>31.8927</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.79</v>
       </c>
       <c r="I159" t="n">
-        <v>1.4162</v>
+        <v>1.4434</v>
       </c>
       <c r="J159" t="n">
-        <v>29.7402</v>
+        <v>30.3114</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.431</v>
+        <v>0.3992</v>
       </c>
       <c r="J160" t="n">
-        <v>9.051</v>
+        <v>8.3832</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2216</v>
+        <v>-0.1983</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.6536</v>
+        <v>-4.1643</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.21</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3487</v>
+        <v>0.3404</v>
       </c>
       <c r="J162" t="n">
-        <v>10.461</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.12</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2244</v>
+        <v>0.2087</v>
       </c>
       <c r="J163" t="n">
-        <v>6.732</v>
+        <v>6.261</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1946</v>
+        <v>0.1782</v>
       </c>
       <c r="J164" t="n">
-        <v>5.838</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.027</v>
+        <v>-2.511</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3031</v>
+        <v>-0.2855</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.093</v>
+        <v>-8.565</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4047</v>
+        <v>0.341</v>
       </c>
       <c r="J167" t="n">
-        <v>12.141</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2328</v>
+        <v>0.1854</v>
       </c>
       <c r="J168" t="n">
-        <v>6.984</v>
+        <v>5.562</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2328</v>
+        <v>0.1854</v>
       </c>
       <c r="J169" t="n">
-        <v>6.984</v>
+        <v>5.562</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0649</v>
+        <v>-0.051</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.947</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.91</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1429</v>
+        <v>-0.1232</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.287</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.67</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3289</v>
+        <v>1.3509</v>
       </c>
       <c r="J172" t="n">
-        <v>38.5381</v>
+        <v>39.1761</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7305</v>
+        <v>0.7027</v>
       </c>
       <c r="J173" t="n">
-        <v>21.1845</v>
+        <v>20.3783</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5535</v>
       </c>
       <c r="J174" t="n">
-        <v>16.9998</v>
+        <v>16.0515</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.03</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1021</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>2.9609</v>
+        <v>2.3693</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5093</v>
+        <v>-0.4704</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.7697</v>
+        <v>-13.6416</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3498</v>
+        <v>0.2994</v>
       </c>
       <c r="J177" t="n">
-        <v>10.1442</v>
+        <v>8.682600000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0106</v>
+        <v>-0.0063</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.3074</v>
+        <v>-0.1827</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.73</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3051</v>
+        <v>-0.2876</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.847899999999999</v>
+        <v>-8.340400000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3051</v>
+        <v>-0.2876</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.847899999999999</v>
+        <v>-8.340400000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3605</v>
+        <v>-0.346</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.4545</v>
+        <v>-10.034</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0892</v>
+        <v>1.0995</v>
       </c>
       <c r="J182" t="n">
-        <v>26.1408</v>
+        <v>26.388</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.456</v>
+        <v>0.4216</v>
       </c>
       <c r="J183" t="n">
-        <v>10.944</v>
+        <v>10.1184</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.15</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4327</v>
+        <v>0.3984</v>
       </c>
       <c r="J184" t="n">
-        <v>10.3848</v>
+        <v>9.5616</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>1.12</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3602</v>
+        <v>0.3265</v>
       </c>
       <c r="J185" t="n">
-        <v>8.6448</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>1.11</v>
       </c>
       <c r="I186" t="n">
-        <v>0.335</v>
+        <v>0.3018</v>
       </c>
       <c r="J186" t="n">
-        <v>8.039999999999999</v>
+        <v>7.2432</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.11</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3083</v>
+        <v>0.2596</v>
       </c>
       <c r="J187" t="n">
-        <v>7.3992</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0699</v>
+        <v>0.0506</v>
       </c>
       <c r="J188" t="n">
-        <v>1.6776</v>
+        <v>1.2144</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>0.74</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2963</v>
+        <v>-0.2784</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.1112</v>
+        <v>-6.6816</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.72</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3151</v>
+        <v>-0.2979</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.5624</v>
+        <v>-7.1496</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3336</v>
+        <v>-0.3174</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.006399999999999</v>
+        <v>-7.6176</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.38</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7506</v>
+        <v>0.7016</v>
       </c>
       <c r="J192" t="n">
-        <v>21.0168</v>
+        <v>19.6448</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>1.02</v>
       </c>
       <c r="I193" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="J193" t="n">
-        <v>2.422</v>
+        <v>1.7388</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.76</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2836</v>
+        <v>-0.2648</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.9408</v>
+        <v>-7.4144</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3027</v>
+        <v>-0.2847</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.4756</v>
+        <v>-7.9716</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3492</v>
+        <v>-0.334</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.7776</v>
+        <v>-9.352</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.31</v>
       </c>
       <c r="I197" t="n">
-        <v>0.79</v>
+        <v>0.763</v>
       </c>
       <c r="J197" t="n">
-        <v>22.12</v>
+        <v>21.364</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5997</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>16.7916</v>
+        <v>15.764</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5557</v>
+        <v>0.5179</v>
       </c>
       <c r="J199" t="n">
-        <v>15.5596</v>
+        <v>14.5012</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>0.99</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.0801</v>
+        <v>-0.0595</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.2428</v>
+        <v>-1.666</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3397</v>
+        <v>-0.2978</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.5116</v>
+        <v>-8.3384</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1</v>
+        <v>-0.0858</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.3</v>
+        <v>-1.9734</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2318</v>
+        <v>-0.2154</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.3314</v>
+        <v>-4.9542</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>0.79</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2414</v>
+        <v>-0.225</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.5522</v>
+        <v>-5.175</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2601</v>
+        <v>-0.2436</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.9823</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4496</v>
+        <v>-0.4426</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.3408</v>
+        <v>-10.1798</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1218</v>
+        <v>1.135</v>
       </c>
       <c r="J207" t="n">
-        <v>25.8014</v>
+        <v>26.105</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.43</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9777</v>
+        <v>0.9745</v>
       </c>
       <c r="J208" t="n">
-        <v>22.4871</v>
+        <v>22.4135</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>1.34</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7952</v>
       </c>
       <c r="J209" t="n">
-        <v>18.699</v>
+        <v>18.2896</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>1.23</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5942</v>
+        <v>0.5667</v>
       </c>
       <c r="J210" t="n">
-        <v>13.6666</v>
+        <v>13.0341</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>1.08</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2366</v>
+        <v>0.2063</v>
       </c>
       <c r="J211" t="n">
-        <v>5.4418</v>
+        <v>4.7449</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>1.06</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1996</v>
+        <v>0.1958</v>
       </c>
       <c r="J212" t="n">
-        <v>4.7904</v>
+        <v>4.6992</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.78</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2456</v>
+        <v>-0.2306</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.8944</v>
+        <v>-5.5344</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.77</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2554</v>
+        <v>-0.2405</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.1296</v>
+        <v>-5.772</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.435</v>
+        <v>-0.4265</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.44</v>
+        <v>-10.236</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.42</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5736</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.584</v>
+        <v>-13.7664</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9375</v>
+        <v>0.8703</v>
       </c>
       <c r="J217" t="n">
-        <v>22.5</v>
+        <v>20.8872</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.43</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5334</v>
+        <v>0.4673</v>
       </c>
       <c r="J218" t="n">
-        <v>12.8016</v>
+        <v>11.2152</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.38</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4838</v>
+        <v>0.4206</v>
       </c>
       <c r="J219" t="n">
-        <v>11.6112</v>
+        <v>10.0944</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.3</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4002</v>
+        <v>0.3427</v>
       </c>
       <c r="J220" t="n">
-        <v>9.604799999999999</v>
+        <v>8.2248</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1148</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.7552</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.5</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1367</v>
+        <v>1.1518</v>
       </c>
       <c r="J222" t="n">
-        <v>34.101</v>
+        <v>34.554</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>1.24</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6556</v>
+        <v>0.6197</v>
       </c>
       <c r="J223" t="n">
-        <v>19.668</v>
+        <v>18.591</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>1</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0111</v>
+        <v>-0.0073</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.333</v>
+        <v>-0.219</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5159</v>
       </c>
       <c r="J225" t="n">
-        <v>-16.677</v>
+        <v>-15.477</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5793</v>
+        <v>-0.5403</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.379</v>
+        <v>-16.209</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3047</v>
+        <v>0.2542</v>
       </c>
       <c r="J227" t="n">
-        <v>9.141</v>
+        <v>7.626</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.11</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2673</v>
+        <v>0.2199</v>
       </c>
       <c r="J228" t="n">
-        <v>8.019</v>
+        <v>6.597</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.1</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2481</v>
+        <v>0.2025</v>
       </c>
       <c r="J229" t="n">
-        <v>7.443</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>1.09</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2285</v>
+        <v>0.1849</v>
       </c>
       <c r="J230" t="n">
-        <v>6.855</v>
+        <v>5.547</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3499</v>
+        <v>-0.3355</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.497</v>
+        <v>-10.065</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.54</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1655</v>
+        <v>1.1795</v>
       </c>
       <c r="J232" t="n">
-        <v>33.7995</v>
+        <v>34.2055</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>1.18</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5044</v>
+        <v>0.4685</v>
       </c>
       <c r="J233" t="n">
-        <v>14.6276</v>
+        <v>13.5865</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3654</v>
+        <v>0.3305</v>
       </c>
       <c r="J234" t="n">
-        <v>10.5966</v>
+        <v>9.5845</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>1.02</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0725</v>
+        <v>0.0562</v>
       </c>
       <c r="J235" t="n">
-        <v>2.1025</v>
+        <v>1.6298</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0286</v>
+        <v>-0.0231</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.8294</v>
+        <v>-0.6699000000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>1.08</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2317</v>
+        <v>0.1871</v>
       </c>
       <c r="J237" t="n">
-        <v>6.7193</v>
+        <v>5.4259</v>
       </c>
     </row>
     <row r="238">
@@ -11409,10 +11409,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0577</v>
+        <v>0.0396</v>
       </c>
       <c r="J238" t="n">
-        <v>1.6733</v>
+        <v>1.1484</v>
       </c>
     </row>
     <row r="239">
@@ -11449,10 +11449,10 @@
         <v>0.88</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1615</v>
+        <v>-0.1427</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.6835</v>
+        <v>-4.1383</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>0.79</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2536</v>
+        <v>-0.234</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.3544</v>
+        <v>-6.786</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.6357</v>
+        <v>-7.0731</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4259</v>
+        <v>0.369</v>
       </c>
       <c r="J242" t="n">
-        <v>11.9252</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.06</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1766</v>
+        <v>0.138</v>
       </c>
       <c r="J243" t="n">
-        <v>4.9448</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.05</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1541</v>
+        <v>0.1185</v>
       </c>
       <c r="J244" t="n">
-        <v>4.3148</v>
+        <v>3.318</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.78</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2686</v>
+        <v>-0.2491</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.5208</v>
+        <v>-6.9748</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3163</v>
+        <v>-0.2992</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.856400000000001</v>
+        <v>-8.377599999999999</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.44</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0235</v>
+        <v>1.0245</v>
       </c>
       <c r="J247" t="n">
-        <v>28.658</v>
+        <v>28.686</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5482</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>15.3496</v>
+        <v>14.3528</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4602</v>
+        <v>0.4242</v>
       </c>
       <c r="J249" t="n">
-        <v>12.8856</v>
+        <v>11.8776</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.14</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4139</v>
+        <v>0.3782</v>
       </c>
       <c r="J250" t="n">
-        <v>11.5892</v>
+        <v>10.5896</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.92</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3205</v>
+        <v>-0.2798</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.974</v>
+        <v>-7.8344</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.09</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2387</v>
+        <v>0.1931</v>
       </c>
       <c r="J252" t="n">
-        <v>7.161</v>
+        <v>5.793</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.153</v>
+        <v>0.1176</v>
       </c>
       <c r="J253" t="n">
-        <v>4.59</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0776</v>
+        <v>0.0551</v>
       </c>
       <c r="J254" t="n">
-        <v>2.328</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0565</v>
+        <v>-0.0448</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.695</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3355</v>
+        <v>-0.3196</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.065</v>
+        <v>-9.587999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.49</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1149</v>
+        <v>1.1282</v>
       </c>
       <c r="J257" t="n">
-        <v>33.447</v>
+        <v>33.846</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.21</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5451</v>
       </c>
       <c r="J258" t="n">
-        <v>17.496</v>
+        <v>16.353</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.5384</v>
+        <v>0.4992</v>
       </c>
       <c r="J259" t="n">
-        <v>16.152</v>
+        <v>14.976</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.87</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4394</v>
+        <v>-0.3968</v>
       </c>
       <c r="J260" t="n">
-        <v>-13.182</v>
+        <v>-11.904</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.742</v>
+        <v>-0.7139</v>
       </c>
       <c r="J261" t="n">
-        <v>-22.26</v>
+        <v>-21.417</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>1.86</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5223</v>
+        <v>1.5555</v>
       </c>
       <c r="J262" t="n">
-        <v>30.446</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>1.75</v>
       </c>
       <c r="I263" t="n">
-        <v>1.3882</v>
+        <v>1.4124</v>
       </c>
       <c r="J263" t="n">
-        <v>27.764</v>
+        <v>28.248</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>1.39</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8985</v>
+        <v>0.8902</v>
       </c>
       <c r="J264" t="n">
-        <v>17.97</v>
+        <v>17.804</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>1.07</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1957</v>
+        <v>0.1654</v>
       </c>
       <c r="J265" t="n">
-        <v>3.914</v>
+        <v>3.308</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.95</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.27</v>
+        <v>-0.2382</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.4</v>
+        <v>-4.764</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>0.89</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1269</v>
+        <v>-0.1113</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.538</v>
+        <v>-2.226</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1941</v>
+        <v>-0.1787</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.882</v>
+        <v>-3.574</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2253</v>
+        <v>-0.2102</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.506</v>
+        <v>-4.204</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>0.64</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3724</v>
+        <v>-0.3597</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.448</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.43</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5571</v>
+        <v>-0.5633</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.142</v>
+        <v>-11.266</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4869</v>
+        <v>0.5212</v>
       </c>
       <c r="J272" t="n">
-        <v>10.7118</v>
+        <v>11.4664</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.87</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1494</v>
+        <v>-0.1336</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.2868</v>
+        <v>-2.9392</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.73</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2922</v>
+        <v>-0.2778</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.4284</v>
+        <v>-6.1116</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.47</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.522</v>
+        <v>-0.5231</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.484</v>
+        <v>-11.5082</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.26</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7022</v>
+        <v>-0.7349</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.4484</v>
+        <v>-16.1678</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.69</v>
       </c>
       <c r="I277" t="n">
-        <v>0.78</v>
+        <v>0.7086</v>
       </c>
       <c r="J277" t="n">
-        <v>17.16</v>
+        <v>15.5892</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.64</v>
       </c>
       <c r="I278" t="n">
-        <v>0.7335</v>
+        <v>0.6622</v>
       </c>
       <c r="J278" t="n">
-        <v>16.137</v>
+        <v>14.5684</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.46</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5613</v>
+        <v>0.4944</v>
       </c>
       <c r="J279" t="n">
-        <v>12.3486</v>
+        <v>10.8768</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2461</v>
+        <v>0.2017</v>
       </c>
       <c r="J280" t="n">
-        <v>5.4142</v>
+        <v>4.4374</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1225</v>
+        <v>0.0926</v>
       </c>
       <c r="J281" t="n">
-        <v>2.695</v>
+        <v>2.0372</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.57</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1802</v>
+        <v>1.1945</v>
       </c>
       <c r="J282" t="n">
-        <v>28.3248</v>
+        <v>28.668</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9994</v>
+        <v>0.9983</v>
       </c>
       <c r="J283" t="n">
-        <v>23.9856</v>
+        <v>23.9592</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.23</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5987</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J284" t="n">
-        <v>14.3688</v>
+        <v>13.6824</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>1.12</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3468</v>
+        <v>0.3146</v>
       </c>
       <c r="J285" t="n">
-        <v>8.3232</v>
+        <v>7.5504</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.269</v>
+        <v>0.238</v>
       </c>
       <c r="J286" t="n">
-        <v>6.456</v>
+        <v>5.712</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>0.739</v>
+        <v>0.6976</v>
       </c>
       <c r="J287" t="n">
-        <v>17.736</v>
+        <v>16.7424</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3038</v>
+        <v>-0.2864</v>
       </c>
       <c r="J288" t="n">
-        <v>-7.2912</v>
+        <v>-6.8736</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.72</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3132</v>
+        <v>-0.2961</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.5168</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.72</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3132</v>
+        <v>-0.2961</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.5168</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3592</v>
+        <v>-0.3446</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.620799999999999</v>
+        <v>-8.2704</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.38</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9641</v>
+        <v>0.957</v>
       </c>
       <c r="J292" t="n">
-        <v>28.923</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2547</v>
+        <v>0.2173</v>
       </c>
       <c r="J293" t="n">
-        <v>7.641</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1394</v>
+        <v>-0.1104</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.182</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.97</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1394</v>
+        <v>-0.1104</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.182</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7492</v>
+        <v>-0.7201</v>
       </c>
       <c r="J296" t="n">
-        <v>-22.476</v>
+        <v>-21.603</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.28</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5476</v>
+        <v>0.4879</v>
       </c>
       <c r="J297" t="n">
-        <v>16.428</v>
+        <v>14.637</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4185</v>
+        <v>0.3621</v>
       </c>
       <c r="J298" t="n">
-        <v>12.555</v>
+        <v>10.863</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="J299" t="n">
-        <v>2.784</v>
+        <v>2.106</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.01</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0358</v>
+        <v>0.025</v>
       </c>
       <c r="J300" t="n">
-        <v>1.074</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.85</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.208</v>
+        <v>-0.1874</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.24</v>
+        <v>-5.622</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.8</v>
       </c>
       <c r="I302" t="n">
-        <v>1.497</v>
+        <v>1.5324</v>
       </c>
       <c r="J302" t="n">
-        <v>38.922</v>
+        <v>39.8424</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.3</v>
       </c>
       <c r="I303" t="n">
-        <v>0.7511</v>
+        <v>0.7242</v>
       </c>
       <c r="J303" t="n">
-        <v>19.5286</v>
+        <v>18.8292</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3843</v>
+        <v>0.3504</v>
       </c>
       <c r="J304" t="n">
-        <v>9.9918</v>
+        <v>9.1104</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>1.05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1678</v>
+        <v>0.1417</v>
       </c>
       <c r="J305" t="n">
-        <v>4.3628</v>
+        <v>3.6842</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.77</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6948</v>
+        <v>-0.6659</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.0648</v>
+        <v>-17.3134</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.17</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4089</v>
+        <v>0.3542</v>
       </c>
       <c r="J307" t="n">
-        <v>10.6314</v>
+        <v>9.209199999999999</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1046</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J308" t="n">
-        <v>-2.7196</v>
+        <v>-2.3244</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>0.91</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1282</v>
+        <v>-0.1114</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.3332</v>
+        <v>-2.8964</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1714</v>
+        <v>-0.1525</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.4564</v>
+        <v>-3.965</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>0.61</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4193</v>
+        <v>-0.4101</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.9018</v>
+        <v>-10.6626</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.52</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6438</v>
+        <v>0.572</v>
       </c>
       <c r="J312" t="n">
-        <v>16.7388</v>
+        <v>14.872</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.43</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5515</v>
+        <v>0.4816</v>
       </c>
       <c r="J313" t="n">
-        <v>14.339</v>
+        <v>12.5216</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.36</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4774</v>
+        <v>0.4107</v>
       </c>
       <c r="J314" t="n">
-        <v>12.4124</v>
+        <v>10.6782</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.24</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3446</v>
+        <v>0.2878</v>
       </c>
       <c r="J315" t="n">
-        <v>8.9596</v>
+        <v>7.4828</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5357</v>
+        <v>-0.5453</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.9282</v>
+        <v>-14.1778</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.03</v>
       </c>
       <c r="I317" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="J317" t="n">
-        <v>2.5376</v>
+        <v>2.1554</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>1.01</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0516</v>
+        <v>0.0412</v>
       </c>
       <c r="J318" t="n">
-        <v>1.3416</v>
+        <v>1.0712</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.84</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2004</v>
+        <v>-0.1813</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.2104</v>
+        <v>-4.7138</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.76</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.279</v>
+        <v>-0.2603</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.254</v>
+        <v>-6.7678</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.72</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3168</v>
+        <v>-0.2996</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.236800000000001</v>
+        <v>-7.7896</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.327</v>
+        <v>0.2809</v>
       </c>
       <c r="J322" t="n">
-        <v>8.829000000000001</v>
+        <v>7.5843</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>0.86</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1745</v>
+        <v>-0.1581</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.7115</v>
+        <v>-4.2687</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>0.76</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2722</v>
+        <v>-0.2545</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.3494</v>
+        <v>-6.8715</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>0.73</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3002</v>
+        <v>-0.2831</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.105399999999999</v>
+        <v>-7.6437</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4537</v>
+        <v>-0.4473</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.2499</v>
+        <v>-12.0771</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>2.06</v>
       </c>
       <c r="I327" t="n">
-        <v>1.7923</v>
+        <v>1.8563</v>
       </c>
       <c r="J327" t="n">
-        <v>48.3921</v>
+        <v>50.1201</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.19</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5118</v>
+        <v>0.481</v>
       </c>
       <c r="J328" t="n">
-        <v>13.8186</v>
+        <v>12.987</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4199</v>
+        <v>0.3878</v>
       </c>
       <c r="J329" t="n">
-        <v>11.3373</v>
+        <v>10.4706</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.06</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1846</v>
+        <v>0.1568</v>
       </c>
       <c r="J330" t="n">
-        <v>4.9842</v>
+        <v>4.2336</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.99</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1087</v>
+        <v>-0.0888</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.9349</v>
+        <v>-2.3976</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.24</v>
       </c>
       <c r="I332" t="n">
-        <v>0.4886</v>
+        <v>0.4296</v>
       </c>
       <c r="J332" t="n">
-        <v>14.1694</v>
+        <v>12.4584</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.282</v>
+        <v>0.2339</v>
       </c>
       <c r="J333" t="n">
-        <v>8.178000000000001</v>
+        <v>6.7831</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.08</v>
       </c>
       <c r="I334" t="n">
-        <v>0.205</v>
+        <v>0.1649</v>
       </c>
       <c r="J334" t="n">
-        <v>5.945</v>
+        <v>4.7821</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>0.98</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0464</v>
+        <v>-0.035</v>
       </c>
       <c r="J335" t="n">
-        <v>-1.3456</v>
+        <v>-1.015</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>0.84</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2165</v>
+        <v>-0.196</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.2785</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.36</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9298</v>
+        <v>0.9176</v>
       </c>
       <c r="J337" t="n">
-        <v>26.9642</v>
+        <v>26.6104</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.17</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4718</v>
       </c>
       <c r="J338" t="n">
-        <v>14.8944</v>
+        <v>13.6822</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.96</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1708</v>
+        <v>-0.1387</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.9532</v>
+        <v>-4.0223</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.92</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.29</v>
+        <v>-0.2497</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.41</v>
+        <v>-7.2413</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.65</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.917</v>
+        <v>-0.9035</v>
       </c>
       <c r="J341" t="n">
-        <v>-26.593</v>
+        <v>-26.2015</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.65</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3279</v>
+        <v>1.3528</v>
       </c>
       <c r="J342" t="n">
-        <v>46.4765</v>
+        <v>47.348</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.37</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9117</v>
+        <v>0.8949</v>
       </c>
       <c r="J343" t="n">
-        <v>31.9095</v>
+        <v>31.3215</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2539</v>
+        <v>-0.215</v>
       </c>
       <c r="J344" t="n">
-        <v>-8.8865</v>
+        <v>-7.525</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4689</v>
+        <v>-0.4271</v>
       </c>
       <c r="J345" t="n">
-        <v>-16.4115</v>
+        <v>-14.9485</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.8</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.612</v>
+        <v>-0.5756</v>
       </c>
       <c r="J346" t="n">
-        <v>-21.42</v>
+        <v>-20.146</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.24</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5081</v>
+        <v>0.4496</v>
       </c>
       <c r="J347" t="n">
-        <v>17.7835</v>
+        <v>15.736</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>0.93</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1093</v>
+        <v>-0.0921</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.8255</v>
+        <v>-3.2235</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>0.92</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1213</v>
+        <v>-0.1033</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.2455</v>
+        <v>-3.6155</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.92</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1213</v>
+        <v>-0.1033</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.2455</v>
+        <v>-3.6155</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.1989</v>
+        <v>-0.1784</v>
       </c>
       <c r="J351" t="n">
-        <v>-6.9615</v>
+        <v>-6.244</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.32</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8207</v>
+        <v>0.7956</v>
       </c>
       <c r="J352" t="n">
-        <v>24.621</v>
+        <v>23.868</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.08</v>
       </c>
       <c r="I353" t="n">
-        <v>0.2735</v>
+        <v>0.2382</v>
       </c>
       <c r="J353" t="n">
-        <v>8.205</v>
+        <v>7.146</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.05</v>
       </c>
       <c r="I354" t="n">
-        <v>0.1879</v>
+        <v>0.1586</v>
       </c>
       <c r="J354" t="n">
-        <v>5.637</v>
+        <v>4.758</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>1.01</v>
       </c>
       <c r="I355" t="n">
-        <v>0.0457</v>
+        <v>0.0343</v>
       </c>
       <c r="J355" t="n">
-        <v>1.371</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.99</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.0736</v>
+        <v>-0.0536</v>
       </c>
       <c r="J356" t="n">
-        <v>-2.208</v>
+        <v>-1.608</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.49</v>
       </c>
       <c r="I357" t="n">
-        <v>0.8783</v>
+        <v>0.8312</v>
       </c>
       <c r="J357" t="n">
-        <v>26.349</v>
+        <v>24.936</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>1.35</v>
       </c>
       <c r="I358" t="n">
-        <v>0.6705</v>
+        <v>0.6127</v>
       </c>
       <c r="J358" t="n">
-        <v>20.115</v>
+        <v>18.381</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.92</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.125</v>
+        <v>-0.1062</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.75</v>
+        <v>-3.186</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.7</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3491</v>
+        <v>-0.3345</v>
       </c>
       <c r="J360" t="n">
-        <v>-10.473</v>
+        <v>-10.035</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.62</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.421</v>
+        <v>-0.4131</v>
       </c>
       <c r="J361" t="n">
-        <v>-12.63</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.317</v>
+        <v>0.2608</v>
       </c>
       <c r="J362" t="n">
-        <v>8.875999999999999</v>
+        <v>7.3024</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>1.19</v>
       </c>
       <c r="I363" t="n">
-        <v>0.2926</v>
+        <v>0.239</v>
       </c>
       <c r="J363" t="n">
-        <v>8.1928</v>
+        <v>6.692</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2167</v>
+        <v>0.1724</v>
       </c>
       <c r="J364" t="n">
-        <v>6.0676</v>
+        <v>4.8272</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>1.11</v>
       </c>
       <c r="I365" t="n">
-        <v>0.1902</v>
+        <v>0.1497</v>
       </c>
       <c r="J365" t="n">
-        <v>5.3256</v>
+        <v>4.1916</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.0344</v>
+        <v>-0.0252</v>
       </c>
       <c r="J366" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.7056</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.2</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3313</v>
+        <v>0.3218</v>
       </c>
       <c r="J367" t="n">
-        <v>9.276400000000001</v>
+        <v>9.010400000000001</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.09</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1763</v>
+        <v>0.1606</v>
       </c>
       <c r="J368" t="n">
-        <v>4.9364</v>
+        <v>4.4968</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.01</v>
       </c>
       <c r="I369" t="n">
-        <v>0.0303</v>
+        <v>0.0238</v>
       </c>
       <c r="J369" t="n">
-        <v>0.8484</v>
+        <v>0.6664</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>0.98</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.0463</v>
+        <v>-0.0349</v>
       </c>
       <c r="J370" t="n">
-        <v>-1.2964</v>
+        <v>-0.9772</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.97</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.0619</v>
+        <v>-0.0484</v>
       </c>
       <c r="J371" t="n">
-        <v>-1.7332</v>
+        <v>-1.3552</v>
       </c>
     </row>
     <row r="372">
@@ -16769,10 +16769,10 @@
         <v>1.2</v>
       </c>
       <c r="I372" t="n">
-        <v>0.4275</v>
+        <v>0.3701</v>
       </c>
       <c r="J372" t="n">
-        <v>12.3975</v>
+        <v>10.7329</v>
       </c>
     </row>
     <row r="373">
@@ -16809,10 +16809,10 @@
         <v>1.08</v>
       </c>
       <c r="I373" t="n">
-        <v>0.2081</v>
+        <v>0.1669</v>
       </c>
       <c r="J373" t="n">
-        <v>6.0349</v>
+        <v>4.8401</v>
       </c>
     </row>
     <row r="374">
@@ -16849,10 +16849,10 @@
         <v>0.99</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.027</v>
+        <v>-0.0192</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.783</v>
+        <v>-0.5568</v>
       </c>
     </row>
     <row r="375">
@@ -16889,10 +16889,10 @@
         <v>0.95</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.0882</v>
+        <v>-0.0721</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.5578</v>
+        <v>-2.0909</v>
       </c>
     </row>
     <row r="376">
@@ -16929,10 +16929,10 @@
         <v>0.92</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.126</v>
+        <v>-0.1071</v>
       </c>
       <c r="J376" t="n">
-        <v>-3.654</v>
+        <v>-3.1059</v>
       </c>
     </row>
     <row r="377">
@@ -16969,10 +16969,10 @@
         <v>1.18</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5153</v>
+        <v>0.4758</v>
       </c>
       <c r="J377" t="n">
-        <v>14.9437</v>
+        <v>13.7982</v>
       </c>
     </row>
     <row r="378">
@@ -17009,10 +17009,10 @@
         <v>1.16</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4691</v>
+        <v>0.4294</v>
       </c>
       <c r="J378" t="n">
-        <v>13.6039</v>
+        <v>12.4526</v>
       </c>
     </row>
     <row r="379">
@@ -17049,10 +17049,10 @@
         <v>1.14</v>
       </c>
       <c r="I379" t="n">
-        <v>0.422</v>
+        <v>0.3825</v>
       </c>
       <c r="J379" t="n">
-        <v>12.238</v>
+        <v>11.0925</v>
       </c>
     </row>
     <row r="380">
@@ -17089,10 +17089,10 @@
         <v>1.09</v>
       </c>
       <c r="I380" t="n">
-        <v>0.2986</v>
+        <v>0.2627</v>
       </c>
       <c r="J380" t="n">
-        <v>8.6594</v>
+        <v>7.6183</v>
       </c>
     </row>
     <row r="381">
@@ -17129,10 +17129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.2498</v>
+        <v>-0.2109</v>
       </c>
       <c r="J381" t="n">
-        <v>-7.2442</v>
+        <v>-6.1161</v>
       </c>
     </row>
     <row r="382">
@@ -17169,10 +17169,10 @@
         <v>0.96</v>
       </c>
       <c r="I382" t="n">
-        <v>-0.0211</v>
+        <v>-0.0045</v>
       </c>
       <c r="J382" t="n">
-        <v>-0.4642</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="383">
@@ -17209,10 +17209,10 @@
         <v>0.89</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.1148</v>
+        <v>-0.0973</v>
       </c>
       <c r="J383" t="n">
-        <v>-2.5256</v>
+        <v>-2.1406</v>
       </c>
     </row>
     <row r="384">
@@ -17249,10 +17249,10 @@
         <v>0.88</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1269</v>
+        <v>-0.1095</v>
       </c>
       <c r="J384" t="n">
-        <v>-2.7918</v>
+        <v>-2.409</v>
       </c>
     </row>
     <row r="385">
@@ -17289,10 +17289,10 @@
         <v>0.34</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.6292</v>
+        <v>-0.6465</v>
       </c>
       <c r="J385" t="n">
-        <v>-13.8424</v>
+        <v>-14.223</v>
       </c>
     </row>
     <row r="386">
@@ -17329,10 +17329,10 @@
         <v>0.26</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6982</v>
+        <v>-0.7292</v>
       </c>
       <c r="J386" t="n">
-        <v>-15.3604</v>
+        <v>-16.0424</v>
       </c>
     </row>
     <row r="387">
@@ -17369,10 +17369,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>1.35</v>
+        <v>1.3722</v>
       </c>
       <c r="J387" t="n">
-        <v>29.7</v>
+        <v>30.1884</v>
       </c>
     </row>
     <row r="388">
@@ -17409,10 +17409,10 @@
         <v>1.51</v>
       </c>
       <c r="I388" t="n">
-        <v>1.0834</v>
+        <v>1.0971</v>
       </c>
       <c r="J388" t="n">
-        <v>23.8348</v>
+        <v>24.1362</v>
       </c>
     </row>
     <row r="389">
@@ -17449,10 +17449,10 @@
         <v>1.35</v>
       </c>
       <c r="I389" t="n">
-        <v>0.8234</v>
+        <v>0.8105</v>
       </c>
       <c r="J389" t="n">
-        <v>18.1148</v>
+        <v>17.831</v>
       </c>
     </row>
     <row r="390">
@@ -17489,10 +17489,10 @@
         <v>1.29</v>
       </c>
       <c r="I390" t="n">
-        <v>0.7059</v>
+        <v>0.6861</v>
       </c>
       <c r="J390" t="n">
-        <v>15.5298</v>
+        <v>15.0942</v>
       </c>
     </row>
     <row r="391">
@@ -17529,10 +17529,10 @@
         <v>1.18</v>
       </c>
       <c r="I391" t="n">
-        <v>0.4712</v>
+        <v>0.4411</v>
       </c>
       <c r="J391" t="n">
-        <v>10.3664</v>
+        <v>9.7042</v>
       </c>
     </row>
     <row r="392">
@@ -17569,10 +17569,10 @@
         <v>1.27</v>
       </c>
       <c r="I392" t="n">
-        <v>0.6925</v>
+        <v>0.6622</v>
       </c>
       <c r="J392" t="n">
-        <v>18.6975</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="393">
@@ -17609,10 +17609,10 @@
         <v>1.27</v>
       </c>
       <c r="I393" t="n">
-        <v>0.6925</v>
+        <v>0.6622</v>
       </c>
       <c r="J393" t="n">
-        <v>18.6975</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="394">
@@ -17649,10 +17649,10 @@
         <v>1.19</v>
       </c>
       <c r="I394" t="n">
-        <v>0.5243</v>
+        <v>0.4896</v>
       </c>
       <c r="J394" t="n">
-        <v>14.1561</v>
+        <v>13.2192</v>
       </c>
     </row>
     <row r="395">
@@ -17689,10 +17689,10 @@
         <v>1.18</v>
       </c>
       <c r="I395" t="n">
-        <v>0.5024</v>
+        <v>0.4676</v>
       </c>
       <c r="J395" t="n">
-        <v>13.5648</v>
+        <v>12.6252</v>
       </c>
     </row>
     <row r="396">
@@ -17729,10 +17729,10 @@
         <v>1.07</v>
       </c>
       <c r="I396" t="n">
-        <v>0.2293</v>
+        <v>0.1996</v>
       </c>
       <c r="J396" t="n">
-        <v>6.1911</v>
+        <v>5.3892</v>
       </c>
     </row>
     <row r="397">
@@ -17769,10 +17769,10 @@
         <v>1.37</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7144</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="J397" t="n">
-        <v>19.2888</v>
+        <v>17.8146</v>
       </c>
     </row>
     <row r="398">
@@ -17809,10 +17809,10 @@
         <v>1.08</v>
       </c>
       <c r="I398" t="n">
-        <v>0.2171</v>
+        <v>0.1738</v>
       </c>
       <c r="J398" t="n">
-        <v>5.8617</v>
+        <v>4.6926</v>
       </c>
     </row>
     <row r="399">
@@ -17849,10 +17849,10 @@
         <v>0.83</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J399" t="n">
-        <v>-5.9346</v>
+        <v>-5.3811</v>
       </c>
     </row>
     <row r="400">
@@ -17889,10 +17889,10 @@
         <v>0.83</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J400" t="n">
-        <v>-5.9346</v>
+        <v>-5.3811</v>
       </c>
     </row>
     <row r="401">
@@ -17929,10 +17929,10 @@
         <v>0.76</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.289</v>
+        <v>-0.2704</v>
       </c>
       <c r="J401" t="n">
-        <v>-7.803</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="402">
@@ -17969,10 +17969,10 @@
         <v>1.44</v>
       </c>
       <c r="I402" t="n">
-        <v>1.018</v>
+        <v>1.0181</v>
       </c>
       <c r="J402" t="n">
-        <v>28.504</v>
+        <v>28.5068</v>
       </c>
     </row>
     <row r="403">
@@ -18009,10 +18009,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5243</v>
+        <v>0.4896</v>
       </c>
       <c r="J403" t="n">
-        <v>14.6804</v>
+        <v>13.7088</v>
       </c>
     </row>
     <row r="404">
@@ -18049,10 +18049,10 @@
         <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.4801</v>
+        <v>0.4452</v>
       </c>
       <c r="J404" t="n">
-        <v>13.4428</v>
+        <v>12.4656</v>
       </c>
     </row>
     <row r="405">
@@ -18089,10 +18089,10 @@
         <v>1.14</v>
       </c>
       <c r="I405" t="n">
-        <v>0.4105</v>
+        <v>0.3759</v>
       </c>
       <c r="J405" t="n">
-        <v>11.494</v>
+        <v>10.5252</v>
       </c>
     </row>
     <row r="406">
@@ -18129,10 +18129,10 @@
         <v>1.04</v>
       </c>
       <c r="I406" t="n">
-        <v>0.1385</v>
+        <v>0.1148</v>
       </c>
       <c r="J406" t="n">
-        <v>3.878</v>
+        <v>3.2144</v>
       </c>
     </row>
     <row r="407">
@@ -18169,10 +18169,10 @@
         <v>1.06</v>
       </c>
       <c r="I407" t="n">
-        <v>0.1836</v>
+        <v>0.144</v>
       </c>
       <c r="J407" t="n">
-        <v>5.1408</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="408">
@@ -18209,10 +18209,10 @@
         <v>0.96</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0558</v>
       </c>
       <c r="J408" t="n">
-        <v>-1.9068</v>
+        <v>-1.5624</v>
       </c>
     </row>
     <row r="409">
@@ -18249,10 +18249,10 @@
         <v>0.9</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.141</v>
+        <v>-0.1227</v>
       </c>
       <c r="J409" t="n">
-        <v>-3.948</v>
+        <v>-3.4356</v>
       </c>
     </row>
     <row r="410">
@@ -18289,10 +18289,10 @@
         <v>0.88</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1631</v>
+        <v>-0.1438</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.5668</v>
+        <v>-4.0264</v>
       </c>
     </row>
     <row r="411">
@@ -18329,10 +18329,10 @@
         <v>0.84</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.2053</v>
+        <v>-0.1852</v>
       </c>
       <c r="J411" t="n">
-        <v>-5.7484</v>
+        <v>-5.1856</v>
       </c>
     </row>
     <row r="412">
@@ -18369,10 +18369,10 @@
         <v>1.76</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4252</v>
+        <v>1.4524</v>
       </c>
       <c r="J412" t="n">
-        <v>32.7796</v>
+        <v>33.4052</v>
       </c>
     </row>
     <row r="413">
@@ -18409,10 +18409,10 @@
         <v>1.57</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1806</v>
+        <v>1.1948</v>
       </c>
       <c r="J413" t="n">
-        <v>27.1538</v>
+        <v>27.4804</v>
       </c>
     </row>
     <row r="414">
@@ -18449,10 +18449,10 @@
         <v>1.22</v>
       </c>
       <c r="I414" t="n">
-        <v>0.5777</v>
+        <v>0.5484</v>
       </c>
       <c r="J414" t="n">
-        <v>13.2871</v>
+        <v>12.6132</v>
       </c>
     </row>
     <row r="415">
@@ -18489,10 +18489,10 @@
         <v>1.02</v>
       </c>
       <c r="I415" t="n">
-        <v>0.0527</v>
+        <v>0.0361</v>
       </c>
       <c r="J415" t="n">
-        <v>1.2121</v>
+        <v>0.8303</v>
       </c>
     </row>
     <row r="416">
@@ -18529,10 +18529,10 @@
         <v>0.87</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4722</v>
+        <v>-0.4344</v>
       </c>
       <c r="J416" t="n">
-        <v>-10.8606</v>
+        <v>-9.991199999999999</v>
       </c>
     </row>
     <row r="417">
@@ -18569,10 +18569,10 @@
         <v>0.95</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.0687</v>
+        <v>-0.0569</v>
       </c>
       <c r="J417" t="n">
-        <v>-1.5801</v>
+        <v>-1.3087</v>
       </c>
     </row>
     <row r="418">
@@ -18609,10 +18609,10 @@
         <v>0.9</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.1315</v>
+        <v>-0.1162</v>
       </c>
       <c r="J418" t="n">
-        <v>-3.0245</v>
+        <v>-2.6726</v>
       </c>
     </row>
     <row r="419">
@@ -18649,10 +18649,10 @@
         <v>0.79</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.2448</v>
+        <v>-0.2268</v>
       </c>
       <c r="J419" t="n">
-        <v>-5.6304</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="420">
@@ -18689,10 +18689,10 @@
         <v>0.75</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J420" t="n">
-        <v>-6.5044</v>
+        <v>-6.095</v>
       </c>
     </row>
     <row r="421">
@@ -18729,10 +18729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3385</v>
+        <v>-0.3228</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.7855</v>
+        <v>-7.4244</v>
       </c>
     </row>
     <row r="422">
@@ -18769,10 +18769,10 @@
         <v>2.18</v>
       </c>
       <c r="I422" t="n">
-        <v>1.8509</v>
+        <v>1.9129</v>
       </c>
       <c r="J422" t="n">
-        <v>33.3162</v>
+        <v>34.4322</v>
       </c>
     </row>
     <row r="423">
@@ -18809,10 +18809,10 @@
         <v>1.8</v>
       </c>
       <c r="I423" t="n">
-        <v>1.4175</v>
+        <v>1.4465</v>
       </c>
       <c r="J423" t="n">
-        <v>25.515</v>
+        <v>26.037</v>
       </c>
     </row>
     <row r="424">
@@ -18849,10 +18849,10 @@
         <v>1.52</v>
       </c>
       <c r="I424" t="n">
-        <v>1.0805</v>
+        <v>1.1008</v>
       </c>
       <c r="J424" t="n">
-        <v>19.449</v>
+        <v>19.8144</v>
       </c>
     </row>
     <row r="425">
@@ -18889,10 +18889,10 @@
         <v>1.29</v>
       </c>
       <c r="I425" t="n">
-        <v>0.6785</v>
+        <v>0.6595</v>
       </c>
       <c r="J425" t="n">
-        <v>12.213</v>
+        <v>11.871</v>
       </c>
     </row>
     <row r="426">
@@ -18929,10 +18929,10 @@
         <v>1.26</v>
       </c>
       <c r="I426" t="n">
-        <v>0.6169</v>
+        <v>0.5938</v>
       </c>
       <c r="J426" t="n">
-        <v>11.1042</v>
+        <v>10.6884</v>
       </c>
     </row>
     <row r="427">
@@ -18969,10 +18969,10 @@
         <v>0.92</v>
       </c>
       <c r="I427" t="n">
-        <v>-0.0319</v>
+        <v>0.0038</v>
       </c>
       <c r="J427" t="n">
-        <v>-0.5742</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="428">
@@ -19009,10 +19009,10 @@
         <v>0.63</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.3581</v>
+        <v>-0.3507</v>
       </c>
       <c r="J428" t="n">
-        <v>-6.4458</v>
+        <v>-6.3126</v>
       </c>
     </row>
     <row r="429">
@@ -19049,10 +19049,10 @@
         <v>0.44</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.5241</v>
+        <v>-0.5252</v>
       </c>
       <c r="J429" t="n">
-        <v>-9.4338</v>
+        <v>-9.4536</v>
       </c>
     </row>
     <row r="430">
@@ -19089,10 +19089,10 @@
         <v>0.4</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.5596</v>
+        <v>-0.5647</v>
       </c>
       <c r="J430" t="n">
-        <v>-10.0728</v>
+        <v>-10.1646</v>
       </c>
     </row>
     <row r="431">
@@ -19129,10 +19129,10 @@
         <v>0.33</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6223</v>
+        <v>-0.6365</v>
       </c>
       <c r="J431" t="n">
-        <v>-11.2014</v>
+        <v>-11.457</v>
       </c>
     </row>
     <row r="432">
@@ -19169,10 +19169,10 @@
         <v>1.35</v>
       </c>
       <c r="I432" t="n">
-        <v>0.5238</v>
+        <v>0.537</v>
       </c>
       <c r="J432" t="n">
-        <v>18.333</v>
+        <v>18.795</v>
       </c>
     </row>
     <row r="433">
@@ -19209,10 +19209,10 @@
         <v>1.15</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2677</v>
+        <v>0.2537</v>
       </c>
       <c r="J433" t="n">
-        <v>9.3695</v>
+        <v>8.8795</v>
       </c>
     </row>
     <row r="434">
@@ -19249,10 +19249,10 @@
         <v>0.95</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.0878</v>
+        <v>-0.0717</v>
       </c>
       <c r="J434" t="n">
-        <v>-3.073</v>
+        <v>-2.5095</v>
       </c>
     </row>
     <row r="435">
@@ -19289,10 +19289,10 @@
         <v>0.83</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.2242</v>
+        <v>-0.2037</v>
       </c>
       <c r="J435" t="n">
-        <v>-7.847</v>
+        <v>-7.1295</v>
       </c>
     </row>
     <row r="436">
@@ -19329,10 +19329,10 @@
         <v>0.83</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.2242</v>
+        <v>-0.2037</v>
       </c>
       <c r="J436" t="n">
-        <v>-7.847</v>
+        <v>-7.1295</v>
       </c>
     </row>
     <row r="437">
@@ -19369,10 +19369,10 @@
         <v>1.48</v>
       </c>
       <c r="I437" t="n">
-        <v>0.6303</v>
+        <v>0.5603</v>
       </c>
       <c r="J437" t="n">
-        <v>22.0605</v>
+        <v>19.6105</v>
       </c>
     </row>
     <row r="438">
@@ -19409,10 +19409,10 @@
         <v>1.14</v>
       </c>
       <c r="I438" t="n">
-        <v>0.2353</v>
+        <v>0.1871</v>
       </c>
       <c r="J438" t="n">
-        <v>8.2355</v>
+        <v>6.5485</v>
       </c>
     </row>
     <row r="439">
@@ -19449,10 +19449,10 @@
         <v>1.01</v>
       </c>
       <c r="I439" t="n">
-        <v>0.0275</v>
+        <v>0.0182</v>
       </c>
       <c r="J439" t="n">
-        <v>0.9625</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="440">
@@ -19489,10 +19489,10 @@
         <v>0.86</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.1965</v>
+        <v>-0.1759</v>
       </c>
       <c r="J440" t="n">
-        <v>-6.8775</v>
+        <v>-6.1565</v>
       </c>
     </row>
     <row r="441">
@@ -19529,10 +19529,10 @@
         <v>0.83</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.2278</v>
+        <v>-0.2076</v>
       </c>
       <c r="J441" t="n">
-        <v>-7.973</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="442">
@@ -19569,10 +19569,10 @@
         <v>2.01</v>
       </c>
       <c r="I442" t="n">
-        <v>1.6865</v>
+        <v>1.7332</v>
       </c>
       <c r="J442" t="n">
-        <v>35.4165</v>
+        <v>36.3972</v>
       </c>
     </row>
     <row r="443">
@@ -19609,10 +19609,10 @@
         <v>1.55</v>
       </c>
       <c r="I443" t="n">
-        <v>1.1286</v>
+        <v>1.1455</v>
       </c>
       <c r="J443" t="n">
-        <v>23.7006</v>
+        <v>24.0555</v>
       </c>
     </row>
     <row r="444">
@@ -19649,10 +19649,10 @@
         <v>1.39</v>
       </c>
       <c r="I444" t="n">
-        <v>0.8915</v>
+        <v>0.8857</v>
       </c>
       <c r="J444" t="n">
-        <v>18.7215</v>
+        <v>18.5997</v>
       </c>
     </row>
     <row r="445">
@@ -19689,10 +19689,10 @@
         <v>1.36</v>
       </c>
       <c r="I445" t="n">
-        <v>0.8351</v>
+        <v>0.8252</v>
       </c>
       <c r="J445" t="n">
-        <v>17.5371</v>
+        <v>17.3292</v>
       </c>
     </row>
     <row r="446">
@@ -19729,10 +19729,10 @@
         <v>1.03</v>
       </c>
       <c r="I446" t="n">
-        <v>0.0618</v>
+        <v>0.0376</v>
       </c>
       <c r="J446" t="n">
-        <v>1.2978</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="447">
@@ -19769,10 +19769,10 @@
         <v>0.97</v>
       </c>
       <c r="I447" t="n">
-        <v>-0.0146</v>
+        <v>-0.0015</v>
       </c>
       <c r="J447" t="n">
-        <v>-0.3066</v>
+        <v>-0.0315</v>
       </c>
     </row>
     <row r="448">
@@ -19809,10 +19809,10 @@
         <v>0.87</v>
       </c>
       <c r="I448" t="n">
-        <v>-0.1461</v>
+        <v>-0.13</v>
       </c>
       <c r="J448" t="n">
-        <v>-3.0681</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="449">
@@ -19849,10 +19849,10 @@
         <v>0.65</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.3612</v>
+        <v>-0.3484</v>
       </c>
       <c r="J449" t="n">
-        <v>-7.5852</v>
+        <v>-7.3164</v>
       </c>
     </row>
     <row r="450">
@@ -19889,10 +19889,10 @@
         <v>0.54</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.4586</v>
+        <v>-0.4524</v>
       </c>
       <c r="J450" t="n">
-        <v>-9.630599999999999</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="451">
@@ -19929,10 +19929,10 @@
         <v>0.46</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5306</v>
       </c>
       <c r="J451" t="n">
-        <v>-11.1027</v>
+        <v>-11.1426</v>
       </c>
     </row>
     <row r="452">
@@ -19969,10 +19969,10 @@
         <v>1.69</v>
       </c>
       <c r="I452" t="n">
-        <v>1.3583</v>
+        <v>1.3826</v>
       </c>
       <c r="J452" t="n">
-        <v>39.3907</v>
+        <v>40.0954</v>
       </c>
     </row>
     <row r="453">
@@ -20009,10 +20009,10 @@
         <v>1.27</v>
       </c>
       <c r="I453" t="n">
-        <v>0.6918</v>
+        <v>0.6616</v>
       </c>
       <c r="J453" t="n">
-        <v>20.0622</v>
+        <v>19.1864</v>
       </c>
     </row>
     <row r="454">
@@ -20049,10 +20049,10 @@
         <v>1.17</v>
       </c>
       <c r="I454" t="n">
-        <v>0.4796</v>
+        <v>0.4449</v>
       </c>
       <c r="J454" t="n">
-        <v>13.9084</v>
+        <v>12.9021</v>
       </c>
     </row>
     <row r="455">
@@ -20089,10 +20089,10 @@
         <v>0.98</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1349</v>
+        <v>-0.1077</v>
       </c>
       <c r="J455" t="n">
-        <v>-3.9121</v>
+        <v>-3.1233</v>
       </c>
     </row>
     <row r="456">
@@ -20129,10 +20129,10 @@
         <v>0.89</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.4065</v>
+        <v>-0.3654</v>
       </c>
       <c r="J456" t="n">
-        <v>-11.7885</v>
+        <v>-10.5966</v>
       </c>
     </row>
     <row r="457">
@@ -20169,10 +20169,10 @@
         <v>1.3</v>
       </c>
       <c r="I457" t="n">
-        <v>0.593</v>
+        <v>0.5337</v>
       </c>
       <c r="J457" t="n">
-        <v>17.197</v>
+        <v>15.4773</v>
       </c>
     </row>
     <row r="458">
@@ -20209,10 +20209,10 @@
         <v>1.23</v>
       </c>
       <c r="I458" t="n">
-        <v>0.4803</v>
+        <v>0.4215</v>
       </c>
       <c r="J458" t="n">
-        <v>13.9287</v>
+        <v>12.2235</v>
       </c>
     </row>
     <row r="459">
@@ -20249,10 +20249,10 @@
         <v>0.95</v>
       </c>
       <c r="I459" t="n">
-        <v>-0.0873</v>
+        <v>-0.0713</v>
       </c>
       <c r="J459" t="n">
-        <v>-2.5317</v>
+        <v>-2.0677</v>
       </c>
     </row>
     <row r="460">
@@ -20289,10 +20289,10 @@
         <v>0.8</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.2539</v>
+        <v>-0.2341</v>
       </c>
       <c r="J460" t="n">
-        <v>-7.3631</v>
+        <v>-6.7889</v>
       </c>
     </row>
     <row r="461">
@@ -20329,10 +20329,10 @@
         <v>0.8</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.2539</v>
+        <v>-0.2341</v>
       </c>
       <c r="J461" t="n">
-        <v>-7.3631</v>
+        <v>-6.7889</v>
       </c>
     </row>
   </sheetData>
